--- a/Excel/video_durations.xlsx
+++ b/Excel/video_durations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="512" documentId="8_{A44FB3EB-EA2D-470D-AC31-D31F9A62D29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05569F59-0A13-4992-9A70-13B14219FE2F}"/>
+  <xr:revisionPtr revIDLastSave="531" documentId="8_{A44FB3EB-EA2D-470D-AC31-D31F9A62D29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60AABC6F-7DD5-4BE5-A63F-AB05F7966748}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="876" windowWidth="16260" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12192" yWindow="876" windowWidth="10608" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="video_durations" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="906">
   <si>
     <t>artist</t>
   </si>
@@ -2745,6 +2745,12 @@
   </si>
   <si>
     <t>Like a Prayer</t>
+  </si>
+  <si>
+    <t>Disturbed</t>
+  </si>
+  <si>
+    <t>I'm Not A Girl, Not Yet A Woman</t>
   </si>
 </sst>
 </file>
@@ -3307,10 +3313,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3628,7 +3630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H371"/>
+  <dimension ref="A1:H373"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4471,7 +4473,7 @@
         <v>571</v>
       </c>
       <c r="C41" s="3">
-        <f t="shared" ref="C41:C55" si="0">C40+1</f>
+        <f t="shared" ref="C41:C54" si="0">C40+1</f>
         <v>46156</v>
       </c>
       <c r="D41" t="s">
@@ -4576,10 +4578,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>783</v>
+        <v>115</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>781</v>
+        <v>885</v>
       </c>
       <c r="C46" s="3">
         <f t="shared" si="0"/>
@@ -4589,52 +4591,43 @@
         <v>831</v>
       </c>
       <c r="E46" t="s">
-        <v>784</v>
+        <v>117</v>
       </c>
       <c r="F46">
-        <v>275.5</v>
+        <v>359.67</v>
       </c>
       <c r="G46">
-        <v>4.5916666666666597</v>
+        <v>5.9945000000000004</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>115</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>885</v>
+        <v>867</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>868</v>
       </c>
       <c r="C47" s="3">
         <f t="shared" si="0"/>
         <v>46162</v>
       </c>
       <c r="D47" t="s">
-        <v>831</v>
-      </c>
-      <c r="E47" t="s">
-        <v>117</v>
-      </c>
-      <c r="F47">
-        <v>359.67</v>
-      </c>
-      <c r="G47">
-        <v>5.9945000000000004</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>867</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>868</v>
+        <v>858</v>
+      </c>
+      <c r="B48" t="s">
+        <v>859</v>
       </c>
       <c r="C48" s="3">
         <f t="shared" si="0"/>
         <v>46163</v>
       </c>
       <c r="D48" t="s">
-        <v>9</v>
+        <v>831</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -4654,10 +4647,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>858</v>
-      </c>
-      <c r="B50" t="s">
-        <v>859</v>
+        <v>880</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>881</v>
       </c>
       <c r="C50" s="3">
         <f t="shared" si="0"/>
@@ -4669,25 +4662,34 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>880</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>881</v>
+        <v>499</v>
+      </c>
+      <c r="B51" t="s">
+        <v>500</v>
       </c>
       <c r="C51" s="3">
         <f t="shared" si="0"/>
         <v>46166</v>
       </c>
       <c r="D51" t="s">
-        <v>831</v>
+        <v>9</v>
+      </c>
+      <c r="E51" t="s">
+        <v>501</v>
+      </c>
+      <c r="F51">
+        <v>267.75</v>
+      </c>
+      <c r="G51">
+        <v>4.4625000000000004</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>499</v>
-      </c>
-      <c r="B52" t="s">
-        <v>500</v>
+        <v>878</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>879</v>
       </c>
       <c r="C52" s="3">
         <f t="shared" si="0"/>
@@ -4696,82 +4698,73 @@
       <c r="D52" t="s">
         <v>9</v>
       </c>
-      <c r="E52" t="s">
-        <v>501</v>
-      </c>
-      <c r="F52">
-        <v>267.75</v>
-      </c>
-      <c r="G52">
-        <v>4.4625000000000004</v>
-      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>878</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>879</v>
+        <v>860</v>
+      </c>
+      <c r="B53" t="s">
+        <v>861</v>
       </c>
       <c r="C53" s="3">
         <f t="shared" si="0"/>
         <v>46168</v>
       </c>
       <c r="D53" t="s">
-        <v>9</v>
+        <v>831</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>860</v>
+        <v>424</v>
       </c>
       <c r="B54" t="s">
-        <v>861</v>
+        <v>425</v>
       </c>
       <c r="C54" s="3">
         <f t="shared" si="0"/>
         <v>46169</v>
       </c>
       <c r="D54" t="s">
-        <v>831</v>
+        <v>9</v>
+      </c>
+      <c r="E54" t="s">
+        <v>426</v>
+      </c>
+      <c r="F54">
+        <v>254.75</v>
+      </c>
+      <c r="G54">
+        <v>4.24583333333333</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>424</v>
-      </c>
-      <c r="B55" t="s">
-        <v>425</v>
+        <v>886</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>887</v>
       </c>
       <c r="C55" s="3">
-        <f t="shared" si="0"/>
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" t="s">
-        <v>426</v>
-      </c>
-      <c r="F55">
-        <v>254.75</v>
-      </c>
-      <c r="G55">
-        <v>4.24583333333333</v>
+        <v>831</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>886</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>887</v>
+        <v>835</v>
+      </c>
+      <c r="B56" t="s">
+        <v>905</v>
       </c>
       <c r="C56" s="3">
-        <v>46174</v>
+        <f>C55+1</f>
+        <v>46175</v>
       </c>
       <c r="D56" t="s">
-        <v>831</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -4782,7 +4775,8 @@
         <v>889</v>
       </c>
       <c r="C57" s="3">
-        <v>46175</v>
+        <f t="shared" ref="C57:C61" si="1">C56+1</f>
+        <v>46176</v>
       </c>
       <c r="D57" t="s">
         <v>831</v>
@@ -4796,87 +4790,91 @@
         <v>891</v>
       </c>
       <c r="C58" s="3">
-        <v>46176</v>
+        <f t="shared" si="1"/>
+        <v>46177</v>
       </c>
       <c r="D58" t="s">
-        <v>831</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>137</v>
+        <v>904</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>688</v>
       </c>
       <c r="C59" s="3">
-        <v>46182</v>
+        <f t="shared" si="1"/>
+        <v>46178</v>
       </c>
       <c r="D59" t="s">
-        <v>9</v>
+        <v>831</v>
       </c>
       <c r="E59" t="s">
-        <v>139</v>
+        <v>689</v>
       </c>
       <c r="F59">
-        <v>225.25</v>
+        <v>239</v>
       </c>
       <c r="G59">
-        <v>3.7541666666666602</v>
+        <v>3.9833333333333298</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="B60" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="C60" s="3">
-        <v>46327</v>
+        <f t="shared" si="1"/>
+        <v>46179</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="F60">
-        <v>232.96</v>
+        <v>225.25</v>
       </c>
       <c r="G60">
-        <v>3.88266666666666</v>
+        <v>3.7541666666666602</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>294</v>
-      </c>
-      <c r="B61" t="s">
-        <v>295</v>
+        <v>783</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>781</v>
       </c>
       <c r="C61" s="3">
-        <v>46327</v>
+        <f t="shared" si="1"/>
+        <v>46180</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>831</v>
       </c>
       <c r="E61" t="s">
-        <v>296</v>
+        <v>784</v>
       </c>
       <c r="F61">
-        <v>207.13</v>
+        <v>275.5</v>
       </c>
       <c r="G61">
-        <v>3.4521666666666602</v>
+        <v>4.5916666666666597</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>210</v>
+        <v>167</v>
       </c>
       <c r="B62" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="C62" s="3">
         <v>46327</v>
@@ -4885,21 +4883,21 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="F62">
-        <v>227.71</v>
+        <v>232.96</v>
       </c>
       <c r="G62">
-        <v>3.7951666666666601</v>
+        <v>3.88266666666666</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>210</v>
+        <v>294</v>
       </c>
       <c r="B63" t="s">
-        <v>584</v>
+        <v>295</v>
       </c>
       <c r="C63" s="3">
         <v>46327</v>
@@ -4908,13 +4906,13 @@
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>585</v>
+        <v>296</v>
       </c>
       <c r="F63">
-        <v>234</v>
+        <v>207.13</v>
       </c>
       <c r="G63">
-        <v>3.9</v>
+        <v>3.4521666666666602</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -4922,7 +4920,7 @@
         <v>210</v>
       </c>
       <c r="B64" t="s">
-        <v>614</v>
+        <v>211</v>
       </c>
       <c r="C64" s="3">
         <v>46327</v>
@@ -4931,21 +4929,21 @@
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>615</v>
+        <v>212</v>
       </c>
       <c r="F64">
-        <v>285.04000000000002</v>
+        <v>227.71</v>
       </c>
       <c r="G64">
-        <v>4.7506666666666604</v>
+        <v>3.7951666666666601</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B65" t="s">
-        <v>197</v>
+        <v>584</v>
       </c>
       <c r="C65" s="3">
         <v>46327</v>
@@ -4954,21 +4952,21 @@
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>198</v>
+        <v>585</v>
       </c>
       <c r="F65">
-        <v>283.13</v>
+        <v>234</v>
       </c>
       <c r="G65">
-        <v>4.7188333333333299</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>683</v>
+        <v>210</v>
       </c>
       <c r="B66" t="s">
-        <v>684</v>
+        <v>614</v>
       </c>
       <c r="C66" s="3">
         <v>46327</v>
@@ -4977,21 +4975,21 @@
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>685</v>
+        <v>615</v>
       </c>
       <c r="F66">
-        <v>236.71</v>
+        <v>285.04000000000002</v>
       </c>
       <c r="G66">
-        <v>3.94516666666666</v>
+        <v>4.7506666666666604</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B67" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="C67" s="3">
         <v>46327</v>
@@ -5000,21 +4998,21 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="F67">
-        <v>212.88</v>
+        <v>283.13</v>
       </c>
       <c r="G67">
-        <v>3.548</v>
+        <v>4.7188333333333299</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>258</v>
+        <v>683</v>
       </c>
       <c r="B68" t="s">
-        <v>259</v>
+        <v>684</v>
       </c>
       <c r="C68" s="3">
         <v>46327</v>
@@ -5023,21 +5021,21 @@
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>260</v>
+        <v>685</v>
       </c>
       <c r="F68">
-        <v>232.96</v>
+        <v>236.71</v>
       </c>
       <c r="G68">
-        <v>3.88266666666666</v>
+        <v>3.94516666666666</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>234</v>
       </c>
       <c r="C69" s="3">
         <v>46327</v>
@@ -5046,21 +5044,21 @@
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>28</v>
+        <v>235</v>
       </c>
       <c r="F69">
-        <v>251.54</v>
+        <v>212.88</v>
       </c>
       <c r="G69">
-        <v>4.1923333333333304</v>
+        <v>3.548</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>310</v>
+        <v>258</v>
       </c>
       <c r="B70" t="s">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="C70" s="3">
         <v>46327</v>
@@ -5069,21 +5067,21 @@
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>312</v>
+        <v>260</v>
       </c>
       <c r="F70">
-        <v>260.25</v>
+        <v>232.96</v>
       </c>
       <c r="G70">
-        <v>4.3375000000000004</v>
+        <v>3.88266666666666</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="B71" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="C71" s="3">
         <v>46327</v>
@@ -5092,21 +5090,21 @@
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="F71">
-        <v>355.04</v>
+        <v>251.54</v>
       </c>
       <c r="G71">
-        <v>5.91733333333333</v>
+        <v>4.1923333333333304</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>483</v>
+        <v>310</v>
       </c>
       <c r="B72" t="s">
-        <v>484</v>
+        <v>311</v>
       </c>
       <c r="C72" s="3">
         <v>46327</v>
@@ -5115,21 +5113,21 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>485</v>
+        <v>312</v>
       </c>
       <c r="F72">
-        <v>271.20999999999998</v>
+        <v>260.25</v>
       </c>
       <c r="G72">
-        <v>4.5201666666666602</v>
+        <v>4.3375000000000004</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>734</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>735</v>
+        <v>88</v>
       </c>
       <c r="C73" s="3">
         <v>46327</v>
@@ -5138,21 +5136,21 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>736</v>
+        <v>89</v>
       </c>
       <c r="F73">
-        <v>230.25</v>
+        <v>355.04</v>
       </c>
       <c r="G73">
-        <v>3.8374999999999999</v>
+        <v>5.91733333333333</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>734</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s">
-        <v>737</v>
+        <v>484</v>
       </c>
       <c r="C74" s="3">
         <v>46327</v>
@@ -5161,35 +5159,44 @@
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>738</v>
+        <v>485</v>
       </c>
       <c r="F74">
-        <v>272.42</v>
+        <v>271.20999999999998</v>
       </c>
       <c r="G74">
-        <v>4.5403333333333302</v>
+        <v>4.5201666666666602</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>432</v>
+        <v>734</v>
       </c>
       <c r="B75" t="s">
-        <v>836</v>
+        <v>735</v>
       </c>
       <c r="C75" s="3">
         <v>46327</v>
       </c>
       <c r="D75" t="s">
         <v>9</v>
+      </c>
+      <c r="E75" t="s">
+        <v>736</v>
+      </c>
+      <c r="F75">
+        <v>230.25</v>
+      </c>
+      <c r="G75">
+        <v>3.8374999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>565</v>
+        <v>734</v>
       </c>
       <c r="B76" t="s">
-        <v>566</v>
+        <v>737</v>
       </c>
       <c r="C76" s="3">
         <v>46327</v>
@@ -5198,44 +5205,35 @@
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>567</v>
+        <v>738</v>
       </c>
       <c r="F76">
-        <v>180.13</v>
+        <v>272.42</v>
       </c>
       <c r="G76">
-        <v>3.00216666666666</v>
+        <v>4.5403333333333302</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>432</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>836</v>
       </c>
       <c r="C77" s="3">
         <v>46327</v>
       </c>
       <c r="D77" t="s">
         <v>9</v>
-      </c>
-      <c r="E77" t="s">
-        <v>25</v>
-      </c>
-      <c r="F77">
-        <v>300.13</v>
-      </c>
-      <c r="G77">
-        <v>5.0021666666666604</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>565</v>
       </c>
       <c r="B78" t="s">
-        <v>154</v>
+        <v>566</v>
       </c>
       <c r="C78" s="3">
         <v>46327</v>
@@ -5244,13 +5242,13 @@
         <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>155</v>
+        <v>567</v>
       </c>
       <c r="F78">
-        <v>258.20999999999998</v>
+        <v>180.13</v>
       </c>
       <c r="G78">
-        <v>4.3034999999999997</v>
+        <v>3.00216666666666</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -5258,7 +5256,7 @@
         <v>23</v>
       </c>
       <c r="B79" t="s">
-        <v>183</v>
+        <v>24</v>
       </c>
       <c r="C79" s="3">
         <v>46327</v>
@@ -5267,13 +5265,13 @@
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>184</v>
+        <v>25</v>
       </c>
       <c r="F79">
-        <v>211.32999999999899</v>
+        <v>300.13</v>
       </c>
       <c r="G79">
-        <v>3.52216666666666</v>
+        <v>5.0021666666666604</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -5281,7 +5279,7 @@
         <v>23</v>
       </c>
       <c r="B80" t="s">
-        <v>288</v>
+        <v>154</v>
       </c>
       <c r="C80" s="3">
         <v>46327</v>
@@ -5290,13 +5288,13 @@
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>289</v>
+        <v>155</v>
       </c>
       <c r="F80">
-        <v>191.88</v>
+        <v>258.20999999999998</v>
       </c>
       <c r="G80">
-        <v>3.198</v>
+        <v>4.3034999999999997</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -5304,7 +5302,7 @@
         <v>23</v>
       </c>
       <c r="B81" t="s">
-        <v>290</v>
+        <v>183</v>
       </c>
       <c r="C81" s="3">
         <v>46327</v>
@@ -5313,13 +5311,13 @@
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>291</v>
+        <v>184</v>
       </c>
       <c r="F81">
-        <v>431.42</v>
+        <v>211.32999999999899</v>
       </c>
       <c r="G81">
-        <v>7.1903333333333297</v>
+        <v>3.52216666666666</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -5327,7 +5325,7 @@
         <v>23</v>
       </c>
       <c r="B82" t="s">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="C82" s="3">
         <v>46327</v>
@@ -5336,13 +5334,13 @@
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>365</v>
+        <v>289</v>
       </c>
       <c r="F82">
-        <v>147.25</v>
+        <v>191.88</v>
       </c>
       <c r="G82">
-        <v>2.4541666666666599</v>
+        <v>3.198</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -5350,7 +5348,7 @@
         <v>23</v>
       </c>
       <c r="B83" t="s">
-        <v>404</v>
+        <v>290</v>
       </c>
       <c r="C83" s="3">
         <v>46327</v>
@@ -5359,13 +5357,13 @@
         <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>405</v>
+        <v>291</v>
       </c>
       <c r="F83">
-        <v>243.08</v>
+        <v>431.42</v>
       </c>
       <c r="G83">
-        <v>4.0513333333333303</v>
+        <v>7.1903333333333297</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -5373,7 +5371,7 @@
         <v>23</v>
       </c>
       <c r="B84" t="s">
-        <v>546</v>
+        <v>364</v>
       </c>
       <c r="C84" s="3">
         <v>46327</v>
@@ -5382,13 +5380,13 @@
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>547</v>
+        <v>365</v>
       </c>
       <c r="F84">
-        <v>186.88</v>
+        <v>147.25</v>
       </c>
       <c r="G84">
-        <v>3.1146666666666598</v>
+        <v>2.4541666666666599</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -5396,7 +5394,7 @@
         <v>23</v>
       </c>
       <c r="B85" t="s">
-        <v>620</v>
+        <v>404</v>
       </c>
       <c r="C85" s="3">
         <v>46327</v>
@@ -5405,13 +5403,13 @@
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>621</v>
+        <v>405</v>
       </c>
       <c r="F85">
-        <v>188</v>
+        <v>243.08</v>
       </c>
       <c r="G85">
-        <v>3.1333333333333302</v>
+        <v>4.0513333333333303</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -5419,7 +5417,7 @@
         <v>23</v>
       </c>
       <c r="B86" t="s">
-        <v>634</v>
+        <v>546</v>
       </c>
       <c r="C86" s="3">
         <v>46327</v>
@@ -5428,13 +5426,13 @@
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>635</v>
+        <v>547</v>
       </c>
       <c r="F86">
-        <v>250.63</v>
+        <v>186.88</v>
       </c>
       <c r="G86">
-        <v>4.1771666666666603</v>
+        <v>3.1146666666666598</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -5442,7 +5440,7 @@
         <v>23</v>
       </c>
       <c r="B87" t="s">
-        <v>759</v>
+        <v>620</v>
       </c>
       <c r="C87" s="3">
         <v>46327</v>
@@ -5451,13 +5449,13 @@
         <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>760</v>
+        <v>621</v>
       </c>
       <c r="F87">
-        <v>285.04000000000002</v>
+        <v>188</v>
       </c>
       <c r="G87">
-        <v>4.7506666666666604</v>
+        <v>3.1333333333333302</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -5465,7 +5463,7 @@
         <v>23</v>
       </c>
       <c r="B88" t="s">
-        <v>800</v>
+        <v>634</v>
       </c>
       <c r="C88" s="3">
         <v>46327</v>
@@ -5474,21 +5472,21 @@
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>801</v>
+        <v>635</v>
       </c>
       <c r="F88">
-        <v>127.5</v>
+        <v>250.63</v>
       </c>
       <c r="G88">
-        <v>2.125</v>
+        <v>4.1771666666666603</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>313</v>
+        <v>23</v>
       </c>
       <c r="B89" t="s">
-        <v>314</v>
+        <v>759</v>
       </c>
       <c r="C89" s="3">
         <v>46327</v>
@@ -5497,21 +5495,21 @@
         <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>315</v>
+        <v>760</v>
       </c>
       <c r="F89">
-        <v>237.88</v>
+        <v>285.04000000000002</v>
       </c>
       <c r="G89">
-        <v>3.9646666666666599</v>
+        <v>4.7506666666666604</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>313</v>
+        <v>23</v>
       </c>
       <c r="B90" t="s">
-        <v>316</v>
+        <v>800</v>
       </c>
       <c r="C90" s="3">
         <v>46327</v>
@@ -5520,13 +5518,13 @@
         <v>9</v>
       </c>
       <c r="E90" t="s">
-        <v>317</v>
+        <v>801</v>
       </c>
       <c r="F90">
-        <v>260.79000000000002</v>
+        <v>127.5</v>
       </c>
       <c r="G90">
-        <v>4.3464999999999998</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -5534,7 +5532,7 @@
         <v>313</v>
       </c>
       <c r="B91" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="C91" s="3">
         <v>46327</v>
@@ -5543,13 +5541,13 @@
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="F91">
-        <v>189.79</v>
+        <v>237.88</v>
       </c>
       <c r="G91">
-        <v>3.16316666666666</v>
+        <v>3.9646666666666599</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -5557,7 +5555,7 @@
         <v>313</v>
       </c>
       <c r="B92" t="s">
-        <v>380</v>
+        <v>316</v>
       </c>
       <c r="C92" s="3">
         <v>46327</v>
@@ -5566,13 +5564,13 @@
         <v>9</v>
       </c>
       <c r="E92" t="s">
-        <v>381</v>
+        <v>317</v>
       </c>
       <c r="F92">
-        <v>170.79</v>
+        <v>260.79000000000002</v>
       </c>
       <c r="G92">
-        <v>2.8464999999999998</v>
+        <v>4.3464999999999998</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -5580,7 +5578,7 @@
         <v>313</v>
       </c>
       <c r="B93" t="s">
-        <v>450</v>
+        <v>334</v>
       </c>
       <c r="C93" s="3">
         <v>46327</v>
@@ -5589,13 +5587,13 @@
         <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>451</v>
+        <v>335</v>
       </c>
       <c r="F93">
-        <v>174.13</v>
+        <v>189.79</v>
       </c>
       <c r="G93">
-        <v>2.9021666666666599</v>
+        <v>3.16316666666666</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -5603,7 +5601,7 @@
         <v>313</v>
       </c>
       <c r="B94" t="s">
-        <v>492</v>
+        <v>380</v>
       </c>
       <c r="C94" s="3">
         <v>46327</v>
@@ -5612,13 +5610,13 @@
         <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>493</v>
+        <v>381</v>
       </c>
       <c r="F94">
-        <v>208.82999999999899</v>
+        <v>170.79</v>
       </c>
       <c r="G94">
-        <v>3.4804999999999899</v>
+        <v>2.8464999999999998</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -5626,7 +5624,7 @@
         <v>313</v>
       </c>
       <c r="B95" t="s">
-        <v>627</v>
+        <v>450</v>
       </c>
       <c r="C95" s="3">
         <v>46327</v>
@@ -5635,13 +5633,13 @@
         <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>628</v>
+        <v>451</v>
       </c>
       <c r="F95">
-        <v>287.75</v>
+        <v>174.13</v>
       </c>
       <c r="G95">
-        <v>4.7958333333333298</v>
+        <v>2.9021666666666599</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -5649,7 +5647,7 @@
         <v>313</v>
       </c>
       <c r="B96" t="s">
-        <v>713</v>
+        <v>492</v>
       </c>
       <c r="C96" s="3">
         <v>46327</v>
@@ -5658,13 +5656,13 @@
         <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>714</v>
+        <v>493</v>
       </c>
       <c r="F96">
-        <v>182.21</v>
+        <v>208.82999999999899</v>
       </c>
       <c r="G96">
-        <v>3.0368333333333299</v>
+        <v>3.4804999999999899</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -5672,7 +5670,7 @@
         <v>313</v>
       </c>
       <c r="B97" t="s">
-        <v>715</v>
+        <v>627</v>
       </c>
       <c r="C97" s="3">
         <v>46327</v>
@@ -5681,13 +5679,13 @@
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>716</v>
+        <v>628</v>
       </c>
       <c r="F97">
-        <v>299.25</v>
+        <v>287.75</v>
       </c>
       <c r="G97">
-        <v>4.9874999999999998</v>
+        <v>4.7958333333333298</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -5695,7 +5693,7 @@
         <v>313</v>
       </c>
       <c r="B98" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="C98" s="3">
         <v>46327</v>
@@ -5704,13 +5702,13 @@
         <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="F98">
-        <v>303.5</v>
+        <v>182.21</v>
       </c>
       <c r="G98">
-        <v>5.05833333333333</v>
+        <v>3.0368333333333299</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -5718,7 +5716,7 @@
         <v>313</v>
       </c>
       <c r="B99" t="s">
-        <v>796</v>
+        <v>715</v>
       </c>
       <c r="C99" s="3">
         <v>46327</v>
@@ -5727,13 +5725,13 @@
         <v>9</v>
       </c>
       <c r="E99" t="s">
-        <v>797</v>
+        <v>716</v>
       </c>
       <c r="F99">
-        <v>205.07999999999899</v>
+        <v>299.25</v>
       </c>
       <c r="G99">
-        <v>3.4179999999999899</v>
+        <v>4.9874999999999998</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -5741,7 +5739,7 @@
         <v>313</v>
       </c>
       <c r="B100" t="s">
-        <v>808</v>
+        <v>720</v>
       </c>
       <c r="C100" s="3">
         <v>46327</v>
@@ -5750,21 +5748,21 @@
         <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>809</v>
+        <v>721</v>
       </c>
       <c r="F100">
-        <v>262.33</v>
+        <v>303.5</v>
       </c>
       <c r="G100">
-        <v>4.3721666666666597</v>
+        <v>5.05833333333333</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>70</v>
+        <v>313</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>796</v>
       </c>
       <c r="C101" s="3">
         <v>46327</v>
@@ -5773,21 +5771,21 @@
         <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>72</v>
+        <v>797</v>
       </c>
       <c r="F101">
-        <v>206.04</v>
+        <v>205.07999999999899</v>
       </c>
       <c r="G101">
-        <v>3.4339999999999899</v>
+        <v>3.4179999999999899</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>70</v>
+        <v>313</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>808</v>
       </c>
       <c r="C102" s="3">
         <v>46327</v>
@@ -5796,13 +5794,13 @@
         <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>103</v>
+        <v>809</v>
       </c>
       <c r="F102">
-        <v>211.13</v>
+        <v>262.33</v>
       </c>
       <c r="G102">
-        <v>3.5188333333333301</v>
+        <v>4.3721666666666597</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -5810,7 +5808,7 @@
         <v>70</v>
       </c>
       <c r="B103" t="s">
-        <v>435</v>
+        <v>71</v>
       </c>
       <c r="C103" s="3">
         <v>46327</v>
@@ -5819,44 +5817,44 @@
         <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>436</v>
+        <v>72</v>
       </c>
       <c r="F103">
-        <v>200.54</v>
+        <v>206.04</v>
       </c>
       <c r="G103">
-        <v>3.3423333333333298</v>
+        <v>3.4339999999999899</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>862</v>
+        <v>70</v>
       </c>
       <c r="B104" t="s">
-        <v>478</v>
+        <v>102</v>
       </c>
       <c r="C104" s="3">
         <v>46327</v>
       </c>
       <c r="D104" t="s">
-        <v>831</v>
+        <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>479</v>
+        <v>103</v>
       </c>
       <c r="F104">
-        <v>432.08</v>
+        <v>211.13</v>
       </c>
       <c r="G104">
-        <v>7.2013333333333298</v>
+        <v>3.5188333333333301</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>541</v>
+        <v>70</v>
       </c>
       <c r="B105" t="s">
-        <v>542</v>
+        <v>435</v>
       </c>
       <c r="C105" s="3">
         <v>46327</v>
@@ -5865,35 +5863,44 @@
         <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>543</v>
+        <v>436</v>
       </c>
       <c r="F105">
-        <v>170.17</v>
+        <v>200.54</v>
       </c>
       <c r="G105">
-        <v>2.8361666666666601</v>
+        <v>3.3423333333333298</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>874</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>875</v>
+        <v>862</v>
+      </c>
+      <c r="B106" t="s">
+        <v>478</v>
       </c>
       <c r="C106" s="3">
         <v>46327</v>
       </c>
       <c r="D106" t="s">
-        <v>9</v>
+        <v>831</v>
+      </c>
+      <c r="E106" t="s">
+        <v>479</v>
+      </c>
+      <c r="F106">
+        <v>432.08</v>
+      </c>
+      <c r="G106">
+        <v>7.2013333333333298</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>112</v>
+        <v>541</v>
       </c>
       <c r="B107" t="s">
-        <v>113</v>
+        <v>542</v>
       </c>
       <c r="C107" s="3">
         <v>46327</v>
@@ -5902,36 +5909,27 @@
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>114</v>
+        <v>543</v>
       </c>
       <c r="F107">
-        <v>169.13</v>
+        <v>170.17</v>
       </c>
       <c r="G107">
-        <v>2.81883333333333</v>
+        <v>2.8361666666666601</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>112</v>
-      </c>
-      <c r="B108" t="s">
-        <v>394</v>
+        <v>874</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>875</v>
       </c>
       <c r="C108" s="3">
         <v>46327</v>
       </c>
       <c r="D108" t="s">
         <v>9</v>
-      </c>
-      <c r="E108" t="s">
-        <v>395</v>
-      </c>
-      <c r="F108">
-        <v>151.54</v>
-      </c>
-      <c r="G108">
-        <v>2.5256666666666598</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -5939,7 +5937,7 @@
         <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>409</v>
+        <v>113</v>
       </c>
       <c r="C109" s="3">
         <v>46327</v>
@@ -5948,13 +5946,13 @@
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>410</v>
+        <v>114</v>
       </c>
       <c r="F109">
-        <v>369.83</v>
+        <v>169.13</v>
       </c>
       <c r="G109">
-        <v>6.1638333333333302</v>
+        <v>2.81883333333333</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
@@ -5962,7 +5960,7 @@
         <v>112</v>
       </c>
       <c r="B110" t="s">
-        <v>473</v>
+        <v>394</v>
       </c>
       <c r="C110" s="3">
         <v>46327</v>
@@ -5971,13 +5969,13 @@
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>474</v>
+        <v>395</v>
       </c>
       <c r="F110">
-        <v>332.13</v>
+        <v>151.54</v>
       </c>
       <c r="G110">
-        <v>5.5354999999999999</v>
+        <v>2.5256666666666598</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
@@ -5985,7 +5983,7 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>663</v>
+        <v>409</v>
       </c>
       <c r="C111" s="3">
         <v>46327</v>
@@ -5994,13 +5992,13 @@
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>664</v>
+        <v>410</v>
       </c>
       <c r="F111">
-        <v>267.92</v>
+        <v>369.83</v>
       </c>
       <c r="G111">
-        <v>4.46533333333333</v>
+        <v>6.1638333333333302</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
@@ -6008,7 +6006,7 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>690</v>
+        <v>473</v>
       </c>
       <c r="C112" s="3">
         <v>46327</v>
@@ -6017,21 +6015,21 @@
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>691</v>
+        <v>474</v>
       </c>
       <c r="F112">
-        <v>196.63</v>
+        <v>332.13</v>
       </c>
       <c r="G112">
-        <v>3.2771666666666599</v>
+        <v>5.5354999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>496</v>
+        <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>497</v>
+        <v>663</v>
       </c>
       <c r="C113" s="3">
         <v>46327</v>
@@ -6040,21 +6038,21 @@
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>498</v>
+        <v>664</v>
       </c>
       <c r="F113">
-        <v>413.38</v>
+        <v>267.92</v>
       </c>
       <c r="G113">
-        <v>6.8896666666666597</v>
+        <v>4.46533333333333</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>30</v>
+        <v>690</v>
       </c>
       <c r="C114" s="3">
         <v>46327</v>
@@ -6063,21 +6061,21 @@
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>31</v>
+        <v>691</v>
       </c>
       <c r="F114">
-        <v>333.96</v>
+        <v>196.63</v>
       </c>
       <c r="G114">
-        <v>5.5659999999999998</v>
+        <v>3.2771666666666599</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="B115" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="C115" s="3">
         <v>46327</v>
@@ -6086,21 +6084,21 @@
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="F115">
-        <v>254.13</v>
+        <v>413.38</v>
       </c>
       <c r="G115">
-        <v>4.2355</v>
+        <v>6.8896666666666597</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>300</v>
+        <v>29</v>
       </c>
       <c r="B116" t="s">
-        <v>301</v>
+        <v>30</v>
       </c>
       <c r="C116" s="3">
         <v>46327</v>
@@ -6109,21 +6107,21 @@
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>302</v>
+        <v>31</v>
       </c>
       <c r="F116">
-        <v>233.38</v>
+        <v>333.96</v>
       </c>
       <c r="G116">
-        <v>3.8896666666666602</v>
+        <v>5.5659999999999998</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>191</v>
+        <v>507</v>
       </c>
       <c r="B117" t="s">
-        <v>192</v>
+        <v>508</v>
       </c>
       <c r="C117" s="3">
         <v>46327</v>
@@ -6132,21 +6130,21 @@
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>193</v>
+        <v>509</v>
       </c>
       <c r="F117">
-        <v>231.79</v>
+        <v>254.13</v>
       </c>
       <c r="G117">
-        <v>3.8631666666666602</v>
+        <v>4.2355</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>415</v>
+        <v>300</v>
       </c>
       <c r="B118" t="s">
-        <v>416</v>
+        <v>301</v>
       </c>
       <c r="C118" s="3">
         <v>46327</v>
@@ -6155,21 +6153,21 @@
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>417</v>
+        <v>302</v>
       </c>
       <c r="F118">
-        <v>248.88</v>
+        <v>233.38</v>
       </c>
       <c r="G118">
-        <v>4.1479999999999997</v>
+        <v>3.8896666666666602</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>321</v>
+        <v>191</v>
       </c>
       <c r="B119" t="s">
-        <v>322</v>
+        <v>192</v>
       </c>
       <c r="C119" s="3">
         <v>46327</v>
@@ -6178,21 +6176,21 @@
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="F119">
-        <v>284.95999999999998</v>
+        <v>231.79</v>
       </c>
       <c r="G119">
-        <v>4.7493333333333299</v>
+        <v>3.8631666666666602</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>717</v>
+        <v>415</v>
       </c>
       <c r="B120" t="s">
-        <v>718</v>
+        <v>416</v>
       </c>
       <c r="C120" s="3">
         <v>46327</v>
@@ -6201,21 +6199,21 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>719</v>
+        <v>417</v>
       </c>
       <c r="F120">
-        <v>333.96</v>
+        <v>248.88</v>
       </c>
       <c r="G120">
-        <v>5.5659999999999998</v>
+        <v>4.1479999999999997</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>213</v>
+        <v>321</v>
       </c>
       <c r="B121" t="s">
-        <v>214</v>
+        <v>322</v>
       </c>
       <c r="C121" s="3">
         <v>46327</v>
@@ -6224,21 +6222,21 @@
         <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>215</v>
+        <v>323</v>
       </c>
       <c r="F121">
-        <v>254.71</v>
+        <v>284.95999999999998</v>
       </c>
       <c r="G121">
-        <v>4.2451666666666599</v>
+        <v>4.7493333333333299</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>62</v>
+        <v>717</v>
       </c>
       <c r="B122" t="s">
-        <v>63</v>
+        <v>718</v>
       </c>
       <c r="C122" s="3">
         <v>46327</v>
@@ -6247,21 +6245,21 @@
         <v>9</v>
       </c>
       <c r="E122" t="s">
-        <v>64</v>
+        <v>719</v>
       </c>
       <c r="F122">
-        <v>216.71</v>
+        <v>333.96</v>
       </c>
       <c r="G122">
-        <v>3.6118333333333301</v>
+        <v>5.5659999999999998</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>65</v>
+        <v>214</v>
       </c>
       <c r="C123" s="3">
         <v>46327</v>
@@ -6270,13 +6268,13 @@
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>66</v>
+        <v>215</v>
       </c>
       <c r="F123">
-        <v>151</v>
+        <v>254.71</v>
       </c>
       <c r="G123">
-        <v>2.5166666666666599</v>
+        <v>4.2451666666666599</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
@@ -6284,7 +6282,7 @@
         <v>62</v>
       </c>
       <c r="B124" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="C124" s="3">
         <v>46327</v>
@@ -6293,13 +6291,13 @@
         <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>176</v>
+        <v>64</v>
       </c>
       <c r="F124">
-        <v>188.42</v>
+        <v>216.71</v>
       </c>
       <c r="G124">
-        <v>3.1403333333333299</v>
+        <v>3.6118333333333301</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
@@ -6307,7 +6305,7 @@
         <v>62</v>
       </c>
       <c r="B125" t="s">
-        <v>231</v>
+        <v>65</v>
       </c>
       <c r="C125" s="3">
         <v>46327</v>
@@ -6316,13 +6314,13 @@
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>232</v>
+        <v>66</v>
       </c>
       <c r="F125">
-        <v>188.08</v>
+        <v>151</v>
       </c>
       <c r="G125">
-        <v>3.1346666666666598</v>
+        <v>2.5166666666666599</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
@@ -6330,7 +6328,7 @@
         <v>62</v>
       </c>
       <c r="B126" t="s">
-        <v>359</v>
+        <v>175</v>
       </c>
       <c r="C126" s="3">
         <v>46327</v>
@@ -6339,13 +6337,13 @@
         <v>9</v>
       </c>
       <c r="E126" t="s">
-        <v>360</v>
+        <v>176</v>
       </c>
       <c r="F126">
-        <v>153.38</v>
+        <v>188.42</v>
       </c>
       <c r="G126">
-        <v>2.5563333333333298</v>
+        <v>3.1403333333333299</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
@@ -6353,7 +6351,7 @@
         <v>62</v>
       </c>
       <c r="B127" t="s">
-        <v>443</v>
+        <v>231</v>
       </c>
       <c r="C127" s="3">
         <v>46327</v>
@@ -6362,21 +6360,21 @@
         <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>444</v>
+        <v>232</v>
       </c>
       <c r="F127">
-        <v>198.5</v>
+        <v>188.08</v>
       </c>
       <c r="G127">
-        <v>3.30833333333333</v>
+        <v>3.1346666666666598</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>271</v>
+        <v>62</v>
       </c>
       <c r="B128" t="s">
-        <v>272</v>
+        <v>359</v>
       </c>
       <c r="C128" s="3">
         <v>46327</v>
@@ -6385,21 +6383,21 @@
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>273</v>
+        <v>360</v>
       </c>
       <c r="F128">
-        <v>220.75</v>
+        <v>153.38</v>
       </c>
       <c r="G128">
-        <v>3.67916666666666</v>
+        <v>2.5563333333333298</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>271</v>
+        <v>62</v>
       </c>
       <c r="B129" t="s">
-        <v>387</v>
+        <v>443</v>
       </c>
       <c r="C129" s="3">
         <v>46327</v>
@@ -6408,13 +6406,13 @@
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>388</v>
+        <v>444</v>
       </c>
       <c r="F129">
-        <v>236.82999999999899</v>
+        <v>198.5</v>
       </c>
       <c r="G129">
-        <v>3.9471666666666598</v>
+        <v>3.30833333333333</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -6422,7 +6420,7 @@
         <v>271</v>
       </c>
       <c r="B130" t="s">
-        <v>755</v>
+        <v>272</v>
       </c>
       <c r="C130" s="3">
         <v>46327</v>
@@ -6431,21 +6429,21 @@
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>756</v>
+        <v>273</v>
       </c>
       <c r="F130">
-        <v>214.21</v>
+        <v>220.75</v>
       </c>
       <c r="G130">
-        <v>3.57016666666666</v>
+        <v>3.67916666666666</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>7</v>
+        <v>271</v>
       </c>
       <c r="B131" t="s">
-        <v>8</v>
+        <v>387</v>
       </c>
       <c r="C131" s="3">
         <v>46327</v>
@@ -6454,21 +6452,21 @@
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>10</v>
+        <v>388</v>
       </c>
       <c r="F131">
-        <v>454.25</v>
+        <v>236.82999999999899</v>
       </c>
       <c r="G131">
-        <v>7.5708333333333302</v>
+        <v>3.9471666666666598</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>7</v>
+        <v>271</v>
       </c>
       <c r="B132" t="s">
-        <v>555</v>
+        <v>755</v>
       </c>
       <c r="C132" s="3">
         <v>46327</v>
@@ -6477,13 +6475,13 @@
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>556</v>
+        <v>756</v>
       </c>
       <c r="F132">
-        <v>330.5</v>
+        <v>214.21</v>
       </c>
       <c r="G132">
-        <v>5.5083333333333302</v>
+        <v>3.57016666666666</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -6491,7 +6489,7 @@
         <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>632</v>
+        <v>8</v>
       </c>
       <c r="C133" s="3">
         <v>46327</v>
@@ -6500,21 +6498,21 @@
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>633</v>
+        <v>10</v>
       </c>
       <c r="F133">
-        <v>208.88</v>
+        <v>454.25</v>
       </c>
       <c r="G133">
-        <v>3.4813333333333301</v>
+        <v>7.5708333333333302</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>372</v>
+        <v>7</v>
       </c>
       <c r="B134" t="s">
-        <v>373</v>
+        <v>555</v>
       </c>
       <c r="C134" s="3">
         <v>46327</v>
@@ -6523,21 +6521,21 @@
         <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>374</v>
+        <v>556</v>
       </c>
       <c r="F134">
-        <v>234.07999999999899</v>
+        <v>330.5</v>
       </c>
       <c r="G134">
-        <v>3.90133333333333</v>
+        <v>5.5083333333333302</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>372</v>
+        <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="C135" s="3">
         <v>46327</v>
@@ -6546,13 +6544,13 @@
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="F135">
-        <v>235.54</v>
+        <v>208.88</v>
       </c>
       <c r="G135">
-        <v>3.9256666666666602</v>
+        <v>3.4813333333333301</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -6560,7 +6558,7 @@
         <v>372</v>
       </c>
       <c r="B136" t="s">
-        <v>813</v>
+        <v>373</v>
       </c>
       <c r="C136" s="3">
         <v>46327</v>
@@ -6569,21 +6567,21 @@
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>814</v>
+        <v>374</v>
       </c>
       <c r="F136">
-        <v>296.13</v>
+        <v>234.07999999999899</v>
       </c>
       <c r="G136">
-        <v>4.9355000000000002</v>
+        <v>3.90133333333333</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>741</v>
+        <v>372</v>
       </c>
       <c r="B137" t="s">
-        <v>742</v>
+        <v>609</v>
       </c>
       <c r="C137" s="3">
         <v>46327</v>
@@ -6592,21 +6590,21 @@
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>743</v>
+        <v>610</v>
       </c>
       <c r="F137">
-        <v>186.46</v>
+        <v>235.54</v>
       </c>
       <c r="G137">
-        <v>3.1076666666666601</v>
+        <v>3.9256666666666602</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>35</v>
+        <v>372</v>
       </c>
       <c r="B138" t="s">
-        <v>36</v>
+        <v>813</v>
       </c>
       <c r="C138" s="3">
         <v>46327</v>
@@ -6615,21 +6613,21 @@
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>37</v>
+        <v>814</v>
       </c>
       <c r="F138">
-        <v>237.96</v>
+        <v>296.13</v>
       </c>
       <c r="G138">
-        <v>3.9660000000000002</v>
+        <v>4.9355000000000002</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>35</v>
+        <v>741</v>
       </c>
       <c r="B139" t="s">
-        <v>88</v>
+        <v>742</v>
       </c>
       <c r="C139" s="3">
         <v>46327</v>
@@ -6638,13 +6636,13 @@
         <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>90</v>
+        <v>743</v>
       </c>
       <c r="F139">
-        <v>277.08</v>
+        <v>186.46</v>
       </c>
       <c r="G139">
-        <v>4.6179999999999897</v>
+        <v>3.1076666666666601</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -6652,7 +6650,7 @@
         <v>35</v>
       </c>
       <c r="B140" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="C140" s="3">
         <v>46327</v>
@@ -6661,13 +6659,13 @@
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>355</v>
+        <v>37</v>
       </c>
       <c r="F140">
-        <v>209.88</v>
+        <v>237.96</v>
       </c>
       <c r="G140">
-        <v>3.49799999999999</v>
+        <v>3.9660000000000002</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -6675,7 +6673,7 @@
         <v>35</v>
       </c>
       <c r="B141" t="s">
-        <v>475</v>
+        <v>88</v>
       </c>
       <c r="C141" s="3">
         <v>46327</v>
@@ -6684,13 +6682,13 @@
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>476</v>
+        <v>90</v>
       </c>
       <c r="F141">
-        <v>280.54000000000002</v>
+        <v>277.08</v>
       </c>
       <c r="G141">
-        <v>4.6756666666666602</v>
+        <v>4.6179999999999897</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -6698,7 +6696,7 @@
         <v>35</v>
       </c>
       <c r="B142" t="s">
-        <v>686</v>
+        <v>354</v>
       </c>
       <c r="C142" s="3">
         <v>46327</v>
@@ -6707,13 +6705,13 @@
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>687</v>
+        <v>355</v>
       </c>
       <c r="F142">
-        <v>287.67</v>
+        <v>209.88</v>
       </c>
       <c r="G142">
-        <v>4.7945000000000002</v>
+        <v>3.49799999999999</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -6721,7 +6719,7 @@
         <v>35</v>
       </c>
       <c r="B143" t="s">
-        <v>757</v>
+        <v>475</v>
       </c>
       <c r="C143" s="3">
         <v>46327</v>
@@ -6730,21 +6728,21 @@
         <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>758</v>
+        <v>476</v>
       </c>
       <c r="F143">
-        <v>274.70999999999998</v>
+        <v>280.54000000000002</v>
       </c>
       <c r="G143">
-        <v>4.5785</v>
+        <v>4.6756666666666602</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>356</v>
+        <v>35</v>
       </c>
       <c r="B144" t="s">
-        <v>357</v>
+        <v>686</v>
       </c>
       <c r="C144" s="3">
         <v>46327</v>
@@ -6753,21 +6751,21 @@
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>358</v>
+        <v>687</v>
       </c>
       <c r="F144">
-        <v>236.29</v>
+        <v>287.67</v>
       </c>
       <c r="G144">
-        <v>3.9381666666666599</v>
+        <v>4.7945000000000002</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="B145" t="s">
-        <v>226</v>
+        <v>757</v>
       </c>
       <c r="C145" s="3">
         <v>46327</v>
@@ -6776,21 +6774,21 @@
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>227</v>
+        <v>758</v>
       </c>
       <c r="F145">
-        <v>161.13</v>
+        <v>274.70999999999998</v>
       </c>
       <c r="G145">
-        <v>2.68549999999999</v>
+        <v>4.5785</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>225</v>
+        <v>356</v>
       </c>
       <c r="B146" t="s">
-        <v>557</v>
+        <v>357</v>
       </c>
       <c r="C146" s="3">
         <v>46327</v>
@@ -6799,13 +6797,13 @@
         <v>9</v>
       </c>
       <c r="E146" t="s">
-        <v>558</v>
+        <v>358</v>
       </c>
       <c r="F146">
-        <v>176.96</v>
+        <v>236.29</v>
       </c>
       <c r="G146">
-        <v>2.94933333333333</v>
+        <v>3.9381666666666599</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -6813,7 +6811,7 @@
         <v>225</v>
       </c>
       <c r="B147" t="s">
-        <v>692</v>
+        <v>226</v>
       </c>
       <c r="C147" s="3">
         <v>46327</v>
@@ -6822,21 +6820,21 @@
         <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>693</v>
+        <v>227</v>
       </c>
       <c r="F147">
-        <v>193.75</v>
+        <v>161.13</v>
       </c>
       <c r="G147">
-        <v>3.2291666666666599</v>
+        <v>2.68549999999999</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="B148" t="s">
-        <v>150</v>
+        <v>557</v>
       </c>
       <c r="C148" s="3">
         <v>46327</v>
@@ -6845,21 +6843,21 @@
         <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>151</v>
+        <v>558</v>
       </c>
       <c r="F148">
-        <v>255.96</v>
+        <v>176.96</v>
       </c>
       <c r="G148">
-        <v>4.266</v>
+        <v>2.94933333333333</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="B149" t="s">
-        <v>730</v>
+        <v>692</v>
       </c>
       <c r="C149" s="3">
         <v>46327</v>
@@ -6868,13 +6866,13 @@
         <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>731</v>
+        <v>693</v>
       </c>
       <c r="F149">
-        <v>242.25</v>
+        <v>193.75</v>
       </c>
       <c r="G149">
-        <v>4.0374999999999996</v>
+        <v>3.2291666666666599</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -6882,7 +6880,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>798</v>
+        <v>150</v>
       </c>
       <c r="C150" s="3">
         <v>46327</v>
@@ -6891,21 +6889,21 @@
         <v>9</v>
       </c>
       <c r="E150" t="s">
-        <v>799</v>
+        <v>151</v>
       </c>
       <c r="F150">
-        <v>272.33</v>
+        <v>255.96</v>
       </c>
       <c r="G150">
-        <v>4.5388333333333302</v>
+        <v>4.266</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>200</v>
+        <v>730</v>
       </c>
       <c r="C151" s="3">
         <v>46327</v>
@@ -6914,21 +6912,21 @@
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>201</v>
+        <v>731</v>
       </c>
       <c r="F151">
-        <v>253.33</v>
+        <v>242.25</v>
       </c>
       <c r="G151">
-        <v>4.2221666666666602</v>
+        <v>4.0374999999999996</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="B152" t="s">
-        <v>411</v>
+        <v>798</v>
       </c>
       <c r="C152" s="3">
         <v>46327</v>
@@ -6937,13 +6935,13 @@
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>412</v>
+        <v>799</v>
       </c>
       <c r="F152">
-        <v>277.45999999999998</v>
+        <v>272.33</v>
       </c>
       <c r="G152">
-        <v>4.6243333333333299</v>
+        <v>4.5388333333333302</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
@@ -6951,7 +6949,7 @@
         <v>199</v>
       </c>
       <c r="B153" t="s">
-        <v>825</v>
+        <v>200</v>
       </c>
       <c r="C153" s="3">
         <v>46327</v>
@@ -6960,21 +6958,21 @@
         <v>9</v>
       </c>
       <c r="E153" t="s">
-        <v>826</v>
+        <v>201</v>
       </c>
       <c r="F153">
-        <v>307.25</v>
+        <v>253.33</v>
       </c>
       <c r="G153">
-        <v>5.12083333333333</v>
+        <v>4.2221666666666602</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="B154" t="s">
-        <v>74</v>
+        <v>411</v>
       </c>
       <c r="C154" s="3">
         <v>46327</v>
@@ -6983,21 +6981,21 @@
         <v>9</v>
       </c>
       <c r="E154" t="s">
-        <v>75</v>
+        <v>412</v>
       </c>
       <c r="F154">
-        <v>135.16999999999999</v>
+        <v>277.45999999999998</v>
       </c>
       <c r="G154">
-        <v>2.2528333333333301</v>
+        <v>4.6243333333333299</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="B155" t="s">
-        <v>159</v>
+        <v>825</v>
       </c>
       <c r="C155" s="3">
         <v>46327</v>
@@ -7006,13 +7004,13 @@
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>160</v>
+        <v>826</v>
       </c>
       <c r="F155">
-        <v>178.38</v>
+        <v>307.25</v>
       </c>
       <c r="G155">
-        <v>2.9729999999999999</v>
+        <v>5.12083333333333</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
@@ -7020,7 +7018,7 @@
         <v>73</v>
       </c>
       <c r="B156" t="s">
-        <v>251</v>
+        <v>74</v>
       </c>
       <c r="C156" s="3">
         <v>46327</v>
@@ -7029,13 +7027,13 @@
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="F156">
-        <v>137.13</v>
+        <v>135.16999999999999</v>
       </c>
       <c r="G156">
-        <v>2.2854999999999999</v>
+        <v>2.2528333333333301</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
@@ -7043,7 +7041,7 @@
         <v>73</v>
       </c>
       <c r="B157" t="s">
-        <v>280</v>
+        <v>159</v>
       </c>
       <c r="C157" s="3">
         <v>46327</v>
@@ -7052,13 +7050,13 @@
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>281</v>
+        <v>160</v>
       </c>
       <c r="F157">
-        <v>160.25</v>
+        <v>178.38</v>
       </c>
       <c r="G157">
-        <v>2.6708333333333298</v>
+        <v>2.9729999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
@@ -7066,7 +7064,7 @@
         <v>73</v>
       </c>
       <c r="B158" t="s">
-        <v>559</v>
+        <v>251</v>
       </c>
       <c r="C158" s="3">
         <v>46327</v>
@@ -7075,13 +7073,13 @@
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>560</v>
+        <v>252</v>
       </c>
       <c r="F158">
-        <v>184.46</v>
+        <v>137.13</v>
       </c>
       <c r="G158">
-        <v>3.07433333333333</v>
+        <v>2.2854999999999999</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
@@ -7089,7 +7087,7 @@
         <v>73</v>
       </c>
       <c r="B159" t="s">
-        <v>768</v>
+        <v>280</v>
       </c>
       <c r="C159" s="3">
         <v>46327</v>
@@ -7098,21 +7096,21 @@
         <v>9</v>
       </c>
       <c r="E159" t="s">
-        <v>769</v>
+        <v>281</v>
       </c>
       <c r="F159">
-        <v>144.04</v>
+        <v>160.25</v>
       </c>
       <c r="G159">
-        <v>2.4006666666666598</v>
+        <v>2.6708333333333298</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>535</v>
+        <v>73</v>
       </c>
       <c r="B160" t="s">
-        <v>536</v>
+        <v>559</v>
       </c>
       <c r="C160" s="3">
         <v>46327</v>
@@ -7121,21 +7119,21 @@
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>537</v>
+        <v>560</v>
       </c>
       <c r="F160">
-        <v>185.88</v>
+        <v>184.46</v>
       </c>
       <c r="G160">
-        <v>3.0979999999999999</v>
+        <v>3.07433333333333</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>535</v>
+        <v>73</v>
       </c>
       <c r="B161" t="s">
-        <v>665</v>
+        <v>768</v>
       </c>
       <c r="C161" s="3">
         <v>46327</v>
@@ -7144,13 +7142,13 @@
         <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>666</v>
+        <v>769</v>
       </c>
       <c r="F161">
-        <v>174.17</v>
+        <v>144.04</v>
       </c>
       <c r="G161">
-        <v>2.90283333333333</v>
+        <v>2.4006666666666598</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
@@ -7158,7 +7156,7 @@
         <v>535</v>
       </c>
       <c r="B162" t="s">
-        <v>794</v>
+        <v>536</v>
       </c>
       <c r="C162" s="3">
         <v>46327</v>
@@ -7167,21 +7165,21 @@
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>795</v>
+        <v>537</v>
       </c>
       <c r="F162">
-        <v>232.5</v>
+        <v>185.88</v>
       </c>
       <c r="G162">
-        <v>3.875</v>
+        <v>3.0979999999999999</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>177</v>
+        <v>535</v>
       </c>
       <c r="B163" t="s">
-        <v>178</v>
+        <v>665</v>
       </c>
       <c r="C163" s="3">
         <v>46327</v>
@@ -7190,21 +7188,21 @@
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>179</v>
+        <v>666</v>
       </c>
       <c r="F163">
-        <v>269.54000000000002</v>
+        <v>174.17</v>
       </c>
       <c r="G163">
-        <v>4.4923333333333302</v>
+        <v>2.90283333333333</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>177</v>
+        <v>535</v>
       </c>
       <c r="B164" t="s">
-        <v>389</v>
+        <v>794</v>
       </c>
       <c r="C164" s="3">
         <v>46327</v>
@@ -7213,13 +7211,13 @@
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>390</v>
+        <v>795</v>
       </c>
       <c r="F164">
-        <v>238.5</v>
+        <v>232.5</v>
       </c>
       <c r="G164">
-        <v>3.9750000000000001</v>
+        <v>3.875</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
@@ -7227,7 +7225,7 @@
         <v>177</v>
       </c>
       <c r="B165" t="s">
-        <v>709</v>
+        <v>178</v>
       </c>
       <c r="C165" s="3">
         <v>46327</v>
@@ -7236,21 +7234,21 @@
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>710</v>
+        <v>179</v>
       </c>
       <c r="F165">
-        <v>219.25</v>
+        <v>269.54000000000002</v>
       </c>
       <c r="G165">
-        <v>3.6541666666666601</v>
+        <v>4.4923333333333302</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>261</v>
+        <v>177</v>
       </c>
       <c r="B166" t="s">
-        <v>262</v>
+        <v>389</v>
       </c>
       <c r="C166" s="3">
         <v>46327</v>
@@ -7259,21 +7257,21 @@
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>263</v>
+        <v>390</v>
       </c>
       <c r="F166">
-        <v>266.83</v>
+        <v>238.5</v>
       </c>
       <c r="G166">
-        <v>4.4471666666666598</v>
+        <v>3.9750000000000001</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>261</v>
+        <v>177</v>
       </c>
       <c r="B167" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C167" s="3">
         <v>46327</v>
@@ -7282,13 +7280,13 @@
         <v>9</v>
       </c>
       <c r="E167" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="F167">
-        <v>297.08</v>
+        <v>219.25</v>
       </c>
       <c r="G167">
-        <v>4.9513333333333298</v>
+        <v>3.6541666666666601</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
@@ -7296,7 +7294,7 @@
         <v>261</v>
       </c>
       <c r="B168" t="s">
-        <v>722</v>
+        <v>262</v>
       </c>
       <c r="C168" s="3">
         <v>46327</v>
@@ -7305,21 +7303,21 @@
         <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>723</v>
+        <v>263</v>
       </c>
       <c r="F168">
-        <v>246.5</v>
+        <v>266.83</v>
       </c>
       <c r="G168">
-        <v>4.1083333333333298</v>
+        <v>4.4471666666666598</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>467</v>
+        <v>261</v>
       </c>
       <c r="B169" t="s">
-        <v>468</v>
+        <v>704</v>
       </c>
       <c r="C169" s="3">
         <v>46327</v>
@@ -7328,21 +7326,21 @@
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>469</v>
+        <v>705</v>
       </c>
       <c r="F169">
-        <v>266</v>
+        <v>297.08</v>
       </c>
       <c r="G169">
-        <v>4.43333333333333</v>
+        <v>4.9513333333333298</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>467</v>
+        <v>261</v>
       </c>
       <c r="B170" t="s">
-        <v>516</v>
+        <v>722</v>
       </c>
       <c r="C170" s="3">
         <v>46327</v>
@@ -7351,13 +7349,13 @@
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>517</v>
+        <v>723</v>
       </c>
       <c r="F170">
-        <v>309.29000000000002</v>
+        <v>246.5</v>
       </c>
       <c r="G170">
-        <v>5.1548333333333298</v>
+        <v>4.1083333333333298</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
@@ -7365,7 +7363,7 @@
         <v>467</v>
       </c>
       <c r="B171" t="s">
-        <v>790</v>
+        <v>468</v>
       </c>
       <c r="C171" s="3">
         <v>46327</v>
@@ -7374,21 +7372,21 @@
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>791</v>
+        <v>469</v>
       </c>
       <c r="F171">
-        <v>251.04</v>
+        <v>266</v>
       </c>
       <c r="G171">
-        <v>4.1840000000000002</v>
+        <v>4.43333333333333</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>67</v>
+        <v>467</v>
       </c>
       <c r="B172" t="s">
-        <v>68</v>
+        <v>516</v>
       </c>
       <c r="C172" s="3">
         <v>46327</v>
@@ -7397,35 +7395,44 @@
         <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>69</v>
+        <v>517</v>
       </c>
       <c r="F172">
-        <v>236.04</v>
+        <v>309.29000000000002</v>
       </c>
       <c r="G172">
-        <v>3.9339999999999899</v>
+        <v>5.1548333333333298</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>882</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>883</v>
+        <v>467</v>
+      </c>
+      <c r="B173" t="s">
+        <v>790</v>
       </c>
       <c r="C173" s="3">
         <v>46327</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
+      </c>
+      <c r="E173" t="s">
+        <v>791</v>
+      </c>
+      <c r="F173">
+        <v>251.04</v>
+      </c>
+      <c r="G173">
+        <v>4.1840000000000002</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="B174" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="C174" s="3">
         <v>46327</v>
@@ -7434,36 +7441,27 @@
         <v>9</v>
       </c>
       <c r="E174" t="s">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="F174">
-        <v>615.54</v>
+        <v>236.04</v>
       </c>
       <c r="G174">
-        <v>10.258999999999901</v>
+        <v>3.9339999999999899</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>146</v>
-      </c>
-      <c r="B175" t="s">
-        <v>292</v>
+        <v>882</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>883</v>
       </c>
       <c r="C175" s="3">
         <v>46327</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
-      </c>
-      <c r="E175" t="s">
-        <v>293</v>
-      </c>
-      <c r="F175">
-        <v>367.42</v>
-      </c>
-      <c r="G175">
-        <v>6.1236666666666597</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
@@ -7471,7 +7469,7 @@
         <v>146</v>
       </c>
       <c r="B176" t="s">
-        <v>602</v>
+        <v>147</v>
       </c>
       <c r="C176" s="3">
         <v>46327</v>
@@ -7480,21 +7478,21 @@
         <v>9</v>
       </c>
       <c r="E176" t="s">
-        <v>603</v>
+        <v>148</v>
       </c>
       <c r="F176">
-        <v>342.08</v>
+        <v>615.54</v>
       </c>
       <c r="G176">
-        <v>5.7013333333333298</v>
+        <v>10.258999999999901</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>406</v>
+        <v>146</v>
       </c>
       <c r="B177" t="s">
-        <v>407</v>
+        <v>292</v>
       </c>
       <c r="C177" s="3">
         <v>46327</v>
@@ -7503,21 +7501,21 @@
         <v>9</v>
       </c>
       <c r="E177" t="s">
-        <v>408</v>
+        <v>293</v>
       </c>
       <c r="F177">
-        <v>221.21</v>
+        <v>367.42</v>
       </c>
       <c r="G177">
-        <v>3.6868333333333299</v>
+        <v>6.1236666666666597</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>406</v>
+        <v>146</v>
       </c>
       <c r="B178" t="s">
-        <v>671</v>
+        <v>602</v>
       </c>
       <c r="C178" s="3">
         <v>46327</v>
@@ -7526,13 +7524,13 @@
         <v>9</v>
       </c>
       <c r="E178" t="s">
-        <v>672</v>
+        <v>603</v>
       </c>
       <c r="F178">
-        <v>193.71</v>
+        <v>342.08</v>
       </c>
       <c r="G178">
-        <v>3.2284999999999999</v>
+        <v>5.7013333333333298</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
@@ -7540,7 +7538,7 @@
         <v>406</v>
       </c>
       <c r="B179" t="s">
-        <v>761</v>
+        <v>407</v>
       </c>
       <c r="C179" s="3">
         <v>46327</v>
@@ -7549,35 +7547,44 @@
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>762</v>
+        <v>408</v>
       </c>
       <c r="F179">
-        <v>221.25</v>
+        <v>221.21</v>
       </c>
       <c r="G179">
-        <v>3.6875</v>
+        <v>3.6868333333333299</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>846</v>
+        <v>406</v>
       </c>
       <c r="B180" t="s">
-        <v>847</v>
+        <v>671</v>
       </c>
       <c r="C180" s="3">
         <v>46327</v>
       </c>
       <c r="D180" t="s">
-        <v>831</v>
+        <v>9</v>
+      </c>
+      <c r="E180" t="s">
+        <v>672</v>
+      </c>
+      <c r="F180">
+        <v>193.71</v>
+      </c>
+      <c r="G180">
+        <v>3.2284999999999999</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>172</v>
+        <v>406</v>
       </c>
       <c r="B181" t="s">
-        <v>173</v>
+        <v>761</v>
       </c>
       <c r="C181" s="3">
         <v>46327</v>
@@ -7586,36 +7593,27 @@
         <v>9</v>
       </c>
       <c r="E181" t="s">
-        <v>174</v>
+        <v>762</v>
       </c>
       <c r="F181">
-        <v>211.32999999999899</v>
+        <v>221.25</v>
       </c>
       <c r="G181">
-        <v>3.52216666666666</v>
+        <v>3.6875</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>172</v>
+        <v>846</v>
       </c>
       <c r="B182" t="s">
-        <v>305</v>
+        <v>847</v>
       </c>
       <c r="C182" s="3">
         <v>46327</v>
       </c>
       <c r="D182" t="s">
-        <v>9</v>
-      </c>
-      <c r="E182" t="s">
-        <v>306</v>
-      </c>
-      <c r="F182">
-        <v>583.66999999999996</v>
-      </c>
-      <c r="G182">
-        <v>9.7278333333333293</v>
+        <v>831</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
@@ -7623,7 +7621,7 @@
         <v>172</v>
       </c>
       <c r="B183" t="s">
-        <v>439</v>
+        <v>173</v>
       </c>
       <c r="C183" s="3">
         <v>46327</v>
@@ -7632,13 +7630,13 @@
         <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>440</v>
+        <v>174</v>
       </c>
       <c r="F183">
-        <v>377.88</v>
+        <v>211.32999999999899</v>
       </c>
       <c r="G183">
-        <v>6.298</v>
+        <v>3.52216666666666</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
@@ -7646,7 +7644,7 @@
         <v>172</v>
       </c>
       <c r="B184" t="s">
-        <v>544</v>
+        <v>305</v>
       </c>
       <c r="C184" s="3">
         <v>46327</v>
@@ -7655,13 +7653,13 @@
         <v>9</v>
       </c>
       <c r="E184" t="s">
-        <v>545</v>
+        <v>306</v>
       </c>
       <c r="F184">
-        <v>257.92</v>
+        <v>583.66999999999996</v>
       </c>
       <c r="G184">
-        <v>4.2986666666666604</v>
+        <v>9.7278333333333293</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
@@ -7669,22 +7667,22 @@
         <v>172</v>
       </c>
       <c r="B185" t="s">
-        <v>658</v>
+        <v>439</v>
       </c>
       <c r="C185" s="3">
         <v>46327</v>
       </c>
       <c r="D185" t="s">
-        <v>831</v>
+        <v>9</v>
       </c>
       <c r="E185" t="s">
-        <v>659</v>
+        <v>440</v>
       </c>
       <c r="F185">
-        <v>267.42</v>
+        <v>377.88</v>
       </c>
       <c r="G185">
-        <v>4.4569999999999999</v>
+        <v>6.298</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
@@ -7692,7 +7690,7 @@
         <v>172</v>
       </c>
       <c r="B186" t="s">
-        <v>669</v>
+        <v>544</v>
       </c>
       <c r="C186" s="3">
         <v>46327</v>
@@ -7701,44 +7699,44 @@
         <v>9</v>
       </c>
       <c r="E186" t="s">
-        <v>670</v>
+        <v>545</v>
       </c>
       <c r="F186">
-        <v>173.17</v>
+        <v>257.92</v>
       </c>
       <c r="G186">
-        <v>2.8861666666666599</v>
+        <v>4.2986666666666604</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>552</v>
+        <v>172</v>
       </c>
       <c r="B187" t="s">
-        <v>595</v>
+        <v>658</v>
       </c>
       <c r="C187" s="3">
         <v>46327</v>
       </c>
       <c r="D187" t="s">
-        <v>9</v>
+        <v>831</v>
       </c>
       <c r="E187" t="s">
-        <v>596</v>
+        <v>659</v>
       </c>
       <c r="F187">
-        <v>263.33</v>
+        <v>267.42</v>
       </c>
       <c r="G187">
-        <v>4.3888333333333298</v>
+        <v>4.4569999999999999</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>552</v>
+        <v>172</v>
       </c>
       <c r="B188" t="s">
-        <v>694</v>
+        <v>669</v>
       </c>
       <c r="C188" s="3">
         <v>46327</v>
@@ -7747,21 +7745,21 @@
         <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="F188">
-        <v>277.75</v>
+        <v>173.17</v>
       </c>
       <c r="G188">
-        <v>4.6291666666666602</v>
+        <v>2.8861666666666599</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>97</v>
+        <v>552</v>
       </c>
       <c r="B189" t="s">
-        <v>98</v>
+        <v>595</v>
       </c>
       <c r="C189" s="3">
         <v>46327</v>
@@ -7770,21 +7768,21 @@
         <v>9</v>
       </c>
       <c r="E189" t="s">
-        <v>99</v>
+        <v>596</v>
       </c>
       <c r="F189">
-        <v>348.75</v>
+        <v>263.33</v>
       </c>
       <c r="G189">
-        <v>5.8125</v>
+        <v>4.3888333333333298</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>97</v>
+        <v>552</v>
       </c>
       <c r="B190" t="s">
-        <v>130</v>
+        <v>694</v>
       </c>
       <c r="C190" s="3">
         <v>46327</v>
@@ -7793,13 +7791,13 @@
         <v>9</v>
       </c>
       <c r="E190" t="s">
-        <v>131</v>
+        <v>695</v>
       </c>
       <c r="F190">
-        <v>237.63</v>
+        <v>277.75</v>
       </c>
       <c r="G190">
-        <v>3.9605000000000001</v>
+        <v>4.6291666666666602</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
@@ -7807,7 +7805,7 @@
         <v>97</v>
       </c>
       <c r="B191" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="C191" s="3">
         <v>46327</v>
@@ -7816,13 +7814,13 @@
         <v>9</v>
       </c>
       <c r="E191" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="F191">
-        <v>254.25</v>
+        <v>348.75</v>
       </c>
       <c r="G191">
-        <v>4.2374999999999998</v>
+        <v>5.8125</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
@@ -7830,7 +7828,7 @@
         <v>97</v>
       </c>
       <c r="B192" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C192" s="3">
         <v>46327</v>
@@ -7839,13 +7837,13 @@
         <v>9</v>
       </c>
       <c r="E192" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="F192">
-        <v>214.54</v>
+        <v>237.63</v>
       </c>
       <c r="G192">
-        <v>3.5756666666666601</v>
+        <v>3.9605000000000001</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
@@ -7853,7 +7851,7 @@
         <v>97</v>
       </c>
       <c r="B193" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="C193" s="3">
         <v>46327</v>
@@ -7862,13 +7860,13 @@
         <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="F193">
-        <v>346.75</v>
+        <v>254.25</v>
       </c>
       <c r="G193">
-        <v>5.7791666666666597</v>
+        <v>4.2374999999999998</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
@@ -7876,7 +7874,7 @@
         <v>97</v>
       </c>
       <c r="B194" t="s">
-        <v>266</v>
+        <v>170</v>
       </c>
       <c r="C194" s="3">
         <v>46327</v>
@@ -7885,13 +7883,13 @@
         <v>9</v>
       </c>
       <c r="E194" t="s">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="F194">
-        <v>192.88</v>
+        <v>214.54</v>
       </c>
       <c r="G194">
-        <v>3.2146666666666599</v>
+        <v>3.5756666666666601</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
@@ -7899,7 +7897,7 @@
         <v>97</v>
       </c>
       <c r="B195" t="s">
-        <v>494</v>
+        <v>194</v>
       </c>
       <c r="C195" s="3">
         <v>46327</v>
@@ -7908,13 +7906,13 @@
         <v>9</v>
       </c>
       <c r="E195" t="s">
-        <v>495</v>
+        <v>195</v>
       </c>
       <c r="F195">
-        <v>292.58</v>
+        <v>346.75</v>
       </c>
       <c r="G195">
-        <v>4.8763333333333296</v>
+        <v>5.7791666666666597</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
@@ -7922,7 +7920,7 @@
         <v>97</v>
       </c>
       <c r="B196" t="s">
-        <v>579</v>
+        <v>266</v>
       </c>
       <c r="C196" s="3">
         <v>46327</v>
@@ -7931,13 +7929,13 @@
         <v>9</v>
       </c>
       <c r="E196" t="s">
-        <v>580</v>
+        <v>267</v>
       </c>
       <c r="F196">
-        <v>282.20999999999998</v>
+        <v>192.88</v>
       </c>
       <c r="G196">
-        <v>4.7035</v>
+        <v>3.2146666666666599</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
@@ -7945,7 +7943,7 @@
         <v>97</v>
       </c>
       <c r="B197" t="s">
-        <v>586</v>
+        <v>494</v>
       </c>
       <c r="C197" s="3">
         <v>46327</v>
@@ -7954,13 +7952,13 @@
         <v>9</v>
       </c>
       <c r="E197" t="s">
-        <v>587</v>
+        <v>495</v>
       </c>
       <c r="F197">
-        <v>281.88</v>
+        <v>292.58</v>
       </c>
       <c r="G197">
-        <v>4.6979999999999897</v>
+        <v>4.8763333333333296</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
@@ -7968,7 +7966,7 @@
         <v>97</v>
       </c>
       <c r="B198" t="s">
-        <v>618</v>
+        <v>579</v>
       </c>
       <c r="C198" s="3">
         <v>46327</v>
@@ -7977,13 +7975,13 @@
         <v>9</v>
       </c>
       <c r="E198" t="s">
-        <v>619</v>
+        <v>580</v>
       </c>
       <c r="F198">
-        <v>246.63</v>
+        <v>282.20999999999998</v>
       </c>
       <c r="G198">
-        <v>4.1105</v>
+        <v>4.7035</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
@@ -7991,7 +7989,7 @@
         <v>97</v>
       </c>
       <c r="B199" t="s">
-        <v>711</v>
+        <v>586</v>
       </c>
       <c r="C199" s="3">
         <v>46327</v>
@@ -8000,13 +7998,13 @@
         <v>9</v>
       </c>
       <c r="E199" t="s">
-        <v>712</v>
+        <v>587</v>
       </c>
       <c r="F199">
-        <v>406.63</v>
+        <v>281.88</v>
       </c>
       <c r="G199">
-        <v>6.7771666666666599</v>
+        <v>4.6979999999999897</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
@@ -8014,7 +8012,7 @@
         <v>97</v>
       </c>
       <c r="B200" t="s">
-        <v>820</v>
+        <v>618</v>
       </c>
       <c r="C200" s="3">
         <v>46327</v>
@@ -8023,21 +8021,21 @@
         <v>9</v>
       </c>
       <c r="E200" t="s">
-        <v>821</v>
+        <v>619</v>
       </c>
       <c r="F200">
-        <v>228.42</v>
+        <v>246.63</v>
       </c>
       <c r="G200">
-        <v>3.8069999999999999</v>
+        <v>4.1105</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="B201" t="s">
-        <v>308</v>
+        <v>711</v>
       </c>
       <c r="C201" s="3">
         <v>46327</v>
@@ -8046,21 +8044,21 @@
         <v>9</v>
       </c>
       <c r="E201" t="s">
-        <v>309</v>
+        <v>712</v>
       </c>
       <c r="F201">
-        <v>134</v>
+        <v>406.63</v>
       </c>
       <c r="G201">
-        <v>2.2333333333333298</v>
+        <v>6.7771666666666599</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="B202" t="s">
-        <v>378</v>
+        <v>820</v>
       </c>
       <c r="C202" s="3">
         <v>46327</v>
@@ -8069,13 +8067,13 @@
         <v>9</v>
       </c>
       <c r="E202" t="s">
-        <v>379</v>
+        <v>821</v>
       </c>
       <c r="F202">
-        <v>152.29</v>
+        <v>228.42</v>
       </c>
       <c r="G202">
-        <v>2.53816666666666</v>
+        <v>3.8069999999999999</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
@@ -8083,7 +8081,7 @@
         <v>307</v>
       </c>
       <c r="B203" t="s">
-        <v>649</v>
+        <v>308</v>
       </c>
       <c r="C203" s="3">
         <v>46327</v>
@@ -8092,21 +8090,21 @@
         <v>9</v>
       </c>
       <c r="E203" t="s">
-        <v>650</v>
+        <v>309</v>
       </c>
       <c r="F203">
-        <v>273.20999999999998</v>
+        <v>134</v>
       </c>
       <c r="G203">
-        <v>4.5534999999999997</v>
+        <v>2.2333333333333298</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>418</v>
+        <v>307</v>
       </c>
       <c r="B204" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="C204" s="3">
         <v>46327</v>
@@ -8115,21 +8113,21 @@
         <v>9</v>
       </c>
       <c r="E204" t="s">
-        <v>420</v>
+        <v>379</v>
       </c>
       <c r="F204">
-        <v>320.45999999999998</v>
+        <v>152.29</v>
       </c>
       <c r="G204">
-        <v>5.3409999999999904</v>
+        <v>2.53816666666666</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>418</v>
+        <v>307</v>
       </c>
       <c r="B205" t="s">
-        <v>465</v>
+        <v>649</v>
       </c>
       <c r="C205" s="3">
         <v>46327</v>
@@ -8138,21 +8136,21 @@
         <v>9</v>
       </c>
       <c r="E205" t="s">
-        <v>466</v>
+        <v>650</v>
       </c>
       <c r="F205">
-        <v>257.95999999999998</v>
+        <v>273.20999999999998</v>
       </c>
       <c r="G205">
-        <v>4.2993333333333297</v>
+        <v>4.5534999999999997</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>624</v>
+        <v>418</v>
       </c>
       <c r="B206" t="s">
-        <v>625</v>
+        <v>419</v>
       </c>
       <c r="C206" s="3">
         <v>46327</v>
@@ -8161,21 +8159,21 @@
         <v>9</v>
       </c>
       <c r="E206" t="s">
-        <v>626</v>
+        <v>420</v>
       </c>
       <c r="F206">
-        <v>488.75</v>
+        <v>320.45999999999998</v>
       </c>
       <c r="G206">
-        <v>8.1458333333333304</v>
+        <v>5.3409999999999904</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>530</v>
+        <v>418</v>
       </c>
       <c r="B207" t="s">
-        <v>531</v>
+        <v>465</v>
       </c>
       <c r="C207" s="3">
         <v>46327</v>
@@ -8184,21 +8182,21 @@
         <v>9</v>
       </c>
       <c r="E207" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="F207">
-        <v>216.71</v>
+        <v>257.95999999999998</v>
       </c>
       <c r="G207">
-        <v>3.6118333333333301</v>
+        <v>4.2993333333333297</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>510</v>
+        <v>624</v>
       </c>
       <c r="B208" t="s">
-        <v>511</v>
+        <v>625</v>
       </c>
       <c r="C208" s="3">
         <v>46327</v>
@@ -8207,21 +8205,21 @@
         <v>9</v>
       </c>
       <c r="E208" t="s">
-        <v>512</v>
+        <v>626</v>
       </c>
       <c r="F208">
-        <v>384.58</v>
+        <v>488.75</v>
       </c>
       <c r="G208">
-        <v>6.4096666666666602</v>
+        <v>8.1458333333333304</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="B209" t="s">
-        <v>667</v>
+        <v>531</v>
       </c>
       <c r="C209" s="3">
         <v>46327</v>
@@ -8230,13 +8228,13 @@
         <v>9</v>
       </c>
       <c r="E209" t="s">
-        <v>668</v>
+        <v>532</v>
       </c>
       <c r="F209">
-        <v>271.83</v>
+        <v>216.71</v>
       </c>
       <c r="G209">
-        <v>4.5305</v>
+        <v>3.6118333333333301</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
@@ -8244,7 +8242,7 @@
         <v>510</v>
       </c>
       <c r="B210" t="s">
-        <v>792</v>
+        <v>511</v>
       </c>
       <c r="C210" s="3">
         <v>46327</v>
@@ -8253,21 +8251,21 @@
         <v>9</v>
       </c>
       <c r="E210" t="s">
-        <v>793</v>
+        <v>512</v>
       </c>
       <c r="F210">
-        <v>371.04</v>
+        <v>384.58</v>
       </c>
       <c r="G210">
-        <v>6.1840000000000002</v>
+        <v>6.4096666666666602</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>348</v>
+        <v>510</v>
       </c>
       <c r="B211" t="s">
-        <v>349</v>
+        <v>667</v>
       </c>
       <c r="C211" s="3">
         <v>46327</v>
@@ -8276,21 +8274,21 @@
         <v>9</v>
       </c>
       <c r="E211" t="s">
-        <v>350</v>
+        <v>668</v>
       </c>
       <c r="F211">
-        <v>490.29</v>
+        <v>271.83</v>
       </c>
       <c r="G211">
-        <v>8.1715</v>
+        <v>4.5305</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>653</v>
+        <v>510</v>
       </c>
       <c r="B212" t="s">
-        <v>654</v>
+        <v>792</v>
       </c>
       <c r="C212" s="3">
         <v>46327</v>
@@ -8299,21 +8297,21 @@
         <v>9</v>
       </c>
       <c r="E212" t="s">
-        <v>655</v>
+        <v>793</v>
       </c>
       <c r="F212">
-        <v>214.13</v>
+        <v>371.04</v>
       </c>
       <c r="G212">
-        <v>3.56883333333333</v>
+        <v>6.1840000000000002</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>38</v>
+        <v>348</v>
       </c>
       <c r="B213" t="s">
-        <v>39</v>
+        <v>349</v>
       </c>
       <c r="C213" s="3">
         <v>46327</v>
@@ -8322,21 +8320,21 @@
         <v>9</v>
       </c>
       <c r="E213" t="s">
-        <v>40</v>
+        <v>350</v>
       </c>
       <c r="F213">
-        <v>138.16999999999999</v>
+        <v>490.29</v>
       </c>
       <c r="G213">
-        <v>2.30283333333333</v>
+        <v>8.1715</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>470</v>
+        <v>653</v>
       </c>
       <c r="B214" t="s">
-        <v>471</v>
+        <v>654</v>
       </c>
       <c r="C214" s="3">
         <v>46327</v>
@@ -8345,21 +8343,21 @@
         <v>9</v>
       </c>
       <c r="E214" t="s">
-        <v>472</v>
+        <v>655</v>
       </c>
       <c r="F214">
-        <v>255.63</v>
+        <v>214.13</v>
       </c>
       <c r="G214">
-        <v>4.2604999999999897</v>
+        <v>3.56883333333333</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>202</v>
+        <v>38</v>
       </c>
       <c r="B215" t="s">
-        <v>200</v>
+        <v>39</v>
       </c>
       <c r="C215" s="3">
         <v>46327</v>
@@ -8368,21 +8366,21 @@
         <v>9</v>
       </c>
       <c r="E215" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="F215">
-        <v>254.83</v>
+        <v>138.16999999999999</v>
       </c>
       <c r="G215">
-        <v>4.2471666666666597</v>
+        <v>2.30283333333333</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>202</v>
+        <v>470</v>
       </c>
       <c r="B216" t="s">
-        <v>264</v>
+        <v>471</v>
       </c>
       <c r="C216" s="3">
         <v>46327</v>
@@ -8391,13 +8389,13 @@
         <v>9</v>
       </c>
       <c r="E216" t="s">
-        <v>265</v>
+        <v>472</v>
       </c>
       <c r="F216">
-        <v>223.88</v>
+        <v>255.63</v>
       </c>
       <c r="G216">
-        <v>3.7313333333333301</v>
+        <v>4.2604999999999897</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
@@ -8405,7 +8403,7 @@
         <v>202</v>
       </c>
       <c r="B217" t="s">
-        <v>396</v>
+        <v>200</v>
       </c>
       <c r="C217" s="3">
         <v>46327</v>
@@ -8414,21 +8412,21 @@
         <v>9</v>
       </c>
       <c r="E217" t="s">
-        <v>397</v>
+        <v>203</v>
       </c>
       <c r="F217">
-        <v>197.46</v>
+        <v>254.83</v>
       </c>
       <c r="G217">
-        <v>3.2909999999999999</v>
+        <v>4.2471666666666597</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>339</v>
-      </c>
-      <c r="B218" s="4" t="s">
-        <v>340</v>
+        <v>202</v>
+      </c>
+      <c r="B218" t="s">
+        <v>264</v>
       </c>
       <c r="C218" s="3">
         <v>46327</v>
@@ -8437,21 +8435,21 @@
         <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>341</v>
+        <v>265</v>
       </c>
       <c r="F218">
-        <v>290.17</v>
+        <v>223.88</v>
       </c>
       <c r="G218">
-        <v>4.8361666666666601</v>
+        <v>3.7313333333333301</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>339</v>
+        <v>202</v>
       </c>
       <c r="B219" t="s">
-        <v>732</v>
+        <v>396</v>
       </c>
       <c r="C219" s="3">
         <v>46327</v>
@@ -8460,21 +8458,21 @@
         <v>9</v>
       </c>
       <c r="E219" t="s">
-        <v>733</v>
+        <v>397</v>
       </c>
       <c r="F219">
-        <v>284.92</v>
+        <v>197.46</v>
       </c>
       <c r="G219">
-        <v>4.7486666666666597</v>
+        <v>3.2909999999999999</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>480</v>
-      </c>
-      <c r="B220" t="s">
-        <v>481</v>
+        <v>339</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>340</v>
       </c>
       <c r="C220" s="3">
         <v>46327</v>
@@ -8483,21 +8481,21 @@
         <v>9</v>
       </c>
       <c r="E220" t="s">
-        <v>482</v>
+        <v>341</v>
       </c>
       <c r="F220">
-        <v>256.08</v>
+        <v>290.17</v>
       </c>
       <c r="G220">
-        <v>4.2679999999999998</v>
+        <v>4.8361666666666601</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>143</v>
+        <v>339</v>
       </c>
       <c r="B221" t="s">
-        <v>144</v>
+        <v>732</v>
       </c>
       <c r="C221" s="3">
         <v>46327</v>
@@ -8506,21 +8504,21 @@
         <v>9</v>
       </c>
       <c r="E221" t="s">
-        <v>145</v>
+        <v>733</v>
       </c>
       <c r="F221">
-        <v>234.17</v>
+        <v>284.92</v>
       </c>
       <c r="G221">
-        <v>3.90283333333333</v>
+        <v>4.7486666666666597</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B222" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C222" s="3">
         <v>46327</v>
@@ -8529,21 +8527,21 @@
         <v>9</v>
       </c>
       <c r="E222" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F222">
-        <v>432.08</v>
+        <v>256.08</v>
       </c>
       <c r="G222">
-        <v>7.2013333333333298</v>
+        <v>4.2679999999999998</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B223" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C223" s="3">
         <v>46327</v>
@@ -8552,21 +8550,21 @@
         <v>9</v>
       </c>
       <c r="E223" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F223">
-        <v>300.79000000000002</v>
+        <v>234.17</v>
       </c>
       <c r="G223">
-        <v>5.0131666666666597</v>
+        <v>3.90283333333333</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>827</v>
+        <v>477</v>
       </c>
       <c r="B224" t="s">
-        <v>828</v>
+        <v>478</v>
       </c>
       <c r="C224" s="3">
         <v>46327</v>
@@ -8575,21 +8573,21 @@
         <v>9</v>
       </c>
       <c r="E224" t="s">
-        <v>829</v>
+        <v>479</v>
       </c>
       <c r="F224">
-        <v>350.33</v>
+        <v>432.08</v>
       </c>
       <c r="G224">
-        <v>5.83883333333333</v>
+        <v>7.2013333333333298</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>770</v>
+        <v>134</v>
       </c>
       <c r="B225" t="s">
-        <v>771</v>
+        <v>135</v>
       </c>
       <c r="C225" s="3">
         <v>46327</v>
@@ -8598,21 +8596,21 @@
         <v>9</v>
       </c>
       <c r="E225" t="s">
-        <v>772</v>
+        <v>136</v>
       </c>
       <c r="F225">
-        <v>184.58</v>
+        <v>300.79000000000002</v>
       </c>
       <c r="G225">
-        <v>3.0763333333333298</v>
+        <v>5.0131666666666597</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>369</v>
+        <v>827</v>
       </c>
       <c r="B226" t="s">
-        <v>370</v>
+        <v>828</v>
       </c>
       <c r="C226" s="3">
         <v>46327</v>
@@ -8621,21 +8619,21 @@
         <v>9</v>
       </c>
       <c r="E226" t="s">
-        <v>371</v>
+        <v>829</v>
       </c>
       <c r="F226">
-        <v>215.67</v>
+        <v>350.33</v>
       </c>
       <c r="G226">
-        <v>3.5945</v>
+        <v>5.83883333333333</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>611</v>
+        <v>770</v>
       </c>
       <c r="B227" t="s">
-        <v>612</v>
+        <v>771</v>
       </c>
       <c r="C227" s="3">
         <v>46327</v>
@@ -8644,35 +8642,44 @@
         <v>9</v>
       </c>
       <c r="E227" t="s">
-        <v>613</v>
+        <v>772</v>
       </c>
       <c r="F227">
-        <v>243.96</v>
+        <v>184.58</v>
       </c>
       <c r="G227">
-        <v>4.0659999999999998</v>
+        <v>3.0763333333333298</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>852</v>
+        <v>369</v>
       </c>
       <c r="B228" t="s">
-        <v>853</v>
+        <v>370</v>
       </c>
       <c r="C228" s="3">
         <v>46327</v>
       </c>
       <c r="D228" t="s">
         <v>9</v>
+      </c>
+      <c r="E228" t="s">
+        <v>371</v>
+      </c>
+      <c r="F228">
+        <v>215.67</v>
+      </c>
+      <c r="G228">
+        <v>3.5945</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>502</v>
+        <v>611</v>
       </c>
       <c r="B229" t="s">
-        <v>503</v>
+        <v>612</v>
       </c>
       <c r="C229" s="3">
         <v>46327</v>
@@ -8681,36 +8688,27 @@
         <v>9</v>
       </c>
       <c r="E229" t="s">
-        <v>504</v>
+        <v>613</v>
       </c>
       <c r="F229">
-        <v>556.91999999999996</v>
+        <v>243.96</v>
       </c>
       <c r="G229">
-        <v>9.282</v>
+        <v>4.0659999999999998</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>502</v>
+        <v>852</v>
       </c>
       <c r="B230" t="s">
-        <v>651</v>
+        <v>853</v>
       </c>
       <c r="C230" s="3">
         <v>46327</v>
       </c>
       <c r="D230" t="s">
         <v>9</v>
-      </c>
-      <c r="E230" t="s">
-        <v>652</v>
-      </c>
-      <c r="F230">
-        <v>356.46</v>
-      </c>
-      <c r="G230">
-        <v>5.9409999999999998</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -8718,7 +8716,7 @@
         <v>502</v>
       </c>
       <c r="B231" t="s">
-        <v>744</v>
+        <v>503</v>
       </c>
       <c r="C231" s="3">
         <v>46327</v>
@@ -8727,21 +8725,21 @@
         <v>9</v>
       </c>
       <c r="E231" t="s">
-        <v>745</v>
+        <v>504</v>
       </c>
       <c r="F231">
-        <v>279.17</v>
+        <v>556.91999999999996</v>
       </c>
       <c r="G231">
-        <v>4.65283333333333</v>
+        <v>9.282</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>375</v>
+        <v>502</v>
       </c>
       <c r="B232" t="s">
-        <v>376</v>
+        <v>651</v>
       </c>
       <c r="C232" s="3">
         <v>46327</v>
@@ -8750,21 +8748,21 @@
         <v>9</v>
       </c>
       <c r="E232" t="s">
-        <v>377</v>
+        <v>652</v>
       </c>
       <c r="F232">
-        <v>180.67</v>
+        <v>356.46</v>
       </c>
       <c r="G232">
-        <v>3.0111666666666599</v>
+        <v>5.9409999999999998</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>375</v>
+        <v>502</v>
       </c>
       <c r="B233" t="s">
-        <v>815</v>
+        <v>744</v>
       </c>
       <c r="C233" s="3">
         <v>46327</v>
@@ -8773,44 +8771,44 @@
         <v>9</v>
       </c>
       <c r="E233" t="s">
-        <v>816</v>
+        <v>745</v>
       </c>
       <c r="F233">
-        <v>162.82999999999899</v>
+        <v>279.17</v>
       </c>
       <c r="G233">
-        <v>2.71383333333333</v>
+        <v>4.65283333333333</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>660</v>
+        <v>375</v>
       </c>
       <c r="B234" t="s">
-        <v>661</v>
+        <v>376</v>
       </c>
       <c r="C234" s="3">
         <v>46327</v>
       </c>
       <c r="D234" t="s">
-        <v>831</v>
+        <v>9</v>
       </c>
       <c r="E234" t="s">
-        <v>662</v>
+        <v>377</v>
       </c>
       <c r="F234">
-        <v>256.5</v>
+        <v>180.67</v>
       </c>
       <c r="G234">
-        <v>4.2750000000000004</v>
+        <v>3.0111666666666599</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>94</v>
+        <v>375</v>
       </c>
       <c r="B235" t="s">
-        <v>700</v>
+        <v>815</v>
       </c>
       <c r="C235" s="3">
         <v>46327</v>
@@ -8819,44 +8817,44 @@
         <v>9</v>
       </c>
       <c r="E235" t="s">
-        <v>701</v>
+        <v>816</v>
       </c>
       <c r="F235">
-        <v>204.07999999999899</v>
+        <v>162.82999999999899</v>
       </c>
       <c r="G235">
-        <v>3.40133333333333</v>
+        <v>2.71383333333333</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>548</v>
+        <v>660</v>
       </c>
       <c r="B236" t="s">
-        <v>549</v>
+        <v>661</v>
       </c>
       <c r="C236" s="3">
         <v>46327</v>
       </c>
       <c r="D236" t="s">
-        <v>9</v>
+        <v>831</v>
       </c>
       <c r="E236" t="s">
-        <v>550</v>
+        <v>662</v>
       </c>
       <c r="F236">
-        <v>158.63</v>
+        <v>256.5</v>
       </c>
       <c r="G236">
-        <v>2.6438333333333301</v>
+        <v>4.2750000000000004</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>780</v>
+        <v>94</v>
       </c>
       <c r="B237" t="s">
-        <v>781</v>
+        <v>700</v>
       </c>
       <c r="C237" s="3">
         <v>46327</v>
@@ -8865,44 +8863,44 @@
         <v>9</v>
       </c>
       <c r="E237" t="s">
-        <v>782</v>
+        <v>701</v>
       </c>
       <c r="F237">
-        <v>212.96</v>
+        <v>204.07999999999899</v>
       </c>
       <c r="G237">
-        <v>3.5493333333333301</v>
+        <v>3.40133333333333</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>486</v>
+        <v>548</v>
       </c>
       <c r="B238" t="s">
-        <v>487</v>
+        <v>549</v>
       </c>
       <c r="C238" s="3">
         <v>46327</v>
       </c>
       <c r="D238" t="s">
-        <v>831</v>
+        <v>9</v>
       </c>
       <c r="E238" t="s">
-        <v>488</v>
+        <v>550</v>
       </c>
       <c r="F238">
-        <v>231.07999999999899</v>
+        <v>158.63</v>
       </c>
       <c r="G238">
-        <v>3.8513333333333302</v>
+        <v>2.6438333333333301</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>677</v>
+        <v>780</v>
       </c>
       <c r="B239" t="s">
-        <v>678</v>
+        <v>781</v>
       </c>
       <c r="C239" s="3">
         <v>46327</v>
@@ -8911,44 +8909,44 @@
         <v>9</v>
       </c>
       <c r="E239" t="s">
-        <v>679</v>
+        <v>782</v>
       </c>
       <c r="F239">
-        <v>561.25</v>
+        <v>212.96</v>
       </c>
       <c r="G239">
-        <v>9.3541666666666607</v>
+        <v>3.5493333333333301</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>810</v>
+        <v>486</v>
       </c>
       <c r="B240" t="s">
-        <v>811</v>
+        <v>487</v>
       </c>
       <c r="C240" s="3">
         <v>46327</v>
       </c>
       <c r="D240" t="s">
-        <v>9</v>
+        <v>831</v>
       </c>
       <c r="E240" t="s">
-        <v>812</v>
+        <v>488</v>
       </c>
       <c r="F240">
-        <v>202.25</v>
+        <v>231.07999999999899</v>
       </c>
       <c r="G240">
-        <v>3.37083333333333</v>
+        <v>3.8513333333333302</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>242</v>
+        <v>677</v>
       </c>
       <c r="B241" t="s">
-        <v>243</v>
+        <v>678</v>
       </c>
       <c r="C241" s="3">
         <v>46327</v>
@@ -8957,21 +8955,21 @@
         <v>9</v>
       </c>
       <c r="E241" t="s">
-        <v>244</v>
+        <v>679</v>
       </c>
       <c r="F241">
-        <v>204.63</v>
+        <v>561.25</v>
       </c>
       <c r="G241">
-        <v>3.4104999999999999</v>
+        <v>9.3541666666666607</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>242</v>
+        <v>810</v>
       </c>
       <c r="B242" t="s">
-        <v>278</v>
+        <v>811</v>
       </c>
       <c r="C242" s="3">
         <v>46327</v>
@@ -8980,21 +8978,21 @@
         <v>9</v>
       </c>
       <c r="E242" t="s">
-        <v>279</v>
+        <v>812</v>
       </c>
       <c r="F242">
-        <v>196.25</v>
+        <v>202.25</v>
       </c>
       <c r="G242">
-        <v>3.2708333333333299</v>
+        <v>3.37083333333333</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>452</v>
+        <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>453</v>
+        <v>243</v>
       </c>
       <c r="C243" s="3">
         <v>46327</v>
@@ -9003,35 +9001,44 @@
         <v>9</v>
       </c>
       <c r="E243" t="s">
-        <v>454</v>
+        <v>244</v>
       </c>
       <c r="F243">
-        <v>270.63</v>
+        <v>204.63</v>
       </c>
       <c r="G243">
-        <v>4.5104999999999897</v>
+        <v>3.4104999999999999</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>848</v>
+        <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>849</v>
+        <v>278</v>
       </c>
       <c r="C244" s="3">
         <v>46327</v>
       </c>
       <c r="D244" t="s">
-        <v>831</v>
+        <v>9</v>
+      </c>
+      <c r="E244" t="s">
+        <v>279</v>
+      </c>
+      <c r="F244">
+        <v>196.25</v>
+      </c>
+      <c r="G244">
+        <v>3.2708333333333299</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>268</v>
+        <v>452</v>
       </c>
       <c r="B245" t="s">
-        <v>269</v>
+        <v>453</v>
       </c>
       <c r="C245" s="3">
         <v>46327</v>
@@ -9040,44 +9047,35 @@
         <v>9</v>
       </c>
       <c r="E245" t="s">
-        <v>270</v>
+        <v>454</v>
       </c>
       <c r="F245">
-        <v>321.42</v>
+        <v>270.63</v>
       </c>
       <c r="G245">
-        <v>5.3570000000000002</v>
+        <v>4.5104999999999897</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>268</v>
+        <v>848</v>
       </c>
       <c r="B246" t="s">
-        <v>276</v>
+        <v>849</v>
       </c>
       <c r="C246" s="3">
         <v>46327</v>
       </c>
       <c r="D246" t="s">
-        <v>9</v>
-      </c>
-      <c r="E246" t="s">
-        <v>277</v>
-      </c>
-      <c r="F246">
-        <v>393.79</v>
-      </c>
-      <c r="G246">
-        <v>6.5631666666666604</v>
+        <v>831</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>32</v>
+        <v>268</v>
       </c>
       <c r="B247" t="s">
-        <v>33</v>
+        <v>269</v>
       </c>
       <c r="C247" s="3">
         <v>46327</v>
@@ -9086,21 +9084,21 @@
         <v>9</v>
       </c>
       <c r="E247" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="F247">
-        <v>241.29</v>
+        <v>321.42</v>
       </c>
       <c r="G247">
-        <v>4.0214999999999996</v>
+        <v>5.3570000000000002</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>32</v>
+        <v>268</v>
       </c>
       <c r="B248" t="s">
-        <v>413</v>
+        <v>276</v>
       </c>
       <c r="C248" s="3">
         <v>46327</v>
@@ -9109,13 +9107,13 @@
         <v>9</v>
       </c>
       <c r="E248" t="s">
-        <v>414</v>
+        <v>277</v>
       </c>
       <c r="F248">
-        <v>146.54</v>
+        <v>393.79</v>
       </c>
       <c r="G248">
-        <v>2.4423333333333299</v>
+        <v>6.5631666666666604</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -9123,7 +9121,7 @@
         <v>32</v>
       </c>
       <c r="B249" t="s">
-        <v>561</v>
+        <v>33</v>
       </c>
       <c r="C249" s="3">
         <v>46327</v>
@@ -9132,21 +9130,21 @@
         <v>9</v>
       </c>
       <c r="E249" t="s">
-        <v>562</v>
+        <v>34</v>
       </c>
       <c r="F249">
-        <v>172.46</v>
+        <v>241.29</v>
       </c>
       <c r="G249">
-        <v>2.8743333333333299</v>
+        <v>4.0214999999999996</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="B250" t="s">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="C250" s="3">
         <v>46327</v>
@@ -9155,21 +9153,21 @@
         <v>9</v>
       </c>
       <c r="E250" t="s">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="F250">
-        <v>167.46</v>
+        <v>146.54</v>
       </c>
       <c r="G250">
-        <v>2.7909999999999999</v>
+        <v>2.4423333333333299</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="B251" t="s">
-        <v>327</v>
+        <v>561</v>
       </c>
       <c r="C251" s="3">
         <v>46327</v>
@@ -9178,13 +9176,13 @@
         <v>9</v>
       </c>
       <c r="E251" t="s">
-        <v>328</v>
+        <v>562</v>
       </c>
       <c r="F251">
-        <v>257.45999999999998</v>
+        <v>172.46</v>
       </c>
       <c r="G251">
-        <v>4.2909999999999897</v>
+        <v>2.8743333333333299</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -9192,7 +9190,7 @@
         <v>76</v>
       </c>
       <c r="B252" t="s">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="C252" s="3">
         <v>46327</v>
@@ -9201,21 +9199,21 @@
         <v>9</v>
       </c>
       <c r="E252" t="s">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="F252">
-        <v>179.21</v>
+        <v>167.46</v>
       </c>
       <c r="G252">
-        <v>2.9868333333333301</v>
+        <v>2.7909999999999999</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>785</v>
+        <v>76</v>
       </c>
       <c r="B253" t="s">
-        <v>786</v>
+        <v>327</v>
       </c>
       <c r="C253" s="3">
         <v>46327</v>
@@ -9224,21 +9222,21 @@
         <v>9</v>
       </c>
       <c r="E253" t="s">
-        <v>787</v>
+        <v>328</v>
       </c>
       <c r="F253">
-        <v>541.5</v>
+        <v>257.45999999999998</v>
       </c>
       <c r="G253">
-        <v>9.0250000000000004</v>
+        <v>4.2909999999999897</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B254" t="s">
-        <v>42</v>
+        <v>329</v>
       </c>
       <c r="C254" s="3">
         <v>46327</v>
@@ -9247,21 +9245,21 @@
         <v>9</v>
       </c>
       <c r="E254" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="F254">
-        <v>307.29000000000002</v>
+        <v>179.21</v>
       </c>
       <c r="G254">
-        <v>5.1215000000000002</v>
+        <v>2.9868333333333301</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>361</v>
+        <v>785</v>
       </c>
       <c r="B255" t="s">
-        <v>362</v>
+        <v>786</v>
       </c>
       <c r="C255" s="3">
         <v>46327</v>
@@ -9270,21 +9268,21 @@
         <v>9</v>
       </c>
       <c r="E255" t="s">
-        <v>363</v>
+        <v>787</v>
       </c>
       <c r="F255">
-        <v>193.58</v>
+        <v>541.5</v>
       </c>
       <c r="G255">
-        <v>3.2263333333333302</v>
+        <v>9.0250000000000004</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>336</v>
+        <v>41</v>
       </c>
       <c r="B256" t="s">
-        <v>337</v>
+        <v>42</v>
       </c>
       <c r="C256" s="3">
         <v>46327</v>
@@ -9293,21 +9291,21 @@
         <v>9</v>
       </c>
       <c r="E256" t="s">
-        <v>338</v>
+        <v>43</v>
       </c>
       <c r="F256">
-        <v>132.33000000000001</v>
+        <v>307.29000000000002</v>
       </c>
       <c r="G256">
-        <v>2.2054999999999998</v>
+        <v>5.1215000000000002</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>817</v>
+        <v>361</v>
       </c>
       <c r="B257" t="s">
-        <v>818</v>
+        <v>362</v>
       </c>
       <c r="C257" s="3">
         <v>46327</v>
@@ -9316,21 +9314,21 @@
         <v>9</v>
       </c>
       <c r="E257" t="s">
-        <v>819</v>
+        <v>363</v>
       </c>
       <c r="F257">
-        <v>210</v>
+        <v>193.58</v>
       </c>
       <c r="G257">
-        <v>3.5</v>
+        <v>3.2263333333333302</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>188</v>
+        <v>336</v>
       </c>
       <c r="B258" t="s">
-        <v>189</v>
+        <v>337</v>
       </c>
       <c r="C258" s="3">
         <v>46327</v>
@@ -9339,21 +9337,21 @@
         <v>9</v>
       </c>
       <c r="E258" t="s">
-        <v>190</v>
+        <v>338</v>
       </c>
       <c r="F258">
-        <v>251.67</v>
+        <v>132.33000000000001</v>
       </c>
       <c r="G258">
-        <v>4.1944999999999997</v>
+        <v>2.2054999999999998</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>207</v>
+        <v>817</v>
       </c>
       <c r="B259" t="s">
-        <v>208</v>
+        <v>818</v>
       </c>
       <c r="C259" s="3">
         <v>46327</v>
@@ -9362,21 +9360,21 @@
         <v>9</v>
       </c>
       <c r="E259" t="s">
-        <v>209</v>
+        <v>819</v>
       </c>
       <c r="F259">
-        <v>199.79</v>
+        <v>210</v>
       </c>
       <c r="G259">
-        <v>3.3298333333333301</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="B260" t="s">
-        <v>597</v>
+        <v>189</v>
       </c>
       <c r="C260" s="3">
         <v>46327</v>
@@ -9385,21 +9383,21 @@
         <v>9</v>
       </c>
       <c r="E260" t="s">
-        <v>598</v>
+        <v>190</v>
       </c>
       <c r="F260">
-        <v>191.88</v>
+        <v>251.67</v>
       </c>
       <c r="G260">
-        <v>3.198</v>
+        <v>4.1944999999999997</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="B261" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="C261" s="3">
         <v>46327</v>
@@ -9408,21 +9406,21 @@
         <v>9</v>
       </c>
       <c r="E261" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="F261">
-        <v>230.82999999999899</v>
+        <v>199.79</v>
       </c>
       <c r="G261">
-        <v>3.8471666666666602</v>
+        <v>3.3298333333333301</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>644</v>
+        <v>84</v>
       </c>
       <c r="B262" t="s">
-        <v>645</v>
+        <v>597</v>
       </c>
       <c r="C262" s="3">
         <v>46327</v>
@@ -9431,21 +9429,21 @@
         <v>9</v>
       </c>
       <c r="E262" t="s">
-        <v>646</v>
+        <v>598</v>
       </c>
       <c r="F262">
-        <v>188.58</v>
+        <v>191.88</v>
       </c>
       <c r="G262">
-        <v>3.1429999999999998</v>
+        <v>3.198</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="B263" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="C263" s="3">
         <v>46327</v>
@@ -9454,36 +9452,36 @@
         <v>9</v>
       </c>
       <c r="E263" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="F263">
-        <v>213.13</v>
+        <v>230.82999999999899</v>
       </c>
       <c r="G263">
-        <v>3.5521666666666598</v>
+        <v>3.8471666666666602</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>50</v>
+        <v>644</v>
       </c>
       <c r="B264" t="s">
-        <v>463</v>
+        <v>645</v>
       </c>
       <c r="C264" s="3">
         <v>46327</v>
       </c>
       <c r="D264" t="s">
-        <v>831</v>
+        <v>9</v>
       </c>
       <c r="E264" t="s">
-        <v>464</v>
+        <v>646</v>
       </c>
       <c r="F264">
-        <v>252.25</v>
+        <v>188.58</v>
       </c>
       <c r="G264">
-        <v>4.2041666666666604</v>
+        <v>3.1429999999999998</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -9491,7 +9489,7 @@
         <v>50</v>
       </c>
       <c r="B265" t="s">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="C265" s="3">
         <v>46327</v>
@@ -9500,44 +9498,44 @@
         <v>9</v>
       </c>
       <c r="E265" t="s">
-        <v>594</v>
+        <v>52</v>
       </c>
       <c r="F265">
-        <v>216.25</v>
+        <v>213.13</v>
       </c>
       <c r="G265">
-        <v>3.6041666666666599</v>
+        <v>3.5521666666666598</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>318</v>
+        <v>50</v>
       </c>
       <c r="B266" t="s">
-        <v>319</v>
+        <v>463</v>
       </c>
       <c r="C266" s="3">
         <v>46327</v>
       </c>
       <c r="D266" t="s">
-        <v>9</v>
+        <v>831</v>
       </c>
       <c r="E266" t="s">
-        <v>320</v>
+        <v>464</v>
       </c>
       <c r="F266">
-        <v>270.42</v>
+        <v>252.25</v>
       </c>
       <c r="G266">
-        <v>4.5069999999999997</v>
+        <v>4.2041666666666604</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>391</v>
+        <v>50</v>
       </c>
       <c r="B267" t="s">
-        <v>392</v>
+        <v>593</v>
       </c>
       <c r="C267" s="3">
         <v>46327</v>
@@ -9546,21 +9544,21 @@
         <v>9</v>
       </c>
       <c r="E267" t="s">
-        <v>393</v>
+        <v>594</v>
       </c>
       <c r="F267">
-        <v>514.79</v>
+        <v>216.25</v>
       </c>
       <c r="G267">
-        <v>8.5798333333333296</v>
+        <v>3.6041666666666599</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>391</v>
+        <v>318</v>
       </c>
       <c r="B268" t="s">
-        <v>622</v>
+        <v>319</v>
       </c>
       <c r="C268" s="3">
         <v>46327</v>
@@ -9569,13 +9567,13 @@
         <v>9</v>
       </c>
       <c r="E268" t="s">
-        <v>623</v>
+        <v>320</v>
       </c>
       <c r="F268">
-        <v>485.29</v>
+        <v>270.42</v>
       </c>
       <c r="G268">
-        <v>8.0881666666666607</v>
+        <v>4.5069999999999997</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -9583,7 +9581,7 @@
         <v>391</v>
       </c>
       <c r="B269" t="s">
-        <v>766</v>
+        <v>392</v>
       </c>
       <c r="C269" s="3">
         <v>46327</v>
@@ -9592,21 +9590,21 @@
         <v>9</v>
       </c>
       <c r="E269" t="s">
-        <v>767</v>
+        <v>393</v>
       </c>
       <c r="F269">
-        <v>288.83</v>
+        <v>514.79</v>
       </c>
       <c r="G269">
-        <v>4.8138333333333296</v>
+        <v>8.5798333333333296</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>109</v>
+        <v>391</v>
       </c>
       <c r="B270" t="s">
-        <v>110</v>
+        <v>622</v>
       </c>
       <c r="C270" s="3">
         <v>46327</v>
@@ -9615,21 +9613,21 @@
         <v>9</v>
       </c>
       <c r="E270" t="s">
-        <v>111</v>
+        <v>623</v>
       </c>
       <c r="F270">
-        <v>279.04000000000002</v>
+        <v>485.29</v>
       </c>
       <c r="G270">
-        <v>4.6506666666666598</v>
+        <v>8.0881666666666607</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>91</v>
+        <v>391</v>
       </c>
       <c r="B271" t="s">
-        <v>92</v>
+        <v>766</v>
       </c>
       <c r="C271" s="3">
         <v>46327</v>
@@ -9638,21 +9636,21 @@
         <v>9</v>
       </c>
       <c r="E271" t="s">
-        <v>93</v>
+        <v>767</v>
       </c>
       <c r="F271">
-        <v>246.38</v>
+        <v>288.83</v>
       </c>
       <c r="G271">
-        <v>4.1063333333333301</v>
+        <v>4.8138333333333296</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B272" t="s">
-        <v>616</v>
+        <v>110</v>
       </c>
       <c r="C272" s="3">
         <v>46327</v>
@@ -9661,21 +9659,21 @@
         <v>9</v>
       </c>
       <c r="E272" t="s">
-        <v>617</v>
+        <v>111</v>
       </c>
       <c r="F272">
-        <v>182.33</v>
+        <v>279.04000000000002</v>
       </c>
       <c r="G272">
-        <v>3.0388333333333302</v>
+        <v>4.6506666666666598</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>489</v>
-      </c>
-      <c r="B273" s="4" t="s">
-        <v>490</v>
+        <v>91</v>
+      </c>
+      <c r="B273" t="s">
+        <v>92</v>
       </c>
       <c r="C273" s="3">
         <v>46327</v>
@@ -9683,16 +9681,22 @@
       <c r="D273" t="s">
         <v>9</v>
       </c>
+      <c r="E273" t="s">
+        <v>93</v>
+      </c>
+      <c r="F273">
+        <v>246.38</v>
+      </c>
       <c r="G273">
-        <v>4.2041666666666604</v>
+        <v>4.1063333333333301</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>489</v>
+        <v>91</v>
       </c>
       <c r="B274" t="s">
-        <v>490</v>
+        <v>616</v>
       </c>
       <c r="C274" s="3">
         <v>46327</v>
@@ -9701,21 +9705,21 @@
         <v>9</v>
       </c>
       <c r="E274" t="s">
-        <v>491</v>
+        <v>617</v>
       </c>
       <c r="F274">
-        <v>269</v>
+        <v>182.33</v>
       </c>
       <c r="G274">
-        <v>4.4833333333333298</v>
+        <v>3.0388333333333302</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>489</v>
       </c>
-      <c r="B275" t="s">
-        <v>505</v>
+      <c r="B275" s="4" t="s">
+        <v>490</v>
       </c>
       <c r="C275" s="3">
         <v>46327</v>
@@ -9723,14 +9727,8 @@
       <c r="D275" t="s">
         <v>9</v>
       </c>
-      <c r="E275" t="s">
-        <v>506</v>
-      </c>
-      <c r="F275">
-        <v>187.25</v>
-      </c>
       <c r="G275">
-        <v>3.12083333333333</v>
+        <v>4.2041666666666604</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -9738,7 +9736,7 @@
         <v>489</v>
       </c>
       <c r="B276" t="s">
-        <v>518</v>
+        <v>490</v>
       </c>
       <c r="C276" s="3">
         <v>46327</v>
@@ -9747,21 +9745,21 @@
         <v>9</v>
       </c>
       <c r="E276" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="F276">
-        <v>255.21</v>
+        <v>269</v>
       </c>
       <c r="G276">
-        <v>4.2534999999999998</v>
+        <v>4.4833333333333298</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>746</v>
+        <v>489</v>
       </c>
       <c r="B277" t="s">
-        <v>747</v>
+        <v>505</v>
       </c>
       <c r="C277" s="3">
         <v>46327</v>
@@ -9770,21 +9768,21 @@
         <v>9</v>
       </c>
       <c r="E277" t="s">
-        <v>748</v>
+        <v>506</v>
       </c>
       <c r="F277">
-        <v>138.79</v>
+        <v>187.25</v>
       </c>
       <c r="G277">
-        <v>2.3131666666666599</v>
+        <v>3.12083333333333</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>140</v>
+        <v>489</v>
       </c>
       <c r="B278" t="s">
-        <v>141</v>
+        <v>518</v>
       </c>
       <c r="C278" s="3">
         <v>46327</v>
@@ -9793,21 +9791,21 @@
         <v>9</v>
       </c>
       <c r="E278" t="s">
-        <v>142</v>
+        <v>519</v>
       </c>
       <c r="F278">
-        <v>331.5</v>
+        <v>255.21</v>
       </c>
       <c r="G278">
-        <v>5.5250000000000004</v>
+        <v>4.2534999999999998</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>902</v>
-      </c>
-      <c r="B279" s="4" t="s">
-        <v>903</v>
+        <v>746</v>
+      </c>
+      <c r="B279" t="s">
+        <v>747</v>
       </c>
       <c r="C279" s="3">
         <v>46327</v>
@@ -9816,21 +9814,21 @@
         <v>9</v>
       </c>
       <c r="E279" t="s">
-        <v>386</v>
+        <v>748</v>
       </c>
       <c r="F279">
-        <v>242.63</v>
+        <v>138.79</v>
       </c>
       <c r="G279">
-        <v>4.0438333333333301</v>
+        <v>2.3131666666666599</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B280" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C280" s="3">
         <v>46327</v>
@@ -9839,21 +9837,21 @@
         <v>9</v>
       </c>
       <c r="E280" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="F280">
-        <v>157.54</v>
+        <v>331.5</v>
       </c>
       <c r="G280">
-        <v>2.6256666666666599</v>
+        <v>5.5250000000000004</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>460</v>
-      </c>
-      <c r="B281" t="s">
-        <v>461</v>
+        <v>902</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>903</v>
       </c>
       <c r="C281" s="3">
         <v>46327</v>
@@ -9862,21 +9860,21 @@
         <v>9</v>
       </c>
       <c r="E281" t="s">
-        <v>462</v>
+        <v>386</v>
       </c>
       <c r="F281">
-        <v>195.25</v>
+        <v>242.63</v>
       </c>
       <c r="G281">
-        <v>3.2541666666666602</v>
+        <v>4.0438333333333301</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>460</v>
+        <v>124</v>
       </c>
       <c r="B282" t="s">
-        <v>520</v>
+        <v>125</v>
       </c>
       <c r="C282" s="3">
         <v>46327</v>
@@ -9885,13 +9883,13 @@
         <v>9</v>
       </c>
       <c r="E282" t="s">
-        <v>521</v>
+        <v>126</v>
       </c>
       <c r="F282">
-        <v>223.13</v>
+        <v>157.54</v>
       </c>
       <c r="G282">
-        <v>3.7188333333333299</v>
+        <v>2.6256666666666599</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -9899,7 +9897,7 @@
         <v>460</v>
       </c>
       <c r="B283" t="s">
-        <v>696</v>
+        <v>461</v>
       </c>
       <c r="C283" s="3">
         <v>46327</v>
@@ -9908,21 +9906,21 @@
         <v>9</v>
       </c>
       <c r="E283" t="s">
-        <v>697</v>
+        <v>462</v>
       </c>
       <c r="F283">
-        <v>205.38</v>
+        <v>195.25</v>
       </c>
       <c r="G283">
-        <v>3.423</v>
+        <v>3.2541666666666602</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>749</v>
+        <v>460</v>
       </c>
       <c r="B284" t="s">
-        <v>750</v>
+        <v>520</v>
       </c>
       <c r="C284" s="3">
         <v>46327</v>
@@ -9931,21 +9929,21 @@
         <v>9</v>
       </c>
       <c r="E284" t="s">
-        <v>751</v>
+        <v>521</v>
       </c>
       <c r="F284">
-        <v>231.71</v>
+        <v>223.13</v>
       </c>
       <c r="G284">
-        <v>3.8618333333333301</v>
+        <v>3.7188333333333299</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>236</v>
+        <v>460</v>
       </c>
       <c r="B285" t="s">
-        <v>237</v>
+        <v>696</v>
       </c>
       <c r="C285" s="3">
         <v>46327</v>
@@ -9954,21 +9952,21 @@
         <v>9</v>
       </c>
       <c r="E285" t="s">
-        <v>238</v>
+        <v>697</v>
       </c>
       <c r="F285">
-        <v>224.57999999999899</v>
+        <v>205.38</v>
       </c>
       <c r="G285">
-        <v>3.7429999999999999</v>
+        <v>3.423</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>297</v>
+        <v>749</v>
       </c>
       <c r="B286" t="s">
-        <v>298</v>
+        <v>750</v>
       </c>
       <c r="C286" s="3">
         <v>46327</v>
@@ -9977,21 +9975,21 @@
         <v>9</v>
       </c>
       <c r="E286" t="s">
-        <v>299</v>
+        <v>751</v>
       </c>
       <c r="F286">
-        <v>230.5</v>
+        <v>231.71</v>
       </c>
       <c r="G286">
-        <v>3.8416666666666601</v>
+        <v>3.8618333333333301</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="B287" t="s">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="C287" s="3">
         <v>46327</v>
@@ -10000,21 +9998,21 @@
         <v>9</v>
       </c>
       <c r="E287" t="s">
-        <v>83</v>
+        <v>238</v>
       </c>
       <c r="F287">
-        <v>298.70999999999998</v>
+        <v>224.57999999999899</v>
       </c>
       <c r="G287">
-        <v>4.9784999999999897</v>
+        <v>3.7429999999999999</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="B288" t="s">
-        <v>100</v>
+        <v>298</v>
       </c>
       <c r="C288" s="3">
         <v>46327</v>
@@ -10023,13 +10021,13 @@
         <v>9</v>
       </c>
       <c r="E288" t="s">
-        <v>101</v>
+        <v>299</v>
       </c>
       <c r="F288">
-        <v>295.92</v>
+        <v>230.5</v>
       </c>
       <c r="G288">
-        <v>4.9320000000000004</v>
+        <v>3.8416666666666601</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -10037,7 +10035,7 @@
         <v>81</v>
       </c>
       <c r="B289" t="s">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="C289" s="3">
         <v>46327</v>
@@ -10046,13 +10044,13 @@
         <v>9</v>
       </c>
       <c r="E289" t="s">
-        <v>446</v>
+        <v>83</v>
       </c>
       <c r="F289">
-        <v>303.70999999999998</v>
+        <v>298.70999999999998</v>
       </c>
       <c r="G289">
-        <v>5.0618333333333299</v>
+        <v>4.9784999999999897</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -10060,7 +10058,7 @@
         <v>81</v>
       </c>
       <c r="B290" t="s">
-        <v>604</v>
+        <v>100</v>
       </c>
       <c r="C290" s="3">
         <v>46327</v>
@@ -10069,13 +10067,13 @@
         <v>9</v>
       </c>
       <c r="E290" t="s">
-        <v>605</v>
+        <v>101</v>
       </c>
       <c r="F290">
-        <v>250.96</v>
+        <v>295.92</v>
       </c>
       <c r="G290">
-        <v>4.1826666666666599</v>
+        <v>4.9320000000000004</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -10083,7 +10081,7 @@
         <v>81</v>
       </c>
       <c r="B291" t="s">
-        <v>698</v>
+        <v>445</v>
       </c>
       <c r="C291" s="3">
         <v>46327</v>
@@ -10092,13 +10090,13 @@
         <v>9</v>
       </c>
       <c r="E291" t="s">
-        <v>699</v>
+        <v>446</v>
       </c>
       <c r="F291">
-        <v>201.07999999999899</v>
+        <v>303.70999999999998</v>
       </c>
       <c r="G291">
-        <v>3.3513333333333302</v>
+        <v>5.0618333333333299</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -10106,7 +10104,7 @@
         <v>81</v>
       </c>
       <c r="B292" t="s">
-        <v>802</v>
+        <v>604</v>
       </c>
       <c r="C292" s="3">
         <v>46327</v>
@@ -10115,21 +10113,21 @@
         <v>9</v>
       </c>
       <c r="E292" t="s">
-        <v>803</v>
+        <v>605</v>
       </c>
       <c r="F292">
-        <v>335.92</v>
+        <v>250.96</v>
       </c>
       <c r="G292">
-        <v>5.5986666666666602</v>
+        <v>4.1826666666666599</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="B293" t="s">
-        <v>422</v>
+        <v>698</v>
       </c>
       <c r="C293" s="3">
         <v>46327</v>
@@ -10138,21 +10136,21 @@
         <v>9</v>
       </c>
       <c r="E293" t="s">
-        <v>423</v>
+        <v>699</v>
       </c>
       <c r="F293">
-        <v>427.17</v>
+        <v>201.07999999999899</v>
       </c>
       <c r="G293">
-        <v>7.1195000000000004</v>
+        <v>3.3513333333333302</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="B294" t="s">
-        <v>246</v>
+        <v>802</v>
       </c>
       <c r="C294" s="3">
         <v>46327</v>
@@ -10161,21 +10159,21 @@
         <v>9</v>
       </c>
       <c r="E294" t="s">
-        <v>247</v>
+        <v>803</v>
       </c>
       <c r="F294">
-        <v>193.71</v>
+        <v>335.92</v>
       </c>
       <c r="G294">
-        <v>3.2284999999999999</v>
+        <v>5.5986666666666602</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>522</v>
+        <v>421</v>
       </c>
       <c r="B295" t="s">
-        <v>523</v>
+        <v>422</v>
       </c>
       <c r="C295" s="3">
         <v>46327</v>
@@ -10184,21 +10182,21 @@
         <v>9</v>
       </c>
       <c r="E295" t="s">
-        <v>524</v>
+        <v>423</v>
       </c>
       <c r="F295">
-        <v>236.82999999999899</v>
+        <v>427.17</v>
       </c>
       <c r="G295">
-        <v>3.9471666666666598</v>
+        <v>7.1195000000000004</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="B296" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="C296" s="3">
         <v>46327</v>
@@ -10207,21 +10205,21 @@
         <v>9</v>
       </c>
       <c r="E296" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="F296">
-        <v>187.25</v>
+        <v>193.71</v>
       </c>
       <c r="G296">
-        <v>3.12083333333333</v>
+        <v>3.2284999999999999</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>599</v>
+        <v>522</v>
       </c>
       <c r="B297" t="s">
-        <v>600</v>
+        <v>523</v>
       </c>
       <c r="C297" s="3">
         <v>46327</v>
@@ -10230,21 +10228,21 @@
         <v>9</v>
       </c>
       <c r="E297" t="s">
-        <v>601</v>
+        <v>524</v>
       </c>
       <c r="F297">
-        <v>308.25</v>
+        <v>236.82999999999899</v>
       </c>
       <c r="G297">
-        <v>5.1375000000000002</v>
+        <v>3.9471666666666598</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>204</v>
+        <v>282</v>
       </c>
       <c r="B298" t="s">
-        <v>205</v>
+        <v>283</v>
       </c>
       <c r="C298" s="3">
         <v>46327</v>
@@ -10253,35 +10251,44 @@
         <v>9</v>
       </c>
       <c r="E298" t="s">
-        <v>206</v>
+        <v>284</v>
       </c>
       <c r="F298">
-        <v>247.17</v>
+        <v>187.25</v>
       </c>
       <c r="G298">
-        <v>4.1194999999999897</v>
+        <v>3.12083333333333</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>854</v>
+        <v>599</v>
       </c>
       <c r="B299" t="s">
-        <v>855</v>
+        <v>600</v>
       </c>
       <c r="C299" s="3">
         <v>46327</v>
       </c>
       <c r="D299" t="s">
         <v>9</v>
+      </c>
+      <c r="E299" t="s">
+        <v>601</v>
+      </c>
+      <c r="F299">
+        <v>308.25</v>
+      </c>
+      <c r="G299">
+        <v>5.1375000000000002</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>17</v>
+        <v>204</v>
       </c>
       <c r="B300" t="s">
-        <v>18</v>
+        <v>205</v>
       </c>
       <c r="C300" s="3">
         <v>46327</v>
@@ -10290,44 +10297,35 @@
         <v>9</v>
       </c>
       <c r="E300" t="s">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="F300">
-        <v>164.29</v>
+        <v>247.17</v>
       </c>
       <c r="G300">
-        <v>2.7381666666666602</v>
+        <v>4.1194999999999897</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>401</v>
+        <v>854</v>
       </c>
       <c r="B301" t="s">
-        <v>402</v>
+        <v>855</v>
       </c>
       <c r="C301" s="3">
         <v>46327</v>
       </c>
       <c r="D301" t="s">
         <v>9</v>
-      </c>
-      <c r="E301" t="s">
-        <v>403</v>
-      </c>
-      <c r="F301">
-        <v>254.29</v>
-      </c>
-      <c r="G301">
-        <v>4.2381666666666602</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c r="B302" t="s">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="C302" s="3">
         <v>46327</v>
@@ -10336,21 +10334,21 @@
         <v>9</v>
       </c>
       <c r="E302" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="F302">
-        <v>167.32999999999899</v>
+        <v>164.29</v>
       </c>
       <c r="G302">
-        <v>2.7888333333333302</v>
+        <v>2.7381666666666602</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>752</v>
+        <v>401</v>
       </c>
       <c r="B303" t="s">
-        <v>753</v>
+        <v>402</v>
       </c>
       <c r="C303" s="3">
         <v>46327</v>
@@ -10359,21 +10357,21 @@
         <v>9</v>
       </c>
       <c r="E303" t="s">
-        <v>754</v>
+        <v>403</v>
       </c>
       <c r="F303">
-        <v>173.5</v>
+        <v>254.29</v>
       </c>
       <c r="G303">
-        <v>2.8916666666666599</v>
+        <v>4.2381666666666602</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>366</v>
+        <v>161</v>
       </c>
       <c r="B304" t="s">
-        <v>367</v>
+        <v>162</v>
       </c>
       <c r="C304" s="3">
         <v>46327</v>
@@ -10382,21 +10380,21 @@
         <v>9</v>
       </c>
       <c r="E304" t="s">
-        <v>368</v>
+        <v>163</v>
       </c>
       <c r="F304">
-        <v>336.67</v>
+        <v>167.32999999999899</v>
       </c>
       <c r="G304">
-        <v>5.6111666666666604</v>
+        <v>2.7888333333333302</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>228</v>
+        <v>752</v>
       </c>
       <c r="B305" t="s">
-        <v>229</v>
+        <v>753</v>
       </c>
       <c r="C305" s="3">
         <v>46327</v>
@@ -10405,21 +10403,21 @@
         <v>9</v>
       </c>
       <c r="E305" t="s">
-        <v>230</v>
+        <v>754</v>
       </c>
       <c r="F305">
-        <v>229</v>
+        <v>173.5</v>
       </c>
       <c r="G305">
-        <v>3.8166666666666602</v>
+        <v>2.8916666666666599</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>228</v>
-      </c>
-      <c r="B306" s="6" t="s">
-        <v>884</v>
+        <v>366</v>
+      </c>
+      <c r="B306" t="s">
+        <v>367</v>
       </c>
       <c r="C306" s="3">
         <v>46327</v>
@@ -10428,21 +10426,21 @@
         <v>9</v>
       </c>
       <c r="E306" t="s">
-        <v>230</v>
+        <v>368</v>
       </c>
       <c r="F306">
-        <v>229</v>
+        <v>336.67</v>
       </c>
       <c r="G306">
-        <v>3.8166666666666602</v>
+        <v>5.6111666666666604</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>581</v>
+        <v>228</v>
       </c>
       <c r="B307" t="s">
-        <v>647</v>
+        <v>229</v>
       </c>
       <c r="C307" s="3">
         <v>46327</v>
@@ -10451,21 +10449,21 @@
         <v>9</v>
       </c>
       <c r="E307" t="s">
-        <v>648</v>
+        <v>230</v>
       </c>
       <c r="F307">
-        <v>161.79</v>
+        <v>229</v>
       </c>
       <c r="G307">
-        <v>2.6964999999999999</v>
+        <v>3.8166666666666602</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>763</v>
-      </c>
-      <c r="B308" t="s">
-        <v>764</v>
+        <v>228</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>884</v>
       </c>
       <c r="C308" s="3">
         <v>46327</v>
@@ -10474,21 +10472,21 @@
         <v>9</v>
       </c>
       <c r="E308" t="s">
-        <v>765</v>
+        <v>230</v>
       </c>
       <c r="F308">
-        <v>351</v>
+        <v>229</v>
       </c>
       <c r="G308">
-        <v>5.85</v>
+        <v>3.8166666666666602</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>351</v>
+        <v>581</v>
       </c>
       <c r="B309" t="s">
-        <v>352</v>
+        <v>647</v>
       </c>
       <c r="C309" s="3">
         <v>46327</v>
@@ -10497,21 +10495,21 @@
         <v>9</v>
       </c>
       <c r="E309" t="s">
-        <v>353</v>
+        <v>648</v>
       </c>
       <c r="F309">
-        <v>306.67</v>
+        <v>161.79</v>
       </c>
       <c r="G309">
-        <v>5.1111666666666604</v>
+        <v>2.6964999999999999</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>636</v>
+        <v>763</v>
       </c>
       <c r="B310" t="s">
-        <v>637</v>
+        <v>764</v>
       </c>
       <c r="C310" s="3">
         <v>46327</v>
@@ -10520,21 +10518,21 @@
         <v>9</v>
       </c>
       <c r="E310" t="s">
-        <v>638</v>
+        <v>765</v>
       </c>
       <c r="F310">
-        <v>244</v>
+        <v>351</v>
       </c>
       <c r="G310">
-        <v>4.0666666666666602</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>576</v>
+        <v>351</v>
       </c>
       <c r="B311" t="s">
-        <v>577</v>
+        <v>352</v>
       </c>
       <c r="C311" s="3">
         <v>46327</v>
@@ -10543,21 +10541,21 @@
         <v>9</v>
       </c>
       <c r="E311" t="s">
-        <v>578</v>
+        <v>353</v>
       </c>
       <c r="F311">
-        <v>262.79000000000002</v>
+        <v>306.67</v>
       </c>
       <c r="G311">
-        <v>4.3798333333333304</v>
+        <v>5.1111666666666604</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>727</v>
+        <v>636</v>
       </c>
       <c r="B312" t="s">
-        <v>728</v>
+        <v>637</v>
       </c>
       <c r="C312" s="3">
         <v>46327</v>
@@ -10566,87 +10564,87 @@
         <v>9</v>
       </c>
       <c r="E312" t="s">
-        <v>729</v>
+        <v>638</v>
       </c>
       <c r="F312">
-        <v>214.21</v>
+        <v>244</v>
       </c>
       <c r="G312">
-        <v>3.57016666666666</v>
+        <v>4.0666666666666602</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>837</v>
+        <v>576</v>
       </c>
       <c r="B313" t="s">
-        <v>870</v>
+        <v>577</v>
       </c>
       <c r="C313" s="3">
         <v>46327</v>
       </c>
       <c r="D313" t="s">
-        <v>831</v>
+        <v>9</v>
+      </c>
+      <c r="E313" t="s">
+        <v>578</v>
+      </c>
+      <c r="F313">
+        <v>262.79000000000002</v>
+      </c>
+      <c r="G313">
+        <v>4.3798333333333304</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>837</v>
+        <v>727</v>
       </c>
       <c r="B314" t="s">
-        <v>840</v>
+        <v>728</v>
       </c>
       <c r="C314" s="3">
         <v>46327</v>
       </c>
       <c r="D314" t="s">
         <v>9</v>
+      </c>
+      <c r="E314" t="s">
+        <v>729</v>
+      </c>
+      <c r="F314">
+        <v>214.21</v>
+      </c>
+      <c r="G314">
+        <v>3.57016666666666</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>324</v>
+        <v>837</v>
       </c>
       <c r="B315" t="s">
-        <v>325</v>
+        <v>870</v>
       </c>
       <c r="C315" s="3">
         <v>46327</v>
       </c>
       <c r="D315" t="s">
-        <v>9</v>
-      </c>
-      <c r="E315" t="s">
-        <v>326</v>
-      </c>
-      <c r="F315">
-        <v>290.54000000000002</v>
-      </c>
-      <c r="G315">
-        <v>4.8423333333333298</v>
+        <v>831</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>324</v>
+        <v>837</v>
       </c>
       <c r="B316" t="s">
-        <v>441</v>
+        <v>840</v>
       </c>
       <c r="C316" s="3">
         <v>46327</v>
       </c>
       <c r="D316" t="s">
         <v>9</v>
-      </c>
-      <c r="E316" t="s">
-        <v>442</v>
-      </c>
-      <c r="F316">
-        <v>345.75</v>
-      </c>
-      <c r="G316">
-        <v>5.7625000000000002</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -10654,7 +10652,7 @@
         <v>324</v>
       </c>
       <c r="B317" t="s">
-        <v>549</v>
+        <v>325</v>
       </c>
       <c r="C317" s="3">
         <v>46327</v>
@@ -10663,21 +10661,21 @@
         <v>9</v>
       </c>
       <c r="E317" t="s">
-        <v>551</v>
+        <v>326</v>
       </c>
       <c r="F317">
-        <v>280.5</v>
+        <v>290.54000000000002</v>
       </c>
       <c r="G317">
-        <v>4.6749999999999998</v>
+        <v>4.8423333333333298</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>156</v>
+        <v>324</v>
       </c>
       <c r="B318" t="s">
-        <v>157</v>
+        <v>441</v>
       </c>
       <c r="C318" s="3">
         <v>46327</v>
@@ -10686,21 +10684,21 @@
         <v>9</v>
       </c>
       <c r="E318" t="s">
-        <v>158</v>
+        <v>442</v>
       </c>
       <c r="F318">
-        <v>492.46</v>
+        <v>345.75</v>
       </c>
       <c r="G318">
-        <v>8.2076666666666593</v>
+        <v>5.7625000000000002</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>11</v>
+        <v>324</v>
       </c>
       <c r="B319" t="s">
-        <v>12</v>
+        <v>549</v>
       </c>
       <c r="C319" s="3">
         <v>46327</v>
@@ -10709,21 +10707,21 @@
         <v>9</v>
       </c>
       <c r="E319" t="s">
-        <v>13</v>
+        <v>551</v>
       </c>
       <c r="F319">
-        <v>237.88</v>
+        <v>280.5</v>
       </c>
       <c r="G319">
-        <v>3.9646666666666599</v>
+        <v>4.6749999999999998</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="B320" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="C320" s="3">
         <v>46327</v>
@@ -10732,13 +10730,13 @@
         <v>9</v>
       </c>
       <c r="E320" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="F320">
-        <v>279.45999999999998</v>
+        <v>492.46</v>
       </c>
       <c r="G320">
-        <v>4.6576666666666604</v>
+        <v>8.2076666666666593</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -10746,7 +10744,7 @@
         <v>11</v>
       </c>
       <c r="B321" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="C321" s="3">
         <v>46327</v>
@@ -10755,13 +10753,13 @@
         <v>9</v>
       </c>
       <c r="E321" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="F321">
-        <v>166.32999999999899</v>
+        <v>237.88</v>
       </c>
       <c r="G321">
-        <v>2.77216666666666</v>
+        <v>3.9646666666666599</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -10769,7 +10767,7 @@
         <v>11</v>
       </c>
       <c r="B322" t="s">
-        <v>256</v>
+        <v>56</v>
       </c>
       <c r="C322" s="3">
         <v>46327</v>
@@ -10778,13 +10776,13 @@
         <v>9</v>
       </c>
       <c r="E322" t="s">
-        <v>257</v>
+        <v>57</v>
       </c>
       <c r="F322">
-        <v>272.70999999999998</v>
+        <v>279.45999999999998</v>
       </c>
       <c r="G322">
-        <v>4.5451666666666597</v>
+        <v>4.6576666666666604</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -10792,7 +10790,7 @@
         <v>11</v>
       </c>
       <c r="B323" t="s">
-        <v>303</v>
+        <v>60</v>
       </c>
       <c r="C323" s="3">
         <v>46327</v>
@@ -10801,13 +10799,13 @@
         <v>9</v>
       </c>
       <c r="E323" t="s">
-        <v>304</v>
+        <v>61</v>
       </c>
       <c r="F323">
-        <v>182.67</v>
+        <v>166.32999999999899</v>
       </c>
       <c r="G323">
-        <v>3.04449999999999</v>
+        <v>2.77216666666666</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -10815,7 +10813,7 @@
         <v>11</v>
       </c>
       <c r="B324" t="s">
-        <v>382</v>
+        <v>256</v>
       </c>
       <c r="C324" s="3">
         <v>46327</v>
@@ -10824,13 +10822,13 @@
         <v>9</v>
       </c>
       <c r="E324" t="s">
-        <v>383</v>
+        <v>257</v>
       </c>
       <c r="F324">
-        <v>225.54</v>
+        <v>272.70999999999998</v>
       </c>
       <c r="G324">
-        <v>3.7589999999999999</v>
+        <v>4.5451666666666597</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -10838,7 +10836,7 @@
         <v>11</v>
       </c>
       <c r="B325" t="s">
-        <v>656</v>
+        <v>303</v>
       </c>
       <c r="C325" s="3">
         <v>46327</v>
@@ -10847,13 +10845,13 @@
         <v>9</v>
       </c>
       <c r="E325" t="s">
-        <v>657</v>
+        <v>304</v>
       </c>
       <c r="F325">
-        <v>528.88</v>
+        <v>182.67</v>
       </c>
       <c r="G325">
-        <v>8.8146666666666604</v>
+        <v>3.04449999999999</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -10861,7 +10859,7 @@
         <v>11</v>
       </c>
       <c r="B326" t="s">
-        <v>773</v>
+        <v>382</v>
       </c>
       <c r="C326" s="3">
         <v>46327</v>
@@ -10870,13 +10868,13 @@
         <v>9</v>
       </c>
       <c r="E326" t="s">
-        <v>774</v>
+        <v>383</v>
       </c>
       <c r="F326">
-        <v>340.5</v>
+        <v>225.54</v>
       </c>
       <c r="G326">
-        <v>5.6749999999999998</v>
+        <v>3.7589999999999999</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -10884,7 +10882,7 @@
         <v>11</v>
       </c>
       <c r="B327" t="s">
-        <v>806</v>
+        <v>656</v>
       </c>
       <c r="C327" s="3">
         <v>46327</v>
@@ -10893,21 +10891,21 @@
         <v>9</v>
       </c>
       <c r="E327" t="s">
-        <v>807</v>
+        <v>657</v>
       </c>
       <c r="F327">
-        <v>268.54000000000002</v>
+        <v>528.88</v>
       </c>
       <c r="G327">
-        <v>4.47566666666666</v>
+        <v>8.8146666666666604</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="B328" t="s">
-        <v>165</v>
+        <v>773</v>
       </c>
       <c r="C328" s="3">
         <v>46327</v>
@@ -10916,21 +10914,21 @@
         <v>9</v>
       </c>
       <c r="E328" t="s">
-        <v>166</v>
+        <v>774</v>
       </c>
       <c r="F328">
-        <v>182.46</v>
+        <v>340.5</v>
       </c>
       <c r="G328">
-        <v>3.0409999999999999</v>
+        <v>5.6749999999999998</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>606</v>
+        <v>11</v>
       </c>
       <c r="B329" t="s">
-        <v>607</v>
+        <v>806</v>
       </c>
       <c r="C329" s="3">
         <v>46327</v>
@@ -10939,21 +10937,21 @@
         <v>9</v>
       </c>
       <c r="E329" t="s">
-        <v>608</v>
+        <v>807</v>
       </c>
       <c r="F329">
-        <v>258.04000000000002</v>
+        <v>268.54000000000002</v>
       </c>
       <c r="G329">
-        <v>4.3006666666666602</v>
+        <v>4.47566666666666</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="B330" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="C330" s="3">
         <v>46327</v>
@@ -10962,21 +10960,21 @@
         <v>9</v>
       </c>
       <c r="E330" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="F330">
-        <v>194.42</v>
+        <v>182.46</v>
       </c>
       <c r="G330">
-        <v>3.24033333333333</v>
+        <v>3.0409999999999999</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>53</v>
+        <v>606</v>
       </c>
       <c r="B331" t="s">
-        <v>54</v>
+        <v>607</v>
       </c>
       <c r="C331" s="3">
         <v>46327</v>
@@ -10985,21 +10983,21 @@
         <v>9</v>
       </c>
       <c r="E331" t="s">
-        <v>55</v>
+        <v>608</v>
       </c>
       <c r="F331">
-        <v>270.45999999999998</v>
+        <v>258.04000000000002</v>
       </c>
       <c r="G331">
-        <v>4.50766666666666</v>
+        <v>4.3006666666666602</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>777</v>
+        <v>20</v>
       </c>
       <c r="B332" t="s">
-        <v>778</v>
+        <v>21</v>
       </c>
       <c r="C332" s="3">
         <v>46327</v>
@@ -11008,21 +11006,21 @@
         <v>9</v>
       </c>
       <c r="E332" t="s">
-        <v>779</v>
+        <v>22</v>
       </c>
       <c r="F332">
-        <v>282.83</v>
+        <v>194.42</v>
       </c>
       <c r="G332">
-        <v>4.71383333333333</v>
+        <v>3.24033333333333</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>822</v>
+        <v>53</v>
       </c>
       <c r="B333" t="s">
-        <v>823</v>
+        <v>54</v>
       </c>
       <c r="C333" s="3">
         <v>46327</v>
@@ -11031,21 +11029,21 @@
         <v>9</v>
       </c>
       <c r="E333" t="s">
-        <v>824</v>
+        <v>55</v>
       </c>
       <c r="F333">
-        <v>200.29</v>
+        <v>270.45999999999998</v>
       </c>
       <c r="G333">
-        <v>3.3381666666666598</v>
+        <v>4.50766666666666</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>641</v>
+        <v>777</v>
       </c>
       <c r="B334" t="s">
-        <v>642</v>
+        <v>778</v>
       </c>
       <c r="C334" s="3">
         <v>46327</v>
@@ -11054,21 +11052,21 @@
         <v>9</v>
       </c>
       <c r="E334" t="s">
-        <v>643</v>
+        <v>779</v>
       </c>
       <c r="F334">
-        <v>277.38</v>
+        <v>282.83</v>
       </c>
       <c r="G334">
-        <v>4.6230000000000002</v>
+        <v>4.71383333333333</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>121</v>
+        <v>822</v>
       </c>
       <c r="B335" t="s">
-        <v>122</v>
+        <v>823</v>
       </c>
       <c r="C335" s="3">
         <v>46327</v>
@@ -11077,21 +11075,21 @@
         <v>9</v>
       </c>
       <c r="E335" t="s">
-        <v>123</v>
+        <v>824</v>
       </c>
       <c r="F335">
-        <v>280.29000000000002</v>
+        <v>200.29</v>
       </c>
       <c r="G335">
-        <v>4.6715</v>
+        <v>3.3381666666666598</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>121</v>
+        <v>641</v>
       </c>
       <c r="B336" t="s">
-        <v>673</v>
+        <v>642</v>
       </c>
       <c r="C336" s="3">
         <v>46327</v>
@@ -11100,13 +11098,13 @@
         <v>9</v>
       </c>
       <c r="E336" t="s">
-        <v>674</v>
+        <v>643</v>
       </c>
       <c r="F336">
-        <v>312.38</v>
+        <v>277.38</v>
       </c>
       <c r="G336">
-        <v>5.2063333333333297</v>
+        <v>4.6230000000000002</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
@@ -11114,7 +11112,7 @@
         <v>121</v>
       </c>
       <c r="B337" t="s">
-        <v>688</v>
+        <v>122</v>
       </c>
       <c r="C337" s="3">
         <v>46327</v>
@@ -11123,21 +11121,21 @@
         <v>9</v>
       </c>
       <c r="E337" t="s">
-        <v>689</v>
+        <v>123</v>
       </c>
       <c r="F337">
-        <v>239</v>
+        <v>280.29000000000002</v>
       </c>
       <c r="G337">
-        <v>3.9833333333333298</v>
+        <v>4.6715</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="B338" t="s">
-        <v>45</v>
+        <v>673</v>
       </c>
       <c r="C338" s="3">
         <v>46327</v>
@@ -11146,21 +11144,21 @@
         <v>9</v>
       </c>
       <c r="E338" t="s">
-        <v>46</v>
+        <v>674</v>
       </c>
       <c r="F338">
-        <v>600.88</v>
+        <v>312.38</v>
       </c>
       <c r="G338">
-        <v>10.014666666666599</v>
+        <v>5.2063333333333297</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="B339" t="s">
-        <v>58</v>
+        <v>688</v>
       </c>
       <c r="C339" s="3">
         <v>46327</v>
@@ -11169,13 +11167,13 @@
         <v>9</v>
       </c>
       <c r="E339" t="s">
-        <v>59</v>
+        <v>689</v>
       </c>
       <c r="F339">
-        <v>309.5</v>
+        <v>239</v>
       </c>
       <c r="G339">
-        <v>5.1583333333333297</v>
+        <v>3.9833333333333298</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.3">
@@ -11183,7 +11181,7 @@
         <v>44</v>
       </c>
       <c r="B340" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="C340" s="3">
         <v>46327</v>
@@ -11192,13 +11190,13 @@
         <v>9</v>
       </c>
       <c r="E340" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="F340">
-        <v>272.54000000000002</v>
+        <v>600.88</v>
       </c>
       <c r="G340">
-        <v>4.54233333333333</v>
+        <v>10.014666666666599</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
@@ -11206,7 +11204,7 @@
         <v>44</v>
       </c>
       <c r="B341" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="C341" s="3">
         <v>46327</v>
@@ -11215,13 +11213,13 @@
         <v>9</v>
       </c>
       <c r="E341" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="F341">
-        <v>240.13</v>
+        <v>309.5</v>
       </c>
       <c r="G341">
-        <v>4.0021666666666604</v>
+        <v>5.1583333333333297</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
@@ -11229,7 +11227,7 @@
         <v>44</v>
       </c>
       <c r="B342" t="s">
-        <v>430</v>
+        <v>107</v>
       </c>
       <c r="C342" s="3">
         <v>46327</v>
@@ -11238,13 +11236,13 @@
         <v>9</v>
       </c>
       <c r="E342" t="s">
-        <v>431</v>
+        <v>108</v>
       </c>
       <c r="F342">
-        <v>240.54</v>
+        <v>272.54000000000002</v>
       </c>
       <c r="G342">
-        <v>4.0089999999999897</v>
+        <v>4.54233333333333</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
@@ -11252,7 +11250,7 @@
         <v>44</v>
       </c>
       <c r="B343" t="s">
-        <v>437</v>
+        <v>132</v>
       </c>
       <c r="C343" s="3">
         <v>46327</v>
@@ -11261,13 +11259,13 @@
         <v>9</v>
       </c>
       <c r="E343" t="s">
-        <v>438</v>
+        <v>133</v>
       </c>
       <c r="F343">
-        <v>238.29</v>
+        <v>240.13</v>
       </c>
       <c r="G343">
-        <v>3.9714999999999998</v>
+        <v>4.0021666666666604</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.3">
@@ -11275,7 +11273,7 @@
         <v>44</v>
       </c>
       <c r="B344" t="s">
-        <v>533</v>
+        <v>430</v>
       </c>
       <c r="C344" s="3">
         <v>46327</v>
@@ -11284,13 +11282,13 @@
         <v>9</v>
       </c>
       <c r="E344" t="s">
-        <v>534</v>
+        <v>431</v>
       </c>
       <c r="F344">
-        <v>236.17</v>
+        <v>240.54</v>
       </c>
       <c r="G344">
-        <v>3.9361666666666602</v>
+        <v>4.0089999999999897</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.3">
@@ -11298,7 +11296,7 @@
         <v>44</v>
       </c>
       <c r="B345" t="s">
-        <v>591</v>
+        <v>437</v>
       </c>
       <c r="C345" s="3">
         <v>46327</v>
@@ -11307,13 +11305,13 @@
         <v>9</v>
       </c>
       <c r="E345" t="s">
-        <v>592</v>
+        <v>438</v>
       </c>
       <c r="F345">
-        <v>258.13</v>
+        <v>238.29</v>
       </c>
       <c r="G345">
-        <v>4.3021666666666603</v>
+        <v>3.9714999999999998</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.3">
@@ -11321,7 +11319,7 @@
         <v>44</v>
       </c>
       <c r="B346" t="s">
-        <v>639</v>
+        <v>533</v>
       </c>
       <c r="C346" s="3">
         <v>46327</v>
@@ -11330,13 +11328,13 @@
         <v>9</v>
       </c>
       <c r="E346" t="s">
-        <v>640</v>
+        <v>534</v>
       </c>
       <c r="F346">
-        <v>243.08</v>
+        <v>236.17</v>
       </c>
       <c r="G346">
-        <v>4.0513333333333303</v>
+        <v>3.9361666666666602</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.3">
@@ -11344,7 +11342,7 @@
         <v>44</v>
       </c>
       <c r="B347" t="s">
-        <v>675</v>
+        <v>591</v>
       </c>
       <c r="C347" s="3">
         <v>46327</v>
@@ -11353,13 +11351,13 @@
         <v>9</v>
       </c>
       <c r="E347" t="s">
-        <v>676</v>
+        <v>592</v>
       </c>
       <c r="F347">
-        <v>226.13</v>
+        <v>258.13</v>
       </c>
       <c r="G347">
-        <v>3.7688333333333301</v>
+        <v>4.3021666666666603</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
@@ -11367,7 +11365,7 @@
         <v>44</v>
       </c>
       <c r="B348" t="s">
-        <v>775</v>
+        <v>639</v>
       </c>
       <c r="C348" s="3">
         <v>46327</v>
@@ -11376,13 +11374,13 @@
         <v>9</v>
       </c>
       <c r="E348" t="s">
-        <v>776</v>
+        <v>640</v>
       </c>
       <c r="F348">
-        <v>234.75</v>
+        <v>243.08</v>
       </c>
       <c r="G348">
-        <v>3.9125000000000001</v>
+        <v>4.0513333333333303</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
@@ -11390,7 +11388,7 @@
         <v>44</v>
       </c>
       <c r="B349" t="s">
-        <v>804</v>
+        <v>675</v>
       </c>
       <c r="C349" s="3">
         <v>46327</v>
@@ -11399,21 +11397,21 @@
         <v>9</v>
       </c>
       <c r="E349" t="s">
-        <v>805</v>
+        <v>676</v>
       </c>
       <c r="F349">
-        <v>228.57999999999899</v>
+        <v>226.13</v>
       </c>
       <c r="G349">
-        <v>3.8096666666666601</v>
+        <v>3.7688333333333301</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>680</v>
+        <v>44</v>
       </c>
       <c r="B350" t="s">
-        <v>681</v>
+        <v>775</v>
       </c>
       <c r="C350" s="3">
         <v>46327</v>
@@ -11422,21 +11420,21 @@
         <v>9</v>
       </c>
       <c r="E350" t="s">
-        <v>682</v>
+        <v>776</v>
       </c>
       <c r="F350">
-        <v>203.13</v>
+        <v>234.75</v>
       </c>
       <c r="G350">
-        <v>3.3855</v>
+        <v>3.9125000000000001</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>680</v>
+        <v>44</v>
       </c>
       <c r="B351" t="s">
-        <v>702</v>
+        <v>804</v>
       </c>
       <c r="C351" s="3">
         <v>46327</v>
@@ -11445,21 +11443,21 @@
         <v>9</v>
       </c>
       <c r="E351" t="s">
-        <v>703</v>
+        <v>805</v>
       </c>
       <c r="F351">
-        <v>205</v>
+        <v>228.57999999999899</v>
       </c>
       <c r="G351">
-        <v>3.4166666666666599</v>
+        <v>3.8096666666666601</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>222</v>
+        <v>680</v>
       </c>
       <c r="B352" t="s">
-        <v>223</v>
+        <v>681</v>
       </c>
       <c r="C352" s="3">
         <v>46327</v>
@@ -11468,21 +11466,21 @@
         <v>9</v>
       </c>
       <c r="E352" t="s">
-        <v>224</v>
+        <v>682</v>
       </c>
       <c r="F352">
-        <v>246.71</v>
+        <v>203.13</v>
       </c>
       <c r="G352">
-        <v>4.1118333333333297</v>
+        <v>3.3855</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>724</v>
+        <v>680</v>
       </c>
       <c r="B353" t="s">
-        <v>725</v>
+        <v>702</v>
       </c>
       <c r="C353" s="3">
         <v>46327</v>
@@ -11491,21 +11489,21 @@
         <v>9</v>
       </c>
       <c r="E353" t="s">
-        <v>726</v>
+        <v>703</v>
       </c>
       <c r="F353">
-        <v>273.17</v>
+        <v>205</v>
       </c>
       <c r="G353">
-        <v>4.5528333333333304</v>
+        <v>3.4166666666666599</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="B354" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="C354" s="3">
         <v>46327</v>
@@ -11514,21 +11512,21 @@
         <v>9</v>
       </c>
       <c r="E354" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="F354">
-        <v>296.67</v>
+        <v>246.71</v>
       </c>
       <c r="G354">
-        <v>4.9444999999999997</v>
+        <v>4.1118333333333297</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>525</v>
+        <v>724</v>
       </c>
       <c r="B355" t="s">
-        <v>526</v>
+        <v>725</v>
       </c>
       <c r="C355" s="3">
         <v>46327</v>
@@ -11537,21 +11535,21 @@
         <v>9</v>
       </c>
       <c r="E355" t="s">
-        <v>527</v>
+        <v>726</v>
       </c>
       <c r="F355">
-        <v>280.08</v>
+        <v>273.17</v>
       </c>
       <c r="G355">
-        <v>4.6680000000000001</v>
+        <v>4.5528333333333304</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>525</v>
+        <v>239</v>
       </c>
       <c r="B356" t="s">
-        <v>788</v>
+        <v>240</v>
       </c>
       <c r="C356" s="3">
         <v>46327</v>
@@ -11560,21 +11558,21 @@
         <v>9</v>
       </c>
       <c r="E356" t="s">
-        <v>789</v>
+        <v>241</v>
       </c>
       <c r="F356">
-        <v>292.29000000000002</v>
+        <v>296.67</v>
       </c>
       <c r="G356">
-        <v>4.8715000000000002</v>
+        <v>4.9444999999999997</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>14</v>
+        <v>525</v>
       </c>
       <c r="B357" t="s">
-        <v>15</v>
+        <v>526</v>
       </c>
       <c r="C357" s="3">
         <v>46327</v>
@@ -11583,21 +11581,21 @@
         <v>9</v>
       </c>
       <c r="E357" t="s">
-        <v>16</v>
+        <v>527</v>
       </c>
       <c r="F357">
-        <v>215.82999999999899</v>
+        <v>280.08</v>
       </c>
       <c r="G357">
-        <v>3.5971666666666602</v>
+        <v>4.6680000000000001</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>14</v>
+        <v>525</v>
       </c>
       <c r="B358" t="s">
-        <v>568</v>
+        <v>788</v>
       </c>
       <c r="C358" s="3">
         <v>46327</v>
@@ -11606,21 +11604,21 @@
         <v>9</v>
       </c>
       <c r="E358" t="s">
-        <v>569</v>
+        <v>789</v>
       </c>
       <c r="F358">
-        <v>203.57999999999899</v>
+        <v>292.29000000000002</v>
       </c>
       <c r="G358">
-        <v>3.3929999999999998</v>
+        <v>4.8715000000000002</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>248</v>
+        <v>14</v>
       </c>
       <c r="B359" t="s">
-        <v>249</v>
+        <v>15</v>
       </c>
       <c r="C359" s="3">
         <v>46327</v>
@@ -11629,21 +11627,21 @@
         <v>9</v>
       </c>
       <c r="E359" t="s">
-        <v>250</v>
+        <v>16</v>
       </c>
       <c r="F359">
-        <v>202</v>
+        <v>215.82999999999899</v>
       </c>
       <c r="G359">
-        <v>3.36666666666666</v>
+        <v>3.5971666666666602</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="B360" t="s">
-        <v>105</v>
+        <v>568</v>
       </c>
       <c r="C360" s="3">
         <v>46327</v>
@@ -11652,21 +11650,21 @@
         <v>9</v>
       </c>
       <c r="E360" t="s">
-        <v>106</v>
+        <v>569</v>
       </c>
       <c r="F360">
-        <v>275.58</v>
+        <v>203.57999999999899</v>
       </c>
       <c r="G360">
-        <v>4.593</v>
+        <v>3.3929999999999998</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>455</v>
+        <v>248</v>
       </c>
       <c r="B361" t="s">
-        <v>458</v>
+        <v>249</v>
       </c>
       <c r="C361" s="3">
         <v>46327</v>
@@ -11675,21 +11673,21 @@
         <v>9</v>
       </c>
       <c r="E361" t="s">
-        <v>459</v>
+        <v>250</v>
       </c>
       <c r="F361">
-        <v>166.32999999999899</v>
+        <v>202</v>
       </c>
       <c r="G361">
-        <v>2.77216666666666</v>
+        <v>3.36666666666666</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>455</v>
+        <v>104</v>
       </c>
       <c r="B362" t="s">
-        <v>456</v>
+        <v>105</v>
       </c>
       <c r="C362" s="3">
         <v>46327</v>
@@ -11698,21 +11696,21 @@
         <v>9</v>
       </c>
       <c r="E362" t="s">
-        <v>457</v>
+        <v>106</v>
       </c>
       <c r="F362">
-        <v>166.32999999999899</v>
+        <v>275.58</v>
       </c>
       <c r="G362">
-        <v>2.77216666666666</v>
+        <v>4.593</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="B363" t="s">
-        <v>399</v>
+        <v>458</v>
       </c>
       <c r="C363" s="3">
         <v>46327</v>
@@ -11721,21 +11719,21 @@
         <v>9</v>
       </c>
       <c r="E363" t="s">
-        <v>400</v>
+        <v>459</v>
       </c>
       <c r="F363">
-        <v>278.5</v>
+        <v>166.32999999999899</v>
       </c>
       <c r="G363">
-        <v>4.6416666666666604</v>
+        <v>2.77216666666666</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>342</v>
+        <v>455</v>
       </c>
       <c r="B364" t="s">
-        <v>343</v>
+        <v>456</v>
       </c>
       <c r="C364" s="3">
         <v>46327</v>
@@ -11744,21 +11742,21 @@
         <v>9</v>
       </c>
       <c r="E364" t="s">
-        <v>344</v>
+        <v>457</v>
       </c>
       <c r="F364">
-        <v>274.08</v>
+        <v>166.32999999999899</v>
       </c>
       <c r="G364">
-        <v>4.5679999999999996</v>
+        <v>2.77216666666666</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>588</v>
+        <v>398</v>
       </c>
       <c r="B365" t="s">
-        <v>589</v>
+        <v>399</v>
       </c>
       <c r="C365" s="3">
         <v>46327</v>
@@ -11767,21 +11765,21 @@
         <v>9</v>
       </c>
       <c r="E365" t="s">
-        <v>590</v>
+        <v>400</v>
       </c>
       <c r="F365">
-        <v>237.46</v>
+        <v>278.5</v>
       </c>
       <c r="G365">
-        <v>3.9576666666666598</v>
+        <v>4.6416666666666604</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>216</v>
+        <v>342</v>
       </c>
       <c r="B366" t="s">
-        <v>217</v>
+        <v>343</v>
       </c>
       <c r="C366" s="3">
         <v>46327</v>
@@ -11790,21 +11788,21 @@
         <v>9</v>
       </c>
       <c r="E366" t="s">
-        <v>218</v>
+        <v>344</v>
       </c>
       <c r="F366">
-        <v>421.54</v>
+        <v>274.08</v>
       </c>
       <c r="G366">
-        <v>7.0256666666666598</v>
+        <v>4.5679999999999996</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>538</v>
+        <v>588</v>
       </c>
       <c r="B367" t="s">
-        <v>539</v>
+        <v>589</v>
       </c>
       <c r="C367" s="3">
         <v>46327</v>
@@ -11813,110 +11811,156 @@
         <v>9</v>
       </c>
       <c r="E367" t="s">
-        <v>540</v>
+        <v>590</v>
       </c>
       <c r="F367">
-        <v>279</v>
+        <v>237.46</v>
       </c>
       <c r="G367">
-        <v>4.6500000000000004</v>
+        <v>3.9576666666666598</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="B368" t="s">
-        <v>896</v>
+        <v>217</v>
       </c>
       <c r="C368" s="3">
-        <f>C367+1</f>
-        <v>46328</v>
+        <v>46327</v>
       </c>
       <c r="D368" t="s">
-        <v>831</v>
+        <v>9</v>
       </c>
       <c r="E368" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="F368">
-        <v>181.25</v>
+        <v>421.54</v>
       </c>
       <c r="G368">
-        <v>3.0208333333333299</v>
+        <v>7.0256666666666598</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>892</v>
-      </c>
-      <c r="B369" s="4" t="s">
-        <v>893</v>
+        <v>538</v>
+      </c>
+      <c r="B369" t="s">
+        <v>539</v>
       </c>
       <c r="C369" s="3">
-        <f>C368+1</f>
-        <v>46329</v>
+        <v>46327</v>
       </c>
       <c r="D369" t="s">
-        <v>831</v>
+        <v>9</v>
+      </c>
+      <c r="E369" t="s">
+        <v>540</v>
       </c>
       <c r="F369">
-        <v>226.38</v>
+        <v>279</v>
       </c>
       <c r="G369">
-        <v>3.7730000000000001</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>895</v>
-      </c>
-      <c r="B370" s="7" t="s">
-        <v>894</v>
+        <v>185</v>
+      </c>
+      <c r="B370" t="s">
+        <v>896</v>
       </c>
       <c r="C370" s="3">
         <f>C369+1</f>
-        <v>46330</v>
+        <v>46328</v>
       </c>
       <c r="D370" t="s">
-        <v>9</v>
+        <v>831</v>
+      </c>
+      <c r="E370" t="s">
+        <v>187</v>
       </c>
       <c r="F370">
-        <v>292.63</v>
+        <v>181.25</v>
       </c>
       <c r="G370">
-        <v>4.8771666666666604</v>
+        <v>3.0208333333333299</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
+        <v>892</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="C371" s="3">
+        <f>C370+1</f>
+        <v>46329</v>
+      </c>
+      <c r="D371" t="s">
+        <v>831</v>
+      </c>
+      <c r="F371">
+        <v>226.38</v>
+      </c>
+      <c r="G371">
+        <v>3.7730000000000001</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>895</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="C372" s="3">
+        <f>C371+1</f>
+        <v>46330</v>
+      </c>
+      <c r="D372" t="s">
+        <v>9</v>
+      </c>
+      <c r="F372">
+        <v>292.63</v>
+      </c>
+      <c r="G372">
+        <v>4.8771666666666604</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
         <v>94</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B373" t="s">
         <v>95</v>
       </c>
-      <c r="C371" s="3">
-        <f>C369+1</f>
+      <c r="C373" s="3">
+        <f>C371+1</f>
         <v>46330</v>
       </c>
-      <c r="D371" t="s">
-        <v>9</v>
-      </c>
-      <c r="E371" t="s">
+      <c r="D373" t="s">
+        <v>9</v>
+      </c>
+      <c r="E373" t="s">
         <v>96</v>
       </c>
-      <c r="F371">
+      <c r="F373">
         <v>216.57999999999899</v>
       </c>
-      <c r="G371">
+      <c r="G373">
         <v>3.6096666666666599</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H371">
-    <sortCondition ref="C2:C371"/>
-    <sortCondition ref="A2:A371"/>
-    <sortCondition ref="B2:B371"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H373">
+    <sortCondition ref="C2:C373"/>
+    <sortCondition ref="A2:A373"/>
+    <sortCondition ref="B2:B373"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/Excel/video_durations.xlsx
+++ b/Excel/video_durations.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13835" windowHeight="9000"/>
+    <workbookView windowWidth="8195" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="video_durations" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="1013">
   <si>
     <t>artist</t>
   </si>
@@ -929,6 +929,105 @@
     <t>Bailamos</t>
   </si>
   <si>
+    <r>
+      <t>สัญญาหน้าฝน</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> (TH)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>น้ำตามดแดง</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> (TH)</t>
+    </r>
+  </si>
+  <si>
+    <t>Foreigner</t>
+  </si>
+  <si>
+    <t>Waiting for a Girl Like You</t>
+  </si>
+  <si>
+    <t>Waiting for a Girl Like You_Foreigner .mp4</t>
+  </si>
+  <si>
+    <t>Gotye</t>
+  </si>
+  <si>
+    <t>Somebody That I Used To Know</t>
+  </si>
+  <si>
+    <t>Somebody That I Used To Know_Gotye .mp4</t>
+  </si>
+  <si>
+    <t>Your Cheatin' Heart</t>
+  </si>
+  <si>
+    <t>Your Cheatin' Heart_Hank Williams.mp4</t>
+  </si>
+  <si>
+    <t>Impressions The</t>
+  </si>
+  <si>
+    <t>People Get Ready</t>
+  </si>
+  <si>
+    <t>People Get Ready_Impressions The.mp4</t>
+  </si>
+  <si>
+    <t>Handy Man</t>
+  </si>
+  <si>
+    <t>Handy Man_James Taylor.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t>ยิ่งใกล้ยิ่งเจ็บ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> (TH)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>เก็บตะวัน</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> (TH)</t>
+    </r>
+  </si>
+  <si>
     <t>Hot N Cold</t>
   </si>
   <si>
@@ -2021,21 +2120,12 @@
     <t>Landslide_Fleetwood Mac .mp4</t>
   </si>
   <si>
-    <t>Foreigner</t>
-  </si>
-  <si>
     <t>I Want to Know What Love Is</t>
   </si>
   <si>
     <t>I Want to Know What Love Is_Foreigner .mp4</t>
   </si>
   <si>
-    <t>Waiting for a Girl Like You</t>
-  </si>
-  <si>
-    <t>Waiting for a Girl Like You_Foreigner .mp4</t>
-  </si>
-  <si>
     <t>Frank Sinatra</t>
   </si>
   <si>
@@ -2084,15 +2174,6 @@
     <t>Iris_Goo Goo Dolls.mp4</t>
   </si>
   <si>
-    <t>Gotye</t>
-  </si>
-  <si>
-    <t>Somebody That I Used To Know</t>
-  </si>
-  <si>
-    <t>Somebody That I Used To Know_Gotye .mp4</t>
-  </si>
-  <si>
     <t>Graham Lukas</t>
   </si>
   <si>
@@ -2120,12 +2201,6 @@
     <t>Welcome to the Jungle_Guns nâ€™ Roses .mp4</t>
   </si>
   <si>
-    <t>Your Cheatin' Heart</t>
-  </si>
-  <si>
-    <t>Your Cheatin' Heart_Hank Williams.mp4</t>
-  </si>
-  <si>
     <t>Harry Chapin</t>
   </si>
   <si>
@@ -2153,15 +2228,6 @@
     <t>Thunder</t>
   </si>
   <si>
-    <t>Impressions The</t>
-  </si>
-  <si>
-    <t>People Get Ready</t>
-  </si>
-  <si>
-    <t>People Get Ready_Impressions The.mp4</t>
-  </si>
-  <si>
     <t>Incubus</t>
   </si>
   <si>
@@ -2187,12 +2253,6 @@
   </si>
   <si>
     <t>You're Beautiful_James Blunt.mp4</t>
-  </si>
-  <si>
-    <t>Handy Man</t>
-  </si>
-  <si>
-    <t>Handy Man_James Taylor.mp4</t>
   </si>
   <si>
     <t>Janis Joplin</t>
@@ -3068,7 +3128,7 @@
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="179" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -3149,6 +3209,13 @@
     <font>
       <sz val="9"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3591,70 +3658,70 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3691,6 +3758,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4031,11 +4101,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I442"/>
+  <dimension ref="A1:I444"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13.4444444444444" customWidth="1"/>
-    <col min="2" max="2" width="47.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="29.4444444444444" customWidth="1"/>
     <col min="3" max="3" width="10.1111111111111" style="2" customWidth="1"/>
     <col min="4" max="4" width="4.55555555555556" customWidth="1"/>
     <col min="5" max="5" width="24" style="3" customWidth="1"/>
@@ -6890,13 +6960,13 @@
         <v>3.773</v>
       </c>
     </row>
-    <row r="133" s="1" customFormat="1" ht="22.2" spans="1:9">
+    <row r="133" s="1" customFormat="1" ht="27" spans="1:9">
       <c r="A133" s="7"/>
-      <c r="B133" s="20" t="s">
-        <v>286</v>
+      <c r="B133" s="23" t="s">
+        <v>300</v>
       </c>
       <c r="C133" s="8">
-        <f>C132+1</f>
+        <f t="shared" ref="C133:C141" si="0">C132+1</f>
         <v>46242</v>
       </c>
       <c r="D133" s="1" t="s">
@@ -6907,13 +6977,13 @@
       </c>
       <c r="I133"/>
     </row>
-    <row r="134" s="1" customFormat="1" ht="22.2" spans="1:5">
+    <row r="134" s="1" customFormat="1" ht="27" spans="1:5">
       <c r="A134" s="7"/>
-      <c r="B134" s="20" t="s">
-        <v>287</v>
+      <c r="B134" s="23" t="s">
+        <v>301</v>
       </c>
       <c r="C134" s="8">
-        <f>C133+1</f>
+        <f t="shared" si="0"/>
         <v>46243</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -6923,101 +6993,123 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>113</v>
+        <v>302</v>
       </c>
       <c r="B135" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C135" s="2">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="D135" t="s">
         <v>16</v>
       </c>
       <c r="E135" s="3">
-        <v>46246</v>
+        <v>46327</v>
+      </c>
+      <c r="F135" t="s">
+        <v>304</v>
+      </c>
+      <c r="G135">
+        <v>284.92</v>
+      </c>
+      <c r="H135">
+        <v>4.74866666666666</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B136" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C136" s="2">
-        <v>46251</v>
+        <f t="shared" si="0"/>
+        <v>46245</v>
       </c>
       <c r="D136" t="s">
         <v>16</v>
       </c>
       <c r="E136" s="3">
-        <v>46251</v>
+        <v>46327</v>
       </c>
       <c r="F136" t="s">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="G136">
-        <v>270.42</v>
+        <v>243.96</v>
       </c>
       <c r="H136">
-        <v>4.507</v>
+        <v>4.066</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="B137" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C137" s="2">
-        <v>46257</v>
+        <f t="shared" si="0"/>
+        <v>46246</v>
       </c>
       <c r="D137" t="s">
         <v>9</v>
       </c>
       <c r="E137" s="3">
-        <v>46257</v>
+        <v>46327</v>
       </c>
       <c r="F137" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="G137">
-        <v>229</v>
+        <v>162.829999999999</v>
       </c>
       <c r="H137">
-        <v>3.81666666666666</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>2.71383333333333</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>150</v>
-      </c>
-      <c r="B138" s="11" t="s">
-        <v>151</v>
+        <v>310</v>
+      </c>
+      <c r="B138" t="s">
+        <v>311</v>
       </c>
       <c r="C138" s="2">
-        <v>46262</v>
+        <f t="shared" si="0"/>
+        <v>46247</v>
       </c>
       <c r="D138" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E138" s="3">
-        <v>46262</v>
+        <v>46327</v>
+      </c>
+      <c r="F138" t="s">
+        <v>312</v>
+      </c>
+      <c r="G138">
+        <v>158.63</v>
+      </c>
+      <c r="H138">
+        <v>2.64383333333333</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B139" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C139" s="2">
-        <v>46327</v>
+        <f t="shared" si="0"/>
+        <v>46248</v>
       </c>
       <c r="D139" t="s">
         <v>9</v>
@@ -7026,255 +7118,218 @@
         <v>46327</v>
       </c>
       <c r="F139" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="G139">
-        <v>232.96</v>
+        <v>196.25</v>
       </c>
       <c r="H139">
-        <v>3.88266666666666</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
-      <c r="A140" t="s">
-        <v>308</v>
-      </c>
-      <c r="B140" t="s">
-        <v>309</v>
-      </c>
-      <c r="C140" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D140" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F140" t="s">
-        <v>310</v>
-      </c>
-      <c r="G140">
-        <v>207.13</v>
-      </c>
-      <c r="H140">
-        <v>3.45216666666666</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" t="s">
-        <v>311</v>
-      </c>
-      <c r="B141" t="s">
-        <v>312</v>
-      </c>
-      <c r="C141" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D141" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F141" t="s">
-        <v>313</v>
-      </c>
-      <c r="G141">
-        <v>227.71</v>
-      </c>
-      <c r="H141">
-        <v>3.79516666666666</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
+        <v>3.27083333333333</v>
+      </c>
+    </row>
+    <row r="140" s="1" customFormat="1" ht="27" spans="1:9">
+      <c r="A140" s="7"/>
+      <c r="B140" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="C140" s="8">
+        <f t="shared" si="0"/>
+        <v>46249</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" s="9">
+        <v>46235</v>
+      </c>
+      <c r="I140"/>
+    </row>
+    <row r="141" s="1" customFormat="1" ht="27" spans="1:5">
+      <c r="A141" s="7"/>
+      <c r="B141" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C141" s="8">
+        <f t="shared" si="0"/>
+        <v>46250</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" s="9">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>311</v>
+        <v>113</v>
       </c>
       <c r="B142" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C142" s="2">
-        <v>46327</v>
+        <v>46246</v>
       </c>
       <c r="D142" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E142" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F142" t="s">
-        <v>315</v>
-      </c>
-      <c r="G142">
-        <v>234</v>
-      </c>
-      <c r="H142">
-        <v>3.9</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B143" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C143" s="2">
-        <v>46327</v>
+        <v>46251</v>
       </c>
       <c r="D143" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E143" s="3">
-        <v>46327</v>
+        <v>46251</v>
       </c>
       <c r="F143" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
       <c r="G143">
-        <v>285.04</v>
+        <v>270.42</v>
       </c>
       <c r="H143">
-        <v>4.75066666666666</v>
+        <v>4.507</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B144" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C144" s="2">
-        <v>46327</v>
+        <v>46257</v>
       </c>
       <c r="D144" t="s">
         <v>9</v>
       </c>
       <c r="E144" s="3">
-        <v>46327</v>
+        <v>46257</v>
       </c>
       <c r="F144" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="G144">
-        <v>283.13</v>
+        <v>229</v>
       </c>
       <c r="H144">
-        <v>4.71883333333333</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
+        <v>3.81666666666666</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>321</v>
-      </c>
-      <c r="B145" t="s">
-        <v>322</v>
+        <v>150</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="C145" s="2">
-        <v>46327</v>
+        <v>46262</v>
       </c>
       <c r="D145" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E145" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F145" t="s">
-        <v>323</v>
-      </c>
-      <c r="G145">
-        <v>236.71</v>
-      </c>
-      <c r="H145">
-        <v>3.94516666666666</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
+        <v>322</v>
+      </c>
+      <c r="B146" t="s">
+        <v>323</v>
+      </c>
+      <c r="C146" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D146" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F146" t="s">
         <v>324</v>
       </c>
-      <c r="B146" t="s">
-        <v>325</v>
-      </c>
-      <c r="C146" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D146" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F146" t="s">
-        <v>326</v>
-      </c>
       <c r="G146">
-        <v>212.88</v>
+        <v>232.96</v>
       </c>
       <c r="H146">
-        <v>3.548</v>
+        <v>3.88266666666666</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" t="s">
+        <v>326</v>
+      </c>
+      <c r="C147" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D147" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F147" t="s">
         <v>327</v>
       </c>
-      <c r="B147" t="s">
-        <v>328</v>
-      </c>
-      <c r="C147" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D147" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F147" t="s">
-        <v>329</v>
-      </c>
       <c r="G147">
-        <v>232.96</v>
+        <v>207.13</v>
       </c>
       <c r="H147">
-        <v>3.88266666666666</v>
+        <v>3.45216666666666</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
+        <v>328</v>
+      </c>
+      <c r="B148" t="s">
+        <v>329</v>
+      </c>
+      <c r="C148" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D148" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F148" t="s">
         <v>330</v>
       </c>
-      <c r="B148" t="s">
-        <v>331</v>
-      </c>
-      <c r="C148" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D148" t="s">
-        <v>9</v>
-      </c>
-      <c r="E148" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F148" t="s">
-        <v>332</v>
-      </c>
       <c r="G148">
-        <v>251.54</v>
+        <v>227.71</v>
       </c>
       <c r="H148">
-        <v>4.19233333333333</v>
+        <v>3.79516666666666</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B149" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C149" s="2">
         <v>46327</v>
@@ -7286,21 +7341,21 @@
         <v>46327</v>
       </c>
       <c r="F149" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G149">
-        <v>260.25</v>
+        <v>234</v>
       </c>
       <c r="H149">
-        <v>4.3375</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B150" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C150" s="2">
         <v>46327</v>
@@ -7312,21 +7367,21 @@
         <v>46327</v>
       </c>
       <c r="F150" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G150">
-        <v>355.04</v>
+        <v>285.04</v>
       </c>
       <c r="H150">
-        <v>5.91733333333333</v>
+        <v>4.75066666666666</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B151" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C151" s="2">
         <v>46327</v>
@@ -7338,21 +7393,21 @@
         <v>46327</v>
       </c>
       <c r="F151" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G151">
-        <v>271.21</v>
+        <v>283.13</v>
       </c>
       <c r="H151">
-        <v>4.52016666666666</v>
+        <v>4.71883333333333</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B152" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C152" s="2">
         <v>46327</v>
@@ -7364,99 +7419,117 @@
         <v>46327</v>
       </c>
       <c r="F152" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G152">
-        <v>230.25</v>
+        <v>236.71</v>
       </c>
       <c r="H152">
-        <v>3.8375</v>
+        <v>3.94516666666666</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
+        <v>341</v>
+      </c>
+      <c r="B153" t="s">
         <v>342</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D153" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F153" t="s">
+        <v>343</v>
+      </c>
+      <c r="G153">
+        <v>212.88</v>
+      </c>
+      <c r="H153">
+        <v>3.548</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>344</v>
+      </c>
+      <c r="B154" t="s">
         <v>345</v>
       </c>
-      <c r="C153" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F153" t="s">
+      <c r="C154" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D154" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F154" t="s">
         <v>346</v>
       </c>
-      <c r="G153">
-        <v>272.42</v>
-      </c>
-      <c r="H153">
-        <v>4.54033333333333</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
-      <c r="A154" t="s">
-        <v>93</v>
-      </c>
-      <c r="B154" t="s">
-        <v>347</v>
-      </c>
-      <c r="C154" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D154" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="3">
-        <v>46327</v>
+      <c r="G154">
+        <v>232.96</v>
+      </c>
+      <c r="H154">
+        <v>3.88266666666666</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
+        <v>347</v>
+      </c>
+      <c r="B155" t="s">
         <v>348</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D155" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F155" t="s">
         <v>349</v>
       </c>
-      <c r="C155" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F155" t="s">
+      <c r="G155">
+        <v>251.54</v>
+      </c>
+      <c r="H155">
+        <v>4.19233333333333</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
         <v>350</v>
       </c>
-      <c r="G155">
-        <v>180.13</v>
-      </c>
-      <c r="H155">
-        <v>3.00216666666666</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" t="s">
+      <c r="B156" t="s">
         <v>351</v>
       </c>
-      <c r="B156" s="11" t="s">
+      <c r="C156" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F156" t="s">
         <v>352</v>
       </c>
-      <c r="C156" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D156" t="s">
-        <v>16</v>
-      </c>
-      <c r="E156" s="3">
-        <v>46327</v>
+      <c r="G156">
+        <v>260.25</v>
+      </c>
+      <c r="H156">
+        <v>4.3375</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -7479,18 +7552,18 @@
         <v>355</v>
       </c>
       <c r="G157">
-        <v>300.13</v>
+        <v>355.04</v>
       </c>
       <c r="H157">
-        <v>5.00216666666666</v>
+        <v>5.91733333333333</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B158" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C158" s="2">
         <v>46327</v>
@@ -7502,21 +7575,21 @@
         <v>46327</v>
       </c>
       <c r="F158" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G158">
-        <v>258.21</v>
+        <v>271.21</v>
       </c>
       <c r="H158">
-        <v>4.3035</v>
+        <v>4.52016666666666</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B159" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C159" s="2">
         <v>46327</v>
@@ -7528,21 +7601,21 @@
         <v>46327</v>
       </c>
       <c r="F159" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G159">
-        <v>211.329999999999</v>
+        <v>230.25</v>
       </c>
       <c r="H159">
-        <v>3.52216666666666</v>
+        <v>3.8375</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B160" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C160" s="2">
         <v>46327</v>
@@ -7554,21 +7627,21 @@
         <v>46327</v>
       </c>
       <c r="F160" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G160">
-        <v>191.88</v>
+        <v>272.42</v>
       </c>
       <c r="H160">
-        <v>3.198</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
+        <v>4.54033333333333</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>353</v>
+        <v>93</v>
       </c>
       <c r="B161" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C161" s="2">
         <v>46327</v>
@@ -7578,23 +7651,14 @@
       </c>
       <c r="E161" s="3">
         <v>46327</v>
-      </c>
-      <c r="F161" t="s">
-        <v>363</v>
-      </c>
-      <c r="G161">
-        <v>431.42</v>
-      </c>
-      <c r="H161">
-        <v>7.19033333333333</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B162" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C162" s="2">
         <v>46327</v>
@@ -7606,47 +7670,38 @@
         <v>46327</v>
       </c>
       <c r="F162" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G162">
-        <v>147.25</v>
+        <v>180.13</v>
       </c>
       <c r="H162">
-        <v>2.45416666666666</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8">
+        <v>3.00216666666666</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>353</v>
-      </c>
-      <c r="B163" t="s">
-        <v>366</v>
+        <v>368</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>369</v>
       </c>
       <c r="C163" s="2">
         <v>46327</v>
       </c>
       <c r="D163" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E163" s="3">
         <v>46327</v>
-      </c>
-      <c r="F163" t="s">
-        <v>367</v>
-      </c>
-      <c r="G163">
-        <v>243.08</v>
-      </c>
-      <c r="H163">
-        <v>4.05133333333333</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B164" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C164" s="2">
         <v>46327</v>
@@ -7658,21 +7713,21 @@
         <v>46327</v>
       </c>
       <c r="F164" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G164">
-        <v>186.88</v>
+        <v>300.13</v>
       </c>
       <c r="H164">
-        <v>3.11466666666666</v>
+        <v>5.00216666666666</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B165" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C165" s="2">
         <v>46327</v>
@@ -7684,21 +7739,21 @@
         <v>46327</v>
       </c>
       <c r="F165" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G165">
-        <v>188</v>
+        <v>258.21</v>
       </c>
       <c r="H165">
-        <v>3.13333333333333</v>
+        <v>4.3035</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B166" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C166" s="2">
         <v>46327</v>
@@ -7710,21 +7765,21 @@
         <v>46327</v>
       </c>
       <c r="F166" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G166">
-        <v>250.63</v>
+        <v>211.329999999999</v>
       </c>
       <c r="H166">
-        <v>4.17716666666666</v>
+        <v>3.52216666666666</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B167" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C167" s="2">
         <v>46327</v>
@@ -7736,21 +7791,21 @@
         <v>46327</v>
       </c>
       <c r="F167" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G167">
-        <v>285.04</v>
+        <v>191.88</v>
       </c>
       <c r="H167">
-        <v>4.75066666666666</v>
+        <v>3.198</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B168" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C168" s="2">
         <v>46327</v>
@@ -7762,21 +7817,21 @@
         <v>46327</v>
       </c>
       <c r="F168" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G168">
-        <v>127.5</v>
+        <v>431.42</v>
       </c>
       <c r="H168">
-        <v>2.125</v>
+        <v>7.19033333333333</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B169" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C169" s="2">
         <v>46327</v>
@@ -7788,21 +7843,21 @@
         <v>46327</v>
       </c>
       <c r="F169" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G169">
-        <v>237.88</v>
+        <v>147.25</v>
       </c>
       <c r="H169">
-        <v>3.96466666666666</v>
+        <v>2.45416666666666</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B170" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C170" s="2">
         <v>46327</v>
@@ -7814,21 +7869,21 @@
         <v>46327</v>
       </c>
       <c r="F170" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G170">
-        <v>260.79</v>
+        <v>243.08</v>
       </c>
       <c r="H170">
-        <v>4.3465</v>
+        <v>4.05133333333333</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B171" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C171" s="2">
         <v>46327</v>
@@ -7840,21 +7895,21 @@
         <v>46327</v>
       </c>
       <c r="F171" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G171">
-        <v>189.79</v>
+        <v>186.88</v>
       </c>
       <c r="H171">
-        <v>3.16316666666666</v>
+        <v>3.11466666666666</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B172" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C172" s="2">
         <v>46327</v>
@@ -7866,21 +7921,21 @@
         <v>46327</v>
       </c>
       <c r="F172" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G172">
-        <v>170.79</v>
+        <v>188</v>
       </c>
       <c r="H172">
-        <v>2.8465</v>
+        <v>3.13333333333333</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B173" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C173" s="2">
         <v>46327</v>
@@ -7892,21 +7947,21 @@
         <v>46327</v>
       </c>
       <c r="F173" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G173">
-        <v>174.13</v>
+        <v>250.63</v>
       </c>
       <c r="H173">
-        <v>2.90216666666666</v>
+        <v>4.17716666666666</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B174" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C174" s="2">
         <v>46327</v>
@@ -7918,21 +7973,21 @@
         <v>46327</v>
       </c>
       <c r="F174" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G174">
-        <v>208.829999999999</v>
+        <v>285.04</v>
       </c>
       <c r="H174">
-        <v>3.48049999999999</v>
+        <v>4.75066666666666</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B175" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C175" s="2">
         <v>46327</v>
@@ -7944,21 +7999,21 @@
         <v>46327</v>
       </c>
       <c r="F175" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G175">
-        <v>287.75</v>
+        <v>127.5</v>
       </c>
       <c r="H175">
-        <v>4.79583333333333</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="B176" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C176" s="2">
         <v>46327</v>
@@ -7970,21 +8025,21 @@
         <v>46327</v>
       </c>
       <c r="F176" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G176">
-        <v>182.21</v>
+        <v>237.88</v>
       </c>
       <c r="H176">
-        <v>3.03683333333333</v>
+        <v>3.96466666666666</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="B177" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C177" s="2">
         <v>46327</v>
@@ -7996,21 +8051,21 @@
         <v>46327</v>
       </c>
       <c r="F177" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G177">
-        <v>299.25</v>
+        <v>260.79</v>
       </c>
       <c r="H177">
-        <v>4.9875</v>
+        <v>4.3465</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="B178" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C178" s="2">
         <v>46327</v>
@@ -8022,21 +8077,21 @@
         <v>46327</v>
       </c>
       <c r="F178" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G178">
-        <v>303.5</v>
+        <v>189.79</v>
       </c>
       <c r="H178">
-        <v>5.05833333333333</v>
+        <v>3.16316666666666</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="B179" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C179" s="2">
         <v>46327</v>
@@ -8048,21 +8103,21 @@
         <v>46327</v>
       </c>
       <c r="F179" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G179">
-        <v>205.079999999999</v>
+        <v>170.79</v>
       </c>
       <c r="H179">
-        <v>3.41799999999999</v>
+        <v>2.8465</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="B180" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C180" s="2">
         <v>46327</v>
@@ -8074,21 +8129,21 @@
         <v>46327</v>
       </c>
       <c r="F180" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G180">
-        <v>262.33</v>
+        <v>174.13</v>
       </c>
       <c r="H180">
-        <v>4.37216666666666</v>
+        <v>2.90216666666666</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B181" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C181" s="2">
         <v>46327</v>
@@ -8100,21 +8155,21 @@
         <v>46327</v>
       </c>
       <c r="F181" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G181">
-        <v>206.04</v>
+        <v>208.829999999999</v>
       </c>
       <c r="H181">
-        <v>3.43399999999999</v>
+        <v>3.48049999999999</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B182" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C182" s="2">
         <v>46327</v>
@@ -8126,21 +8181,21 @@
         <v>46327</v>
       </c>
       <c r="F182" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G182">
-        <v>211.13</v>
+        <v>287.75</v>
       </c>
       <c r="H182">
-        <v>3.51883333333333</v>
+        <v>4.79583333333333</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B183" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C183" s="2">
         <v>46327</v>
@@ -8152,21 +8207,21 @@
         <v>46327</v>
       </c>
       <c r="F183" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G183">
-        <v>200.54</v>
+        <v>182.21</v>
       </c>
       <c r="H183">
-        <v>3.34233333333333</v>
+        <v>3.03683333333333</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>11</v>
+        <v>395</v>
       </c>
       <c r="B184" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C184" s="2">
         <v>46327</v>
@@ -8178,21 +8233,21 @@
         <v>46327</v>
       </c>
       <c r="F184" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G184">
-        <v>170.17</v>
+        <v>299.25</v>
       </c>
       <c r="H184">
-        <v>2.83616666666666</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
+        <v>4.9875</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>412</v>
-      </c>
-      <c r="B185" s="11" t="s">
-        <v>413</v>
+        <v>395</v>
+      </c>
+      <c r="B185" t="s">
+        <v>414</v>
       </c>
       <c r="C185" s="2">
         <v>46327</v>
@@ -8202,14 +8257,23 @@
       </c>
       <c r="E185" s="3">
         <v>46327</v>
+      </c>
+      <c r="F185" t="s">
+        <v>415</v>
+      </c>
+      <c r="G185">
+        <v>303.5</v>
+      </c>
+      <c r="H185">
+        <v>5.05833333333333</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="B186" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C186" s="2">
         <v>46327</v>
@@ -8221,21 +8285,21 @@
         <v>46327</v>
       </c>
       <c r="F186" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G186">
-        <v>169.13</v>
+        <v>205.079999999999</v>
       </c>
       <c r="H186">
-        <v>2.81883333333333</v>
+        <v>3.41799999999999</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="B187" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C187" s="2">
         <v>46327</v>
@@ -8247,21 +8311,21 @@
         <v>46327</v>
       </c>
       <c r="F187" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G187">
-        <v>151.54</v>
+        <v>262.33</v>
       </c>
       <c r="H187">
-        <v>2.52566666666666</v>
+        <v>4.37216666666666</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B188" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C188" s="2">
         <v>46327</v>
@@ -8273,21 +8337,21 @@
         <v>46327</v>
       </c>
       <c r="F188" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G188">
-        <v>369.83</v>
+        <v>206.04</v>
       </c>
       <c r="H188">
-        <v>6.16383333333333</v>
+        <v>3.43399999999999</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B189" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C189" s="2">
         <v>46327</v>
@@ -8299,21 +8363,21 @@
         <v>46327</v>
       </c>
       <c r="F189" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G189">
-        <v>332.13</v>
+        <v>211.13</v>
       </c>
       <c r="H189">
-        <v>5.5355</v>
+        <v>3.51883333333333</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B190" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C190" s="2">
         <v>46327</v>
@@ -8325,21 +8389,21 @@
         <v>46327</v>
       </c>
       <c r="F190" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G190">
-        <v>267.92</v>
+        <v>200.54</v>
       </c>
       <c r="H190">
-        <v>4.46533333333333</v>
+        <v>3.34233333333333</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>414</v>
+        <v>11</v>
       </c>
       <c r="B191" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C191" s="2">
         <v>46327</v>
@@ -8351,21 +8415,21 @@
         <v>46327</v>
       </c>
       <c r="F191" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G191">
-        <v>196.63</v>
+        <v>170.17</v>
       </c>
       <c r="H191">
-        <v>3.27716666666666</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8">
+        <v>2.83616666666666</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>427</v>
-      </c>
-      <c r="B192" t="s">
-        <v>428</v>
+        <v>429</v>
+      </c>
+      <c r="B192" s="11" t="s">
+        <v>430</v>
       </c>
       <c r="C192" s="2">
         <v>46327</v>
@@ -8375,23 +8439,14 @@
       </c>
       <c r="E192" s="3">
         <v>46327</v>
-      </c>
-      <c r="F192" t="s">
-        <v>429</v>
-      </c>
-      <c r="G192">
-        <v>413.38</v>
-      </c>
-      <c r="H192">
-        <v>6.88966666666666</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B193" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C193" s="2">
         <v>46327</v>
@@ -8403,18 +8458,18 @@
         <v>46327</v>
       </c>
       <c r="F193" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G193">
-        <v>333.96</v>
+        <v>169.13</v>
       </c>
       <c r="H193">
-        <v>5.566</v>
+        <v>2.81883333333333</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B194" t="s">
         <v>434</v>
@@ -8432,70 +8487,70 @@
         <v>435</v>
       </c>
       <c r="G194">
-        <v>254.13</v>
+        <v>151.54</v>
       </c>
       <c r="H194">
-        <v>4.2355</v>
+        <v>2.52566666666666</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
+        <v>431</v>
+      </c>
+      <c r="B195" t="s">
         <v>436</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D195" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F195" t="s">
         <v>437</v>
       </c>
-      <c r="C195" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D195" t="s">
-        <v>9</v>
-      </c>
-      <c r="E195" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F195" t="s">
-        <v>438</v>
-      </c>
       <c r="G195">
-        <v>233.38</v>
+        <v>369.83</v>
       </c>
       <c r="H195">
-        <v>3.88966666666666</v>
+        <v>6.16383333333333</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
+        <v>431</v>
+      </c>
+      <c r="B196" t="s">
+        <v>438</v>
+      </c>
+      <c r="C196" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D196" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F196" t="s">
         <v>439</v>
       </c>
-      <c r="B196" t="s">
-        <v>440</v>
-      </c>
-      <c r="C196" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D196" t="s">
-        <v>9</v>
-      </c>
-      <c r="E196" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F196" t="s">
-        <v>441</v>
-      </c>
       <c r="G196">
-        <v>231.79</v>
+        <v>332.13</v>
       </c>
       <c r="H196">
-        <v>3.86316666666666</v>
+        <v>5.5355</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="B197" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C197" s="2">
         <v>46327</v>
@@ -8507,21 +8562,21 @@
         <v>46327</v>
       </c>
       <c r="F197" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G197">
-        <v>248.88</v>
+        <v>267.92</v>
       </c>
       <c r="H197">
-        <v>4.148</v>
+        <v>4.46533333333333</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="B198" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C198" s="2">
         <v>46327</v>
@@ -8533,21 +8588,21 @@
         <v>46327</v>
       </c>
       <c r="F198" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G198">
-        <v>284.96</v>
+        <v>196.63</v>
       </c>
       <c r="H198">
-        <v>4.74933333333333</v>
+        <v>3.27716666666666</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B199" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C199" s="2">
         <v>46327</v>
@@ -8559,21 +8614,21 @@
         <v>46327</v>
       </c>
       <c r="F199" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G199">
-        <v>254.71</v>
+        <v>413.38</v>
       </c>
       <c r="H199">
-        <v>4.24516666666666</v>
+        <v>6.88966666666666</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B200" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C200" s="2">
         <v>46327</v>
@@ -8585,22 +8640,22 @@
         <v>46327</v>
       </c>
       <c r="F200" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G200">
-        <v>216.71</v>
+        <v>333.96</v>
       </c>
       <c r="H200">
-        <v>3.61183333333333</v>
+        <v>5.566</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
+        <v>450</v>
+      </c>
+      <c r="B201" t="s">
         <v>451</v>
       </c>
-      <c r="B201" t="s">
-        <v>454</v>
-      </c>
       <c r="C201" s="2">
         <v>46327</v>
       </c>
@@ -8611,21 +8666,21 @@
         <v>46327</v>
       </c>
       <c r="F201" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G201">
-        <v>151</v>
+        <v>254.13</v>
       </c>
       <c r="H201">
-        <v>2.51666666666666</v>
+        <v>4.2355</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B202" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C202" s="2">
         <v>46327</v>
@@ -8637,44 +8692,44 @@
         <v>46327</v>
       </c>
       <c r="F202" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G202">
-        <v>188.42</v>
+        <v>233.38</v>
       </c>
       <c r="H202">
-        <v>3.14033333333333</v>
+        <v>3.88966666666666</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B203" t="s">
+        <v>457</v>
+      </c>
+      <c r="C203" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D203" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F203" t="s">
         <v>458</v>
       </c>
-      <c r="C203" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D203" t="s">
-        <v>9</v>
-      </c>
-      <c r="E203" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F203" t="s">
-        <v>459</v>
-      </c>
       <c r="G203">
-        <v>188.08</v>
+        <v>231.79</v>
       </c>
       <c r="H203">
-        <v>3.13466666666666</v>
+        <v>3.86316666666666</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="B204" t="s">
         <v>460</v>
@@ -8692,18 +8747,18 @@
         <v>461</v>
       </c>
       <c r="G204">
-        <v>153.38</v>
+        <v>248.88</v>
       </c>
       <c r="H204">
-        <v>2.55633333333333</v>
+        <v>4.148</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B205" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C205" s="2">
         <v>46327</v>
@@ -8715,21 +8770,21 @@
         <v>46327</v>
       </c>
       <c r="F205" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G205">
-        <v>198.5</v>
+        <v>284.96</v>
       </c>
       <c r="H205">
-        <v>3.30833333333333</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
+        <v>4.74933333333333</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
       <c r="A206" t="s">
-        <v>96</v>
-      </c>
-      <c r="B206" s="15" t="s">
-        <v>464</v>
+        <v>465</v>
+      </c>
+      <c r="B206" t="s">
+        <v>466</v>
       </c>
       <c r="C206" s="2">
         <v>46327</v>
@@ -8740,47 +8795,74 @@
       <c r="E206" s="3">
         <v>46327</v>
       </c>
-    </row>
-    <row r="207" spans="1:5">
+      <c r="F206" t="s">
+        <v>467</v>
+      </c>
+      <c r="G206">
+        <v>254.71</v>
+      </c>
+      <c r="H206">
+        <v>4.24516666666666</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>96</v>
+        <v>468</v>
       </c>
       <c r="B207" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C207" s="2">
         <v>46327</v>
       </c>
       <c r="D207" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E207" s="3">
         <v>46327</v>
       </c>
-    </row>
-    <row r="208" spans="1:5">
+      <c r="F207" t="s">
+        <v>470</v>
+      </c>
+      <c r="G207">
+        <v>216.71</v>
+      </c>
+      <c r="H207">
+        <v>3.61183333333333</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>96</v>
+        <v>468</v>
       </c>
       <c r="B208" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C208" s="2">
         <v>46327</v>
       </c>
       <c r="D208" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E208" s="3">
         <v>46327</v>
+      </c>
+      <c r="F208" t="s">
+        <v>472</v>
+      </c>
+      <c r="G208">
+        <v>151</v>
+      </c>
+      <c r="H208">
+        <v>2.51666666666666</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B209" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C209" s="2">
         <v>46327</v>
@@ -8792,21 +8874,21 @@
         <v>46327</v>
       </c>
       <c r="F209" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="G209">
-        <v>220.75</v>
+        <v>188.42</v>
       </c>
       <c r="H209">
-        <v>3.67916666666666</v>
+        <v>3.14033333333333</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B210" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C210" s="2">
         <v>46327</v>
@@ -8818,21 +8900,21 @@
         <v>46327</v>
       </c>
       <c r="F210" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G210">
-        <v>236.829999999999</v>
+        <v>188.08</v>
       </c>
       <c r="H210">
-        <v>3.94716666666666</v>
+        <v>3.13466666666666</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B211" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C211" s="2">
         <v>46327</v>
@@ -8844,21 +8926,21 @@
         <v>46327</v>
       </c>
       <c r="F211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="G211">
-        <v>214.21</v>
+        <v>153.38</v>
       </c>
       <c r="H211">
-        <v>3.57016666666666</v>
+        <v>2.55633333333333</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B212" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C212" s="2">
         <v>46327</v>
@@ -8870,21 +8952,21 @@
         <v>46327</v>
       </c>
       <c r="F212" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G212">
-        <v>454.25</v>
+        <v>198.5</v>
       </c>
       <c r="H212">
-        <v>7.57083333333333</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8">
+        <v>3.30833333333333</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>474</v>
-      </c>
-      <c r="B213" t="s">
-        <v>477</v>
+        <v>96</v>
+      </c>
+      <c r="B213" s="15" t="s">
+        <v>481</v>
       </c>
       <c r="C213" s="2">
         <v>46327</v>
@@ -8895,74 +8977,47 @@
       <c r="E213" s="3">
         <v>46327</v>
       </c>
-      <c r="F213" t="s">
-        <v>478</v>
-      </c>
-      <c r="G213">
-        <v>330.5</v>
-      </c>
-      <c r="H213">
-        <v>5.50833333333333</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8">
+    </row>
+    <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>474</v>
+        <v>96</v>
       </c>
       <c r="B214" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C214" s="2">
         <v>46327</v>
       </c>
       <c r="D214" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E214" s="3">
         <v>46327</v>
       </c>
-      <c r="F214" t="s">
-        <v>480</v>
-      </c>
-      <c r="G214">
-        <v>208.88</v>
-      </c>
-      <c r="H214">
-        <v>3.48133333333333</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8">
+    </row>
+    <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>481</v>
+        <v>96</v>
       </c>
       <c r="B215" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C215" s="2">
         <v>46327</v>
       </c>
       <c r="D215" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E215" s="3">
         <v>46327</v>
-      </c>
-      <c r="F215" t="s">
-        <v>483</v>
-      </c>
-      <c r="G215">
-        <v>234.079999999999</v>
-      </c>
-      <c r="H215">
-        <v>3.90133333333333</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B216" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C216" s="2">
         <v>46327</v>
@@ -8974,21 +9029,21 @@
         <v>46327</v>
       </c>
       <c r="F216" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G216">
-        <v>235.54</v>
+        <v>220.75</v>
       </c>
       <c r="H216">
-        <v>3.92566666666666</v>
+        <v>3.67916666666666</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B217" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C217" s="2">
         <v>46327</v>
@@ -9000,18 +9055,18 @@
         <v>46327</v>
       </c>
       <c r="F217" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G217">
-        <v>296.13</v>
+        <v>236.829999999999</v>
       </c>
       <c r="H217">
-        <v>4.9355</v>
+        <v>3.94716666666666</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B218" t="s">
         <v>489</v>
@@ -9029,10 +9084,10 @@
         <v>490</v>
       </c>
       <c r="G218">
-        <v>186.46</v>
+        <v>214.21</v>
       </c>
       <c r="H218">
-        <v>3.10766666666666</v>
+        <v>3.57016666666666</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -9055,10 +9110,10 @@
         <v>493</v>
       </c>
       <c r="G219">
-        <v>237.96</v>
+        <v>454.25</v>
       </c>
       <c r="H219">
-        <v>3.966</v>
+        <v>7.57083333333333</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -9066,7 +9121,7 @@
         <v>491</v>
       </c>
       <c r="B220" t="s">
-        <v>337</v>
+        <v>494</v>
       </c>
       <c r="C220" s="2">
         <v>46327</v>
@@ -9078,13 +9133,13 @@
         <v>46327</v>
       </c>
       <c r="F220" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G220">
-        <v>277.08</v>
+        <v>330.5</v>
       </c>
       <c r="H220">
-        <v>4.61799999999999</v>
+        <v>5.50833333333333</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -9092,7 +9147,7 @@
         <v>491</v>
       </c>
       <c r="B221" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C221" s="2">
         <v>46327</v>
@@ -9104,21 +9159,21 @@
         <v>46327</v>
       </c>
       <c r="F221" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G221">
-        <v>209.88</v>
+        <v>208.88</v>
       </c>
       <c r="H221">
-        <v>3.49799999999999</v>
+        <v>3.48133333333333</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B222" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C222" s="2">
         <v>46327</v>
@@ -9130,21 +9185,21 @@
         <v>46327</v>
       </c>
       <c r="F222" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G222">
-        <v>280.54</v>
+        <v>234.079999999999</v>
       </c>
       <c r="H222">
-        <v>4.67566666666666</v>
+        <v>3.90133333333333</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B223" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C223" s="2">
         <v>46327</v>
@@ -9156,21 +9211,21 @@
         <v>46327</v>
       </c>
       <c r="F223" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G223">
-        <v>287.67</v>
+        <v>235.54</v>
       </c>
       <c r="H223">
-        <v>4.7945</v>
+        <v>3.92566666666666</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B224" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C224" s="2">
         <v>46327</v>
@@ -9182,21 +9237,21 @@
         <v>46327</v>
       </c>
       <c r="F224" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G224">
-        <v>274.71</v>
+        <v>296.13</v>
       </c>
       <c r="H224">
-        <v>4.5785</v>
+        <v>4.9355</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B225" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C225" s="2">
         <v>46327</v>
@@ -9208,21 +9263,21 @@
         <v>46327</v>
       </c>
       <c r="F225" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G225">
-        <v>161.13</v>
+        <v>186.46</v>
       </c>
       <c r="H225">
-        <v>2.68549999999999</v>
+        <v>3.10766666666666</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B226" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C226" s="2">
         <v>46327</v>
@@ -9234,21 +9289,21 @@
         <v>46327</v>
       </c>
       <c r="F226" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G226">
-        <v>176.96</v>
+        <v>237.96</v>
       </c>
       <c r="H226">
-        <v>2.94933333333333</v>
+        <v>3.966</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B227" t="s">
-        <v>508</v>
+        <v>354</v>
       </c>
       <c r="C227" s="2">
         <v>46327</v>
@@ -9260,21 +9315,21 @@
         <v>46327</v>
       </c>
       <c r="F227" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G227">
-        <v>193.75</v>
+        <v>277.08</v>
       </c>
       <c r="H227">
-        <v>3.22916666666666</v>
+        <v>4.61799999999999</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" t="s">
-        <v>292</v>
+        <v>508</v>
       </c>
       <c r="B228" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C228" s="2">
         <v>46327</v>
@@ -9286,21 +9341,21 @@
         <v>46327</v>
       </c>
       <c r="F228" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G228">
-        <v>255.96</v>
+        <v>209.88</v>
       </c>
       <c r="H228">
-        <v>4.266</v>
+        <v>3.49799999999999</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" t="s">
-        <v>292</v>
+        <v>508</v>
       </c>
       <c r="B229" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C229" s="2">
         <v>46327</v>
@@ -9312,21 +9367,21 @@
         <v>46327</v>
       </c>
       <c r="F229" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G229">
-        <v>242.25</v>
+        <v>280.54</v>
       </c>
       <c r="H229">
-        <v>4.0375</v>
+        <v>4.67566666666666</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B230" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C230" s="2">
         <v>46327</v>
@@ -9338,21 +9393,21 @@
         <v>46327</v>
       </c>
       <c r="F230" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G230">
-        <v>253.33</v>
+        <v>287.67</v>
       </c>
       <c r="H230">
-        <v>4.22216666666666</v>
+        <v>4.7945</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B231" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C231" s="2">
         <v>46327</v>
@@ -9364,21 +9419,21 @@
         <v>46327</v>
       </c>
       <c r="F231" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G231">
-        <v>277.46</v>
+        <v>274.71</v>
       </c>
       <c r="H231">
-        <v>4.62433333333333</v>
+        <v>4.5785</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B232" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C232" s="2">
         <v>46327</v>
@@ -9390,21 +9445,21 @@
         <v>46327</v>
       </c>
       <c r="F232" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G232">
-        <v>307.25</v>
+        <v>161.13</v>
       </c>
       <c r="H232">
-        <v>5.12083333333333</v>
+        <v>2.68549999999999</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B233" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C233" s="2">
         <v>46327</v>
@@ -9416,21 +9471,21 @@
         <v>46327</v>
       </c>
       <c r="F233" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G233">
-        <v>135.17</v>
+        <v>176.96</v>
       </c>
       <c r="H233">
-        <v>2.25283333333333</v>
+        <v>2.94933333333333</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B234" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C234" s="2">
         <v>46327</v>
@@ -9442,21 +9497,21 @@
         <v>46327</v>
       </c>
       <c r="F234" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G234">
-        <v>178.38</v>
+        <v>193.75</v>
       </c>
       <c r="H234">
-        <v>2.973</v>
+        <v>3.22916666666666</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>521</v>
+        <v>292</v>
       </c>
       <c r="B235" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C235" s="2">
         <v>46327</v>
@@ -9468,21 +9523,21 @@
         <v>46327</v>
       </c>
       <c r="F235" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G235">
-        <v>137.13</v>
+        <v>255.96</v>
       </c>
       <c r="H235">
-        <v>2.2855</v>
+        <v>4.266</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" t="s">
-        <v>521</v>
+        <v>292</v>
       </c>
       <c r="B236" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C236" s="2">
         <v>46327</v>
@@ -9494,21 +9549,21 @@
         <v>46327</v>
       </c>
       <c r="F236" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G236">
-        <v>160.25</v>
+        <v>242.25</v>
       </c>
       <c r="H236">
-        <v>2.67083333333333</v>
+        <v>4.0375</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="B237" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C237" s="2">
         <v>46327</v>
@@ -9520,21 +9575,21 @@
         <v>46327</v>
       </c>
       <c r="F237" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G237">
-        <v>184.46</v>
+        <v>253.33</v>
       </c>
       <c r="H237">
-        <v>3.07433333333333</v>
+        <v>4.22216666666666</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="B238" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C238" s="2">
         <v>46327</v>
@@ -9546,21 +9601,21 @@
         <v>46327</v>
       </c>
       <c r="F238" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G238">
-        <v>144.04</v>
+        <v>277.46</v>
       </c>
       <c r="H238">
-        <v>2.40066666666666</v>
+        <v>4.62433333333333</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B239" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C239" s="2">
         <v>46327</v>
@@ -9572,21 +9627,21 @@
         <v>46327</v>
       </c>
       <c r="F239" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G239">
-        <v>185.88</v>
+        <v>307.25</v>
       </c>
       <c r="H239">
-        <v>3.098</v>
+        <v>5.12083333333333</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B240" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C240" s="2">
         <v>46327</v>
@@ -9598,21 +9653,21 @@
         <v>46327</v>
       </c>
       <c r="F240" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G240">
-        <v>174.17</v>
+        <v>135.17</v>
       </c>
       <c r="H240">
-        <v>2.90283333333333</v>
+        <v>2.25283333333333</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B241" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C241" s="2">
         <v>46327</v>
@@ -9624,21 +9679,21 @@
         <v>46327</v>
       </c>
       <c r="F241" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G241">
-        <v>232.5</v>
+        <v>178.38</v>
       </c>
       <c r="H241">
-        <v>3.875</v>
+        <v>2.973</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B242" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C242" s="2">
         <v>46327</v>
@@ -9650,21 +9705,21 @@
         <v>46327</v>
       </c>
       <c r="F242" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G242">
-        <v>269.54</v>
+        <v>137.13</v>
       </c>
       <c r="H242">
-        <v>4.49233333333333</v>
+        <v>2.2855</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B243" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C243" s="2">
         <v>46327</v>
@@ -9676,21 +9731,21 @@
         <v>46327</v>
       </c>
       <c r="F243" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G243">
-        <v>238.5</v>
+        <v>160.25</v>
       </c>
       <c r="H243">
-        <v>3.975</v>
+        <v>2.67083333333333</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B244" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C244" s="2">
         <v>46327</v>
@@ -9702,18 +9757,18 @@
         <v>46327</v>
       </c>
       <c r="F244" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G244">
-        <v>219.25</v>
+        <v>184.46</v>
       </c>
       <c r="H244">
-        <v>3.65416666666666</v>
+        <v>3.07433333333333</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="B245" t="s">
         <v>549</v>
@@ -9731,18 +9786,18 @@
         <v>550</v>
       </c>
       <c r="G245">
-        <v>266.83</v>
+        <v>144.04</v>
       </c>
       <c r="H245">
-        <v>4.44716666666666</v>
+        <v>2.40066666666666</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B246" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C246" s="2">
         <v>46327</v>
@@ -9754,21 +9809,21 @@
         <v>46327</v>
       </c>
       <c r="F246" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G246">
-        <v>297.08</v>
+        <v>185.88</v>
       </c>
       <c r="H246">
-        <v>4.95133333333333</v>
+        <v>3.098</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B247" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C247" s="2">
         <v>46327</v>
@@ -9780,18 +9835,18 @@
         <v>46327</v>
       </c>
       <c r="F247" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G247">
-        <v>246.5</v>
+        <v>174.17</v>
       </c>
       <c r="H247">
-        <v>4.10833333333333</v>
+        <v>2.90283333333333</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B248" t="s">
         <v>556</v>
@@ -9809,18 +9864,18 @@
         <v>557</v>
       </c>
       <c r="G248">
-        <v>266</v>
+        <v>232.5</v>
       </c>
       <c r="H248">
-        <v>4.43333333333333</v>
+        <v>3.875</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B249" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C249" s="2">
         <v>46327</v>
@@ -9832,21 +9887,21 @@
         <v>46327</v>
       </c>
       <c r="F249" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G249">
-        <v>309.29</v>
+        <v>269.54</v>
       </c>
       <c r="H249">
-        <v>5.15483333333333</v>
+        <v>4.49233333333333</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B250" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C250" s="2">
         <v>46327</v>
@@ -9858,18 +9913,18 @@
         <v>46327</v>
       </c>
       <c r="F250" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G250">
-        <v>251.04</v>
+        <v>238.5</v>
       </c>
       <c r="H250">
-        <v>4.184</v>
+        <v>3.975</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B251" t="s">
         <v>563</v>
@@ -9887,17 +9942,17 @@
         <v>564</v>
       </c>
       <c r="G251">
-        <v>236.04</v>
+        <v>219.25</v>
       </c>
       <c r="H251">
-        <v>3.93399999999999</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5">
+        <v>3.65416666666666</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
       <c r="A252" t="s">
         <v>565</v>
       </c>
-      <c r="B252" s="10" t="s">
+      <c r="B252" t="s">
         <v>566</v>
       </c>
       <c r="C252" s="2">
@@ -9908,11 +9963,20 @@
       </c>
       <c r="E252" s="3">
         <v>46327</v>
+      </c>
+      <c r="F252" t="s">
+        <v>567</v>
+      </c>
+      <c r="G252">
+        <v>266.83</v>
+      </c>
+      <c r="H252">
+        <v>4.44716666666666</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B253" t="s">
         <v>568</v>
@@ -9930,15 +9994,15 @@
         <v>569</v>
       </c>
       <c r="G253">
-        <v>615.54</v>
+        <v>297.08</v>
       </c>
       <c r="H253">
-        <v>10.2589999999999</v>
+        <v>4.95133333333333</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B254" t="s">
         <v>570</v>
@@ -9956,18 +10020,18 @@
         <v>571</v>
       </c>
       <c r="G254">
-        <v>367.42</v>
+        <v>246.5</v>
       </c>
       <c r="H254">
-        <v>6.12366666666666</v>
+        <v>4.10833333333333</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B255" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C255" s="2">
         <v>46327</v>
@@ -9979,18 +10043,18 @@
         <v>46327</v>
       </c>
       <c r="F255" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G255">
-        <v>342.08</v>
+        <v>266</v>
       </c>
       <c r="H255">
-        <v>5.70133333333333</v>
+        <v>4.43333333333333</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B256" t="s">
         <v>575</v>
@@ -10008,15 +10072,15 @@
         <v>576</v>
       </c>
       <c r="G256">
-        <v>221.21</v>
+        <v>309.29</v>
       </c>
       <c r="H256">
-        <v>3.68683333333333</v>
+        <v>5.15483333333333</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B257" t="s">
         <v>577</v>
@@ -10034,18 +10098,18 @@
         <v>578</v>
       </c>
       <c r="G257">
-        <v>193.71</v>
+        <v>251.04</v>
       </c>
       <c r="H257">
-        <v>3.2285</v>
+        <v>4.184</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B258" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C258" s="2">
         <v>46327</v>
@@ -10057,27 +10121,27 @@
         <v>46327</v>
       </c>
       <c r="F258" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G258">
-        <v>221.25</v>
+        <v>236.04</v>
       </c>
       <c r="H258">
-        <v>3.6875</v>
+        <v>3.93399999999999</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>581</v>
-      </c>
-      <c r="B259" t="s">
         <v>582</v>
       </c>
+      <c r="B259" s="10" t="s">
+        <v>583</v>
+      </c>
       <c r="C259" s="2">
         <v>46327</v>
       </c>
       <c r="D259" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E259" s="3">
         <v>46327</v>
@@ -10085,36 +10149,36 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
-        <v>18</v>
+        <v>584</v>
       </c>
       <c r="B260" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C260" s="2">
         <v>46327</v>
       </c>
       <c r="D260" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E260" s="3">
         <v>46327</v>
       </c>
       <c r="F260" t="s">
-        <v>20</v>
+        <v>586</v>
       </c>
       <c r="G260">
-        <v>181.25</v>
+        <v>615.54</v>
       </c>
       <c r="H260">
-        <v>3.02083333333333</v>
+        <v>10.2589999999999</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>169</v>
+        <v>584</v>
       </c>
       <c r="B261" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C261" s="2">
         <v>46327</v>
@@ -10126,21 +10190,21 @@
         <v>46327</v>
       </c>
       <c r="F261" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="G261">
-        <v>211.329999999999</v>
+        <v>367.42</v>
       </c>
       <c r="H261">
-        <v>3.52216666666666</v>
+        <v>6.12366666666666</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" t="s">
-        <v>169</v>
+        <v>584</v>
       </c>
       <c r="B262" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C262" s="2">
         <v>46327</v>
@@ -10152,21 +10216,21 @@
         <v>46327</v>
       </c>
       <c r="F262" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G262">
-        <v>583.67</v>
+        <v>342.08</v>
       </c>
       <c r="H262">
-        <v>9.72783333333333</v>
+        <v>5.70133333333333</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
-        <v>169</v>
+        <v>591</v>
       </c>
       <c r="B263" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C263" s="2">
         <v>46327</v>
@@ -10178,21 +10242,21 @@
         <v>46327</v>
       </c>
       <c r="F263" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="G263">
-        <v>377.88</v>
+        <v>221.21</v>
       </c>
       <c r="H263">
-        <v>6.298</v>
+        <v>3.68683333333333</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" t="s">
-        <v>169</v>
+        <v>591</v>
       </c>
       <c r="B264" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C264" s="2">
         <v>46327</v>
@@ -10204,21 +10268,21 @@
         <v>46327</v>
       </c>
       <c r="F264" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G264">
-        <v>257.92</v>
+        <v>193.71</v>
       </c>
       <c r="H264">
-        <v>4.29866666666666</v>
+        <v>3.2285</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" t="s">
-        <v>169</v>
+        <v>591</v>
       </c>
       <c r="B265" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C265" s="2">
         <v>46327</v>
@@ -10230,73 +10294,64 @@
         <v>46327</v>
       </c>
       <c r="F265" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="G265">
-        <v>173.17</v>
+        <v>221.25</v>
       </c>
       <c r="H265">
-        <v>2.88616666666666</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8">
+        <v>3.6875</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>100</v>
+        <v>598</v>
       </c>
       <c r="B266" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C266" s="2">
         <v>46327</v>
       </c>
       <c r="D266" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E266" s="3">
         <v>46327</v>
-      </c>
-      <c r="F266" t="s">
-        <v>595</v>
-      </c>
-      <c r="G266">
-        <v>263.33</v>
-      </c>
-      <c r="H266">
-        <v>4.38883333333333</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="B267" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C267" s="2">
         <v>46327</v>
       </c>
       <c r="D267" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E267" s="3">
         <v>46327</v>
       </c>
       <c r="F267" t="s">
-        <v>597</v>
+        <v>20</v>
       </c>
       <c r="G267">
-        <v>277.75</v>
+        <v>181.25</v>
       </c>
       <c r="H267">
-        <v>4.62916666666666</v>
+        <v>3.02083333333333</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" t="s">
-        <v>598</v>
+        <v>169</v>
       </c>
       <c r="B268" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C268" s="2">
         <v>46327</v>
@@ -10308,21 +10363,21 @@
         <v>46327</v>
       </c>
       <c r="F268" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G268">
-        <v>348.75</v>
+        <v>211.329999999999</v>
       </c>
       <c r="H268">
-        <v>5.8125</v>
+        <v>3.52216666666666</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" t="s">
-        <v>598</v>
+        <v>169</v>
       </c>
       <c r="B269" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C269" s="2">
         <v>46327</v>
@@ -10334,21 +10389,21 @@
         <v>46327</v>
       </c>
       <c r="F269" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G269">
-        <v>237.63</v>
+        <v>583.67</v>
       </c>
       <c r="H269">
-        <v>3.9605</v>
+        <v>9.72783333333333</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" t="s">
-        <v>598</v>
+        <v>169</v>
       </c>
       <c r="B270" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C270" s="2">
         <v>46327</v>
@@ -10360,21 +10415,21 @@
         <v>46327</v>
       </c>
       <c r="F270" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G270">
-        <v>254.25</v>
+        <v>377.88</v>
       </c>
       <c r="H270">
-        <v>4.2375</v>
+        <v>6.298</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" t="s">
-        <v>598</v>
+        <v>169</v>
       </c>
       <c r="B271" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C271" s="2">
         <v>46327</v>
@@ -10386,21 +10441,21 @@
         <v>46327</v>
       </c>
       <c r="F271" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G271">
-        <v>214.54</v>
+        <v>257.92</v>
       </c>
       <c r="H271">
-        <v>3.57566666666666</v>
+        <v>4.29866666666666</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
-        <v>598</v>
+        <v>169</v>
       </c>
       <c r="B272" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C272" s="2">
         <v>46327</v>
@@ -10412,21 +10467,21 @@
         <v>46327</v>
       </c>
       <c r="F272" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G272">
-        <v>346.75</v>
+        <v>173.17</v>
       </c>
       <c r="H272">
-        <v>5.77916666666666</v>
+        <v>2.88616666666666</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>598</v>
+        <v>100</v>
       </c>
       <c r="B273" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C273" s="2">
         <v>46327</v>
@@ -10438,21 +10493,21 @@
         <v>46327</v>
       </c>
       <c r="F273" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G273">
-        <v>192.88</v>
+        <v>263.33</v>
       </c>
       <c r="H273">
-        <v>3.21466666666666</v>
+        <v>4.38883333333333</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>598</v>
+        <v>100</v>
       </c>
       <c r="B274" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C274" s="2">
         <v>46327</v>
@@ -10464,21 +10519,21 @@
         <v>46327</v>
       </c>
       <c r="F274" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G274">
-        <v>292.58</v>
+        <v>277.75</v>
       </c>
       <c r="H274">
-        <v>4.87633333333333</v>
+        <v>4.62916666666666</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="B275" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C275" s="2">
         <v>46327</v>
@@ -10490,21 +10545,21 @@
         <v>46327</v>
       </c>
       <c r="F275" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="G275">
-        <v>282.21</v>
+        <v>348.75</v>
       </c>
       <c r="H275">
-        <v>4.7035</v>
+        <v>5.8125</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="B276" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C276" s="2">
         <v>46327</v>
@@ -10516,21 +10571,21 @@
         <v>46327</v>
       </c>
       <c r="F276" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="G276">
-        <v>281.88</v>
+        <v>237.63</v>
       </c>
       <c r="H276">
-        <v>4.69799999999999</v>
+        <v>3.9605</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="B277" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C277" s="2">
         <v>46327</v>
@@ -10542,21 +10597,21 @@
         <v>46327</v>
       </c>
       <c r="F277" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="G277">
-        <v>246.63</v>
+        <v>254.25</v>
       </c>
       <c r="H277">
-        <v>4.1105</v>
+        <v>4.2375</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="B278" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C278" s="2">
         <v>46327</v>
@@ -10568,21 +10623,21 @@
         <v>46327</v>
       </c>
       <c r="F278" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="G278">
-        <v>406.63</v>
+        <v>214.54</v>
       </c>
       <c r="H278">
-        <v>6.77716666666666</v>
+        <v>3.57566666666666</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="B279" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C279" s="2">
         <v>46327</v>
@@ -10594,21 +10649,21 @@
         <v>46327</v>
       </c>
       <c r="F279" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="G279">
-        <v>228.42</v>
+        <v>346.75</v>
       </c>
       <c r="H279">
-        <v>3.807</v>
+        <v>5.77916666666666</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" t="s">
-        <v>233</v>
+        <v>615</v>
       </c>
       <c r="B280" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C280" s="2">
         <v>46327</v>
@@ -10620,21 +10675,21 @@
         <v>46327</v>
       </c>
       <c r="F280" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="G280">
-        <v>134</v>
+        <v>192.88</v>
       </c>
       <c r="H280">
-        <v>2.23333333333333</v>
+        <v>3.21466666666666</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" t="s">
-        <v>233</v>
+        <v>615</v>
       </c>
       <c r="B281" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C281" s="2">
         <v>46327</v>
@@ -10646,21 +10701,21 @@
         <v>46327</v>
       </c>
       <c r="F281" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="G281">
-        <v>152.29</v>
+        <v>292.58</v>
       </c>
       <c r="H281">
-        <v>2.53816666666666</v>
+        <v>4.87633333333333</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="B282" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C282" s="2">
         <v>46327</v>
@@ -10672,21 +10727,21 @@
         <v>46327</v>
       </c>
       <c r="F282" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="G282">
-        <v>320.46</v>
+        <v>282.21</v>
       </c>
       <c r="H282">
-        <v>5.34099999999999</v>
+        <v>4.7035</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="B283" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C283" s="2">
         <v>46327</v>
@@ -10698,21 +10753,21 @@
         <v>46327</v>
       </c>
       <c r="F283" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G283">
-        <v>257.96</v>
+        <v>281.88</v>
       </c>
       <c r="H283">
-        <v>4.29933333333333</v>
+        <v>4.69799999999999</v>
       </c>
     </row>
     <row r="284" spans="1:8">
       <c r="A284" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="B284" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C284" s="2">
         <v>46327</v>
@@ -10724,18 +10779,18 @@
         <v>46327</v>
       </c>
       <c r="F284" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G284">
-        <v>488.75</v>
+        <v>246.63</v>
       </c>
       <c r="H284">
-        <v>8.14583333333333</v>
+        <v>4.1105</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="A285" t="s">
-        <v>635</v>
+        <v>615</v>
       </c>
       <c r="B285" t="s">
         <v>636</v>
@@ -10753,223 +10808,226 @@
         <v>637</v>
       </c>
       <c r="G285">
-        <v>216.71</v>
+        <v>406.63</v>
       </c>
       <c r="H285">
-        <v>3.61183333333333</v>
+        <v>6.77716666666666</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" t="s">
+        <v>615</v>
+      </c>
+      <c r="B286" t="s">
         <v>638</v>
       </c>
-      <c r="B286" t="s">
+      <c r="C286" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D286" t="s">
+        <v>9</v>
+      </c>
+      <c r="E286" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F286" t="s">
         <v>639</v>
       </c>
-      <c r="C286" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D286" t="s">
-        <v>16</v>
-      </c>
-      <c r="E286" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F286" t="s">
-        <v>640</v>
-      </c>
       <c r="G286">
-        <v>384.58</v>
+        <v>228.42</v>
       </c>
       <c r="H286">
-        <v>6.40966666666666</v>
+        <v>3.807</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" t="s">
-        <v>638</v>
+        <v>233</v>
       </c>
       <c r="B287" t="s">
+        <v>640</v>
+      </c>
+      <c r="C287" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D287" t="s">
+        <v>9</v>
+      </c>
+      <c r="E287" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F287" t="s">
         <v>641</v>
       </c>
-      <c r="C287" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D287" t="s">
-        <v>9</v>
-      </c>
-      <c r="E287" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F287" t="s">
-        <v>642</v>
-      </c>
       <c r="G287">
-        <v>271.83</v>
+        <v>134</v>
       </c>
       <c r="H287">
-        <v>4.5305</v>
+        <v>2.23333333333333</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" t="s">
-        <v>638</v>
+        <v>233</v>
       </c>
       <c r="B288" t="s">
+        <v>642</v>
+      </c>
+      <c r="C288" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D288" t="s">
+        <v>9</v>
+      </c>
+      <c r="E288" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F288" t="s">
         <v>643</v>
       </c>
-      <c r="C288" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D288" t="s">
-        <v>9</v>
-      </c>
-      <c r="E288" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F288" t="s">
-        <v>644</v>
-      </c>
       <c r="G288">
-        <v>371.04</v>
+        <v>152.29</v>
       </c>
       <c r="H288">
-        <v>6.184</v>
+        <v>2.53816666666666</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" t="s">
+        <v>644</v>
+      </c>
+      <c r="B289" t="s">
         <v>645</v>
       </c>
-      <c r="B289" t="s">
+      <c r="C289" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D289" t="s">
+        <v>9</v>
+      </c>
+      <c r="E289" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F289" t="s">
         <v>646</v>
       </c>
-      <c r="C289" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D289" t="s">
-        <v>9</v>
-      </c>
-      <c r="E289" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F289" t="s">
-        <v>647</v>
-      </c>
       <c r="G289">
-        <v>490.29</v>
+        <v>320.46</v>
       </c>
       <c r="H289">
-        <v>8.1715</v>
+        <v>5.34099999999999</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
+        <v>644</v>
+      </c>
+      <c r="B290" t="s">
+        <v>647</v>
+      </c>
+      <c r="C290" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D290" t="s">
+        <v>9</v>
+      </c>
+      <c r="E290" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F290" t="s">
         <v>648</v>
       </c>
-      <c r="B290" s="11" t="s">
-        <v>649</v>
-      </c>
-      <c r="C290" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D290" t="s">
-        <v>16</v>
-      </c>
-      <c r="E290" s="3">
-        <v>46327</v>
-      </c>
       <c r="G290">
-        <v>226.38</v>
+        <v>257.96</v>
       </c>
       <c r="H290">
-        <v>3.773</v>
+        <v>4.29933333333333</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
+        <v>649</v>
+      </c>
+      <c r="B291" t="s">
         <v>650</v>
       </c>
-      <c r="B291" t="s">
+      <c r="C291" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D291" t="s">
+        <v>9</v>
+      </c>
+      <c r="E291" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F291" t="s">
         <v>651</v>
       </c>
-      <c r="C291" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D291" t="s">
-        <v>9</v>
-      </c>
-      <c r="E291" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F291" t="s">
-        <v>652</v>
-      </c>
       <c r="G291">
-        <v>214.13</v>
+        <v>488.75</v>
       </c>
       <c r="H291">
-        <v>3.56883333333333</v>
+        <v>8.14583333333333</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" t="s">
+        <v>652</v>
+      </c>
+      <c r="B292" t="s">
         <v>653</v>
       </c>
-      <c r="B292" t="s">
+      <c r="C292" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D292" t="s">
+        <v>9</v>
+      </c>
+      <c r="E292" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F292" t="s">
         <v>654</v>
       </c>
-      <c r="C292" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D292" t="s">
-        <v>9</v>
-      </c>
-      <c r="E292" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F292" t="s">
-        <v>655</v>
-      </c>
       <c r="G292">
-        <v>138.17</v>
+        <v>216.71</v>
       </c>
       <c r="H292">
-        <v>2.30283333333333</v>
+        <v>3.61183333333333</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" t="s">
+        <v>655</v>
+      </c>
+      <c r="B293" t="s">
         <v>656</v>
       </c>
-      <c r="B293" t="s">
+      <c r="C293" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D293" t="s">
+        <v>16</v>
+      </c>
+      <c r="E293" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F293" t="s">
         <v>657</v>
       </c>
-      <c r="C293" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D293" t="s">
-        <v>9</v>
-      </c>
-      <c r="E293" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F293" t="s">
-        <v>658</v>
-      </c>
       <c r="G293">
-        <v>255.63</v>
+        <v>384.58</v>
       </c>
       <c r="H293">
-        <v>4.26049999999999</v>
+        <v>6.40966666666666</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" t="s">
-        <v>24</v>
+        <v>655</v>
       </c>
       <c r="B294" t="s">
-        <v>515</v>
+        <v>658</v>
       </c>
       <c r="C294" s="2">
         <v>46327</v>
@@ -10984,15 +11042,15 @@
         <v>659</v>
       </c>
       <c r="G294">
-        <v>254.83</v>
+        <v>271.83</v>
       </c>
       <c r="H294">
-        <v>4.24716666666666</v>
+        <v>4.5305</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295" t="s">
-        <v>24</v>
+        <v>655</v>
       </c>
       <c r="B295" t="s">
         <v>660</v>
@@ -11010,18 +11068,18 @@
         <v>661</v>
       </c>
       <c r="G295">
-        <v>223.88</v>
+        <v>371.04</v>
       </c>
       <c r="H295">
-        <v>3.73133333333333</v>
+        <v>6.184</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296" t="s">
-        <v>24</v>
+        <v>662</v>
       </c>
       <c r="B296" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C296" s="2">
         <v>46327</v>
@@ -11033,47 +11091,44 @@
         <v>46327</v>
       </c>
       <c r="F296" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G296">
-        <v>197.46</v>
+        <v>490.29</v>
       </c>
       <c r="H296">
-        <v>3.291</v>
+        <v>8.1715</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B297" s="11" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C297" s="2">
         <v>46327</v>
       </c>
       <c r="D297" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E297" s="3">
         <v>46327</v>
       </c>
-      <c r="F297" t="s">
-        <v>666</v>
-      </c>
       <c r="G297">
-        <v>290.17</v>
+        <v>226.38</v>
       </c>
       <c r="H297">
-        <v>4.83616666666666</v>
+        <v>3.773</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B298" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C298" s="2">
         <v>46327</v>
@@ -11085,21 +11140,21 @@
         <v>46327</v>
       </c>
       <c r="F298" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G298">
-        <v>284.92</v>
+        <v>214.13</v>
       </c>
       <c r="H298">
-        <v>4.74866666666666</v>
+        <v>3.56883333333333</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B299" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C299" s="2">
         <v>46327</v>
@@ -11111,21 +11166,21 @@
         <v>46327</v>
       </c>
       <c r="F299" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G299">
-        <v>256.08</v>
+        <v>138.17</v>
       </c>
       <c r="H299">
-        <v>4.268</v>
+        <v>2.30283333333333</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B300" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C300" s="2">
         <v>46327</v>
@@ -11137,21 +11192,21 @@
         <v>46327</v>
       </c>
       <c r="F300" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G300">
-        <v>234.17</v>
+        <v>255.63</v>
       </c>
       <c r="H300">
-        <v>3.90283333333333</v>
+        <v>4.26049999999999</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" t="s">
-        <v>675</v>
+        <v>24</v>
       </c>
       <c r="B301" t="s">
-        <v>227</v>
+        <v>532</v>
       </c>
       <c r="C301" s="2">
         <v>46327</v>
@@ -11163,18 +11218,18 @@
         <v>46327</v>
       </c>
       <c r="F301" t="s">
-        <v>228</v>
+        <v>676</v>
       </c>
       <c r="G301">
-        <v>432.08</v>
+        <v>254.83</v>
       </c>
       <c r="H301">
-        <v>7.20133333333333</v>
+        <v>4.24716666666666</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" t="s">
-        <v>676</v>
+        <v>24</v>
       </c>
       <c r="B302" t="s">
         <v>677</v>
@@ -11192,113 +11247,122 @@
         <v>678</v>
       </c>
       <c r="G302">
-        <v>300.79</v>
+        <v>223.88</v>
       </c>
       <c r="H302">
-        <v>5.01316666666666</v>
+        <v>3.73133333333333</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" t="s">
+        <v>24</v>
+      </c>
+      <c r="B303" t="s">
         <v>679</v>
       </c>
-      <c r="B303" t="s">
+      <c r="C303" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D303" t="s">
+        <v>9</v>
+      </c>
+      <c r="E303" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F303" t="s">
         <v>680</v>
       </c>
-      <c r="C303" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D303" t="s">
-        <v>9</v>
-      </c>
-      <c r="E303" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F303" t="s">
-        <v>681</v>
-      </c>
       <c r="G303">
-        <v>350.33</v>
+        <v>197.46</v>
       </c>
       <c r="H303">
-        <v>5.83883333333333</v>
+        <v>3.291</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" t="s">
+        <v>302</v>
+      </c>
+      <c r="B304" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="C304" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D304" t="s">
+        <v>9</v>
+      </c>
+      <c r="E304" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F304" t="s">
         <v>682</v>
       </c>
-      <c r="B304" t="s">
-        <v>683</v>
-      </c>
-      <c r="C304" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D304" t="s">
-        <v>9</v>
-      </c>
-      <c r="E304" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F304" t="s">
-        <v>684</v>
-      </c>
       <c r="G304">
-        <v>215.67</v>
+        <v>290.17</v>
       </c>
       <c r="H304">
-        <v>3.5945</v>
+        <v>4.83616666666666</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" t="s">
+        <v>683</v>
+      </c>
+      <c r="B305" t="s">
+        <v>684</v>
+      </c>
+      <c r="C305" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D305" t="s">
+        <v>9</v>
+      </c>
+      <c r="E305" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F305" t="s">
         <v>685</v>
       </c>
-      <c r="B305" t="s">
+      <c r="G305">
+        <v>256.08</v>
+      </c>
+      <c r="H305">
+        <v>4.268</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306" t="s">
         <v>686</v>
       </c>
-      <c r="C305" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D305" t="s">
-        <v>9</v>
-      </c>
-      <c r="E305" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F305" t="s">
+      <c r="B306" t="s">
         <v>687</v>
       </c>
-      <c r="G305">
-        <v>243.96</v>
-      </c>
-      <c r="H305">
-        <v>4.066</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5">
-      <c r="A306" t="s">
+      <c r="C306" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D306" t="s">
+        <v>9</v>
+      </c>
+      <c r="E306" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F306" t="s">
         <v>688</v>
       </c>
-      <c r="B306" t="s">
-        <v>689</v>
-      </c>
-      <c r="C306" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D306" t="s">
-        <v>9</v>
-      </c>
-      <c r="E306" s="3">
-        <v>46327</v>
+      <c r="G306">
+        <v>234.17</v>
+      </c>
+      <c r="H306">
+        <v>3.90283333333333</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B307" t="s">
-        <v>691</v>
+        <v>227</v>
       </c>
       <c r="C307" s="2">
         <v>46327</v>
@@ -11310,13 +11374,13 @@
         <v>46327</v>
       </c>
       <c r="F307" t="s">
-        <v>692</v>
+        <v>228</v>
       </c>
       <c r="G307">
-        <v>556.92</v>
+        <v>432.08</v>
       </c>
       <c r="H307">
-        <v>9.282</v>
+        <v>7.20133333333333</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -11324,7 +11388,7 @@
         <v>690</v>
       </c>
       <c r="B308" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C308" s="2">
         <v>46327</v>
@@ -11336,44 +11400,44 @@
         <v>46327</v>
       </c>
       <c r="F308" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G308">
-        <v>356.46</v>
+        <v>300.79</v>
       </c>
       <c r="H308">
-        <v>5.941</v>
+        <v>5.01316666666666</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B309" t="s">
+        <v>694</v>
+      </c>
+      <c r="C309" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D309" t="s">
+        <v>9</v>
+      </c>
+      <c r="E309" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F309" t="s">
         <v>695</v>
       </c>
-      <c r="C309" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D309" t="s">
-        <v>9</v>
-      </c>
-      <c r="E309" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F309" t="s">
-        <v>696</v>
-      </c>
       <c r="G309">
-        <v>279.17</v>
+        <v>350.33</v>
       </c>
       <c r="H309">
-        <v>4.65283333333333</v>
+        <v>5.83883333333333</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="A310" t="s">
-        <v>246</v>
+        <v>696</v>
       </c>
       <c r="B310" t="s">
         <v>697</v>
@@ -11391,13 +11455,13 @@
         <v>698</v>
       </c>
       <c r="G310">
-        <v>162.829999999999</v>
+        <v>215.67</v>
       </c>
       <c r="H310">
-        <v>2.71383333333333</v>
-      </c>
-    </row>
-    <row r="311" spans="1:8">
+        <v>3.5945</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
       <c r="A311" t="s">
         <v>699</v>
       </c>
@@ -11413,92 +11477,83 @@
       <c r="E311" s="3">
         <v>46327</v>
       </c>
-      <c r="F311" t="s">
-        <v>701</v>
-      </c>
-      <c r="G311">
-        <v>225.25</v>
-      </c>
-      <c r="H311">
-        <v>3.75416666666666</v>
-      </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" t="s">
+        <v>701</v>
+      </c>
+      <c r="B312" t="s">
         <v>702</v>
       </c>
-      <c r="B312" t="s">
+      <c r="C312" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D312" t="s">
+        <v>9</v>
+      </c>
+      <c r="E312" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F312" t="s">
         <v>703</v>
       </c>
-      <c r="C312" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D312" t="s">
-        <v>16</v>
-      </c>
-      <c r="E312" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F312" t="s">
-        <v>704</v>
-      </c>
       <c r="G312">
-        <v>256.5</v>
+        <v>556.92</v>
       </c>
       <c r="H312">
-        <v>4.275</v>
+        <v>9.282</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" t="s">
-        <v>34</v>
+        <v>701</v>
       </c>
       <c r="B313" t="s">
+        <v>704</v>
+      </c>
+      <c r="C313" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D313" t="s">
+        <v>9</v>
+      </c>
+      <c r="E313" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F313" t="s">
         <v>705</v>
       </c>
-      <c r="C313" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D313" t="s">
-        <v>16</v>
-      </c>
-      <c r="E313" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F313" t="s">
-        <v>706</v>
-      </c>
       <c r="G313">
-        <v>216.579999999999</v>
+        <v>356.46</v>
       </c>
       <c r="H313">
-        <v>3.60966666666666</v>
+        <v>5.941</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" t="s">
-        <v>34</v>
+        <v>701</v>
       </c>
       <c r="B314" t="s">
+        <v>706</v>
+      </c>
+      <c r="C314" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D314" t="s">
+        <v>9</v>
+      </c>
+      <c r="E314" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F314" t="s">
         <v>707</v>
       </c>
-      <c r="C314" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D314" t="s">
-        <v>9</v>
-      </c>
-      <c r="E314" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F314" t="s">
-        <v>110</v>
-      </c>
       <c r="G314">
-        <v>204.079999999999</v>
+        <v>279.17</v>
       </c>
       <c r="H314">
-        <v>3.40133333333333</v>
+        <v>4.65283333333333</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -11521,10 +11576,10 @@
         <v>710</v>
       </c>
       <c r="G315">
-        <v>158.63</v>
+        <v>225.25</v>
       </c>
       <c r="H315">
-        <v>2.64383333333333</v>
+        <v>3.75416666666666</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -11538,7 +11593,7 @@
         <v>46327</v>
       </c>
       <c r="D316" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E316" s="3">
         <v>46327</v>
@@ -11547,44 +11602,44 @@
         <v>713</v>
       </c>
       <c r="G316">
-        <v>212.96</v>
+        <v>256.5</v>
       </c>
       <c r="H316">
-        <v>3.54933333333333</v>
+        <v>4.275</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" t="s">
+        <v>34</v>
+      </c>
+      <c r="B317" t="s">
         <v>714</v>
       </c>
-      <c r="B317" t="s">
+      <c r="C317" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D317" t="s">
+        <v>16</v>
+      </c>
+      <c r="E317" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F317" t="s">
         <v>715</v>
       </c>
-      <c r="C317" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D317" t="s">
-        <v>9</v>
-      </c>
-      <c r="E317" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F317" t="s">
-        <v>716</v>
-      </c>
       <c r="G317">
-        <v>561.25</v>
+        <v>216.579999999999</v>
       </c>
       <c r="H317">
-        <v>9.35416666666666</v>
+        <v>3.60966666666666</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" t="s">
-        <v>717</v>
+        <v>34</v>
       </c>
       <c r="B318" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C318" s="2">
         <v>46327</v>
@@ -11596,21 +11651,21 @@
         <v>46327</v>
       </c>
       <c r="F318" t="s">
-        <v>719</v>
+        <v>110</v>
       </c>
       <c r="G318">
-        <v>202.25</v>
+        <v>204.079999999999</v>
       </c>
       <c r="H318">
-        <v>3.37083333333333</v>
+        <v>3.40133333333333</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" t="s">
-        <v>252</v>
+        <v>717</v>
       </c>
       <c r="B319" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C319" s="2">
         <v>46327</v>
@@ -11622,142 +11677,151 @@
         <v>46327</v>
       </c>
       <c r="F319" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G319">
-        <v>196.25</v>
+        <v>212.96</v>
       </c>
       <c r="H319">
-        <v>3.27083333333333</v>
+        <v>3.54933333333333</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" t="s">
+        <v>720</v>
+      </c>
+      <c r="B320" t="s">
+        <v>721</v>
+      </c>
+      <c r="C320" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D320" t="s">
+        <v>9</v>
+      </c>
+      <c r="E320" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F320" t="s">
         <v>722</v>
       </c>
-      <c r="B320" t="s">
+      <c r="G320">
+        <v>561.25</v>
+      </c>
+      <c r="H320">
+        <v>9.35416666666666</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="A321" t="s">
         <v>723</v>
       </c>
-      <c r="C320" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D320" t="s">
-        <v>9</v>
-      </c>
-      <c r="E320" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F320" t="s">
+      <c r="B321" t="s">
         <v>724</v>
       </c>
-      <c r="G320">
-        <v>270.63</v>
-      </c>
-      <c r="H320">
-        <v>4.51049999999999</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9">
-      <c r="A321" t="s">
+      <c r="C321" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D321" t="s">
+        <v>9</v>
+      </c>
+      <c r="E321" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F321" t="s">
         <v>725</v>
       </c>
-      <c r="B321" t="s">
-        <v>726</v>
-      </c>
-      <c r="C321" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D321" t="s">
-        <v>9</v>
-      </c>
-      <c r="E321" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F321" t="s">
-        <v>727</v>
-      </c>
       <c r="G321">
-        <v>321.42</v>
+        <v>202.25</v>
       </c>
       <c r="H321">
-        <v>5.357</v>
-      </c>
-      <c r="I321" s="1"/>
+        <v>3.37083333333333</v>
+      </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B322" t="s">
+        <v>727</v>
+      </c>
+      <c r="C322" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D322" t="s">
+        <v>9</v>
+      </c>
+      <c r="E322" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F322" t="s">
         <v>728</v>
       </c>
-      <c r="C322" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D322" t="s">
-        <v>9</v>
-      </c>
-      <c r="E322" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F322" t="s">
+      <c r="G322">
+        <v>270.63</v>
+      </c>
+      <c r="H322">
+        <v>4.51049999999999</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9">
+      <c r="A323" t="s">
         <v>729</v>
       </c>
-      <c r="G322">
-        <v>393.79</v>
-      </c>
-      <c r="H322">
-        <v>6.56316666666666</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5">
-      <c r="A323" t="s">
+      <c r="B323" t="s">
         <v>730</v>
       </c>
-      <c r="B323" s="11" t="s">
+      <c r="C323" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D323" t="s">
+        <v>9</v>
+      </c>
+      <c r="E323" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F323" t="s">
         <v>731</v>
       </c>
-      <c r="C323" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D323" t="s">
-        <v>9</v>
-      </c>
-      <c r="E323" s="3">
-        <v>46327</v>
-      </c>
+      <c r="G323">
+        <v>321.42</v>
+      </c>
+      <c r="H323">
+        <v>5.357</v>
+      </c>
+      <c r="I323" s="1"/>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" t="s">
+        <v>729</v>
+      </c>
+      <c r="B324" t="s">
         <v>732</v>
       </c>
-      <c r="B324" t="s">
+      <c r="C324" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D324" t="s">
+        <v>9</v>
+      </c>
+      <c r="E324" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F324" t="s">
         <v>733</v>
       </c>
-      <c r="C324" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D324" t="s">
-        <v>9</v>
-      </c>
-      <c r="E324" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F324" t="s">
+      <c r="G324">
+        <v>393.79</v>
+      </c>
+      <c r="H324">
+        <v>6.56316666666666</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" t="s">
         <v>734</v>
       </c>
-      <c r="G324">
-        <v>241.29</v>
-      </c>
-      <c r="H324">
-        <v>4.0215</v>
-      </c>
-    </row>
-    <row r="325" spans="1:8">
-      <c r="A325" t="s">
-        <v>732</v>
-      </c>
-      <c r="B325" t="s">
+      <c r="B325" s="11" t="s">
         <v>735</v>
       </c>
       <c r="C325" s="2">
@@ -11768,20 +11832,11 @@
       </c>
       <c r="E325" s="3">
         <v>46327</v>
-      </c>
-      <c r="F325" t="s">
-        <v>736</v>
-      </c>
-      <c r="G325">
-        <v>146.54</v>
-      </c>
-      <c r="H325">
-        <v>2.44233333333333</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B326" t="s">
         <v>737</v>
@@ -11799,67 +11854,67 @@
         <v>738</v>
       </c>
       <c r="G326">
-        <v>172.46</v>
+        <v>241.29</v>
       </c>
       <c r="H326">
-        <v>2.87433333333333</v>
+        <v>4.0215</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" t="s">
+        <v>736</v>
+      </c>
+      <c r="B327" t="s">
         <v>739</v>
       </c>
-      <c r="B327" t="s">
+      <c r="C327" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D327" t="s">
+        <v>9</v>
+      </c>
+      <c r="E327" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F327" t="s">
         <v>740</v>
       </c>
-      <c r="C327" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D327" t="s">
-        <v>9</v>
-      </c>
-      <c r="E327" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F327" t="s">
-        <v>741</v>
-      </c>
       <c r="G327">
-        <v>167.46</v>
+        <v>146.54</v>
       </c>
       <c r="H327">
-        <v>2.791</v>
+        <v>2.44233333333333</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B328" t="s">
+        <v>741</v>
+      </c>
+      <c r="C328" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D328" t="s">
+        <v>9</v>
+      </c>
+      <c r="E328" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F328" t="s">
         <v>742</v>
       </c>
-      <c r="C328" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D328" t="s">
-        <v>9</v>
-      </c>
-      <c r="E328" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F328" t="s">
-        <v>743</v>
-      </c>
       <c r="G328">
-        <v>257.46</v>
+        <v>172.46</v>
       </c>
       <c r="H328">
-        <v>4.29099999999999</v>
+        <v>2.87433333333333</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B329" t="s">
         <v>744</v>
@@ -11877,249 +11932,249 @@
         <v>745</v>
       </c>
       <c r="G329">
-        <v>179.21</v>
+        <v>167.46</v>
       </c>
       <c r="H329">
-        <v>2.98683333333333</v>
+        <v>2.791</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" t="s">
+        <v>743</v>
+      </c>
+      <c r="B330" t="s">
         <v>746</v>
       </c>
-      <c r="B330" t="s">
+      <c r="C330" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D330" t="s">
+        <v>9</v>
+      </c>
+      <c r="E330" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F330" t="s">
         <v>747</v>
       </c>
-      <c r="C330" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D330" t="s">
-        <v>9</v>
-      </c>
-      <c r="E330" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F330" t="s">
-        <v>748</v>
-      </c>
       <c r="G330">
-        <v>541.5</v>
+        <v>257.46</v>
       </c>
       <c r="H330">
-        <v>9.025</v>
+        <v>4.29099999999999</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" t="s">
+        <v>743</v>
+      </c>
+      <c r="B331" t="s">
+        <v>748</v>
+      </c>
+      <c r="C331" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D331" t="s">
+        <v>9</v>
+      </c>
+      <c r="E331" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F331" t="s">
         <v>749</v>
       </c>
-      <c r="B331" t="s">
-        <v>750</v>
-      </c>
-      <c r="C331" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D331" t="s">
-        <v>9</v>
-      </c>
-      <c r="E331" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F331" t="s">
-        <v>751</v>
-      </c>
       <c r="G331">
-        <v>307.29</v>
+        <v>179.21</v>
       </c>
       <c r="H331">
-        <v>5.1215</v>
+        <v>2.98683333333333</v>
       </c>
     </row>
     <row r="332" spans="1:8">
       <c r="A332" t="s">
+        <v>750</v>
+      </c>
+      <c r="B332" t="s">
+        <v>751</v>
+      </c>
+      <c r="C332" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D332" t="s">
+        <v>9</v>
+      </c>
+      <c r="E332" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F332" t="s">
         <v>752</v>
       </c>
-      <c r="B332" t="s">
-        <v>753</v>
-      </c>
-      <c r="C332" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D332" t="s">
-        <v>9</v>
-      </c>
-      <c r="E332" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F332" t="s">
-        <v>754</v>
-      </c>
       <c r="G332">
-        <v>193.58</v>
+        <v>541.5</v>
       </c>
       <c r="H332">
-        <v>3.22633333333333</v>
+        <v>9.025</v>
       </c>
     </row>
     <row r="333" spans="1:8">
       <c r="A333" t="s">
+        <v>753</v>
+      </c>
+      <c r="B333" t="s">
+        <v>754</v>
+      </c>
+      <c r="C333" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D333" t="s">
+        <v>9</v>
+      </c>
+      <c r="E333" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F333" t="s">
         <v>755</v>
       </c>
-      <c r="B333" t="s">
-        <v>756</v>
-      </c>
-      <c r="C333" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D333" t="s">
-        <v>9</v>
-      </c>
-      <c r="E333" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F333" t="s">
-        <v>757</v>
-      </c>
       <c r="G333">
-        <v>132.33</v>
+        <v>307.29</v>
       </c>
       <c r="H333">
-        <v>2.2055</v>
+        <v>5.1215</v>
       </c>
     </row>
     <row r="334" spans="1:8">
       <c r="A334" t="s">
+        <v>756</v>
+      </c>
+      <c r="B334" t="s">
+        <v>757</v>
+      </c>
+      <c r="C334" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D334" t="s">
+        <v>9</v>
+      </c>
+      <c r="E334" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F334" t="s">
         <v>758</v>
       </c>
-      <c r="B334" t="s">
-        <v>759</v>
-      </c>
-      <c r="C334" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D334" t="s">
-        <v>9</v>
-      </c>
-      <c r="E334" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F334" t="s">
-        <v>760</v>
-      </c>
       <c r="G334">
-        <v>210</v>
+        <v>193.58</v>
       </c>
       <c r="H334">
-        <v>3.5</v>
+        <v>3.22633333333333</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="A335" t="s">
+        <v>759</v>
+      </c>
+      <c r="B335" t="s">
+        <v>760</v>
+      </c>
+      <c r="C335" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D335" t="s">
+        <v>9</v>
+      </c>
+      <c r="E335" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F335" t="s">
         <v>761</v>
       </c>
-      <c r="B335" t="s">
-        <v>762</v>
-      </c>
-      <c r="C335" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D335" t="s">
-        <v>9</v>
-      </c>
-      <c r="E335" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F335" t="s">
-        <v>763</v>
-      </c>
       <c r="G335">
-        <v>251.67</v>
+        <v>132.33</v>
       </c>
       <c r="H335">
-        <v>4.1945</v>
+        <v>2.2055</v>
       </c>
     </row>
     <row r="336" spans="1:8">
       <c r="A336" t="s">
-        <v>46</v>
+        <v>762</v>
       </c>
       <c r="B336" t="s">
+        <v>763</v>
+      </c>
+      <c r="C336" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D336" t="s">
+        <v>9</v>
+      </c>
+      <c r="E336" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F336" t="s">
         <v>764</v>
       </c>
-      <c r="C336" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D336" t="s">
-        <v>9</v>
-      </c>
-      <c r="E336" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F336" t="s">
-        <v>765</v>
-      </c>
       <c r="G336">
-        <v>191.88</v>
+        <v>210</v>
       </c>
       <c r="H336">
-        <v>3.198</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="337" spans="1:8">
       <c r="A337" t="s">
+        <v>765</v>
+      </c>
+      <c r="B337" t="s">
         <v>766</v>
       </c>
-      <c r="B337" t="s">
+      <c r="C337" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D337" t="s">
+        <v>9</v>
+      </c>
+      <c r="E337" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F337" t="s">
         <v>767</v>
       </c>
-      <c r="C337" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D337" t="s">
-        <v>9</v>
-      </c>
-      <c r="E337" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F337" t="s">
-        <v>768</v>
-      </c>
       <c r="G337">
-        <v>230.829999999999</v>
+        <v>251.67</v>
       </c>
       <c r="H337">
-        <v>3.84716666666666</v>
+        <v>4.1945</v>
       </c>
     </row>
     <row r="338" spans="1:8">
       <c r="A338" t="s">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="B338" t="s">
+        <v>768</v>
+      </c>
+      <c r="C338" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D338" t="s">
+        <v>9</v>
+      </c>
+      <c r="E338" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F338" t="s">
         <v>769</v>
       </c>
-      <c r="C338" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D338" t="s">
-        <v>9</v>
-      </c>
-      <c r="E338" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F338" t="s">
-        <v>770</v>
-      </c>
       <c r="G338">
-        <v>213.13</v>
+        <v>191.88</v>
       </c>
       <c r="H338">
-        <v>3.55216666666666</v>
+        <v>3.198</v>
       </c>
     </row>
     <row r="339" spans="1:8">
       <c r="A339" t="s">
-        <v>115</v>
+        <v>770</v>
       </c>
       <c r="B339" t="s">
         <v>771</v>
@@ -12128,7 +12183,7 @@
         <v>46327</v>
       </c>
       <c r="D339" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E339" s="3">
         <v>46327</v>
@@ -12137,10 +12192,10 @@
         <v>772</v>
       </c>
       <c r="G339">
-        <v>252.25</v>
+        <v>230.829999999999</v>
       </c>
       <c r="H339">
-        <v>4.20416666666666</v>
+        <v>3.84716666666666</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -12163,67 +12218,67 @@
         <v>774</v>
       </c>
       <c r="G340">
-        <v>216.25</v>
+        <v>213.13</v>
       </c>
       <c r="H340">
-        <v>3.60416666666666</v>
+        <v>3.55216666666666</v>
       </c>
     </row>
     <row r="341" spans="1:8">
       <c r="A341" t="s">
+        <v>115</v>
+      </c>
+      <c r="B341" t="s">
         <v>775</v>
       </c>
-      <c r="B341" t="s">
+      <c r="C341" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D341" t="s">
+        <v>16</v>
+      </c>
+      <c r="E341" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F341" t="s">
         <v>776</v>
       </c>
-      <c r="C341" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D341" t="s">
-        <v>9</v>
-      </c>
-      <c r="E341" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F341" t="s">
-        <v>777</v>
-      </c>
       <c r="G341">
-        <v>514.79</v>
+        <v>252.25</v>
       </c>
       <c r="H341">
-        <v>8.57983333333333</v>
+        <v>4.20416666666666</v>
       </c>
     </row>
     <row r="342" spans="1:8">
       <c r="A342" t="s">
-        <v>775</v>
+        <v>115</v>
       </c>
       <c r="B342" t="s">
+        <v>777</v>
+      </c>
+      <c r="C342" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D342" t="s">
+        <v>9</v>
+      </c>
+      <c r="E342" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F342" t="s">
         <v>778</v>
       </c>
-      <c r="C342" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D342" t="s">
-        <v>9</v>
-      </c>
-      <c r="E342" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F342" t="s">
-        <v>779</v>
-      </c>
       <c r="G342">
-        <v>485.29</v>
+        <v>216.25</v>
       </c>
       <c r="H342">
-        <v>8.08816666666666</v>
+        <v>3.60416666666666</v>
       </c>
     </row>
     <row r="343" spans="1:8">
       <c r="A343" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B343" t="s">
         <v>780</v>
@@ -12241,104 +12296,110 @@
         <v>781</v>
       </c>
       <c r="G343">
-        <v>288.83</v>
+        <v>514.79</v>
       </c>
       <c r="H343">
-        <v>4.81383333333333</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5">
+        <v>8.57983333333333</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
       <c r="A344" t="s">
+        <v>779</v>
+      </c>
+      <c r="B344" t="s">
         <v>782</v>
       </c>
-      <c r="B344" s="11" t="s">
+      <c r="C344" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D344" t="s">
+        <v>9</v>
+      </c>
+      <c r="E344" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F344" t="s">
         <v>783</v>
       </c>
-      <c r="C344" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D344" t="s">
-        <v>16</v>
-      </c>
-      <c r="E344" s="3">
-        <v>46327</v>
+      <c r="G344">
+        <v>485.29</v>
+      </c>
+      <c r="H344">
+        <v>8.08816666666666</v>
       </c>
     </row>
     <row r="345" spans="1:8">
       <c r="A345" t="s">
+        <v>779</v>
+      </c>
+      <c r="B345" t="s">
         <v>784</v>
       </c>
-      <c r="B345" t="s">
+      <c r="C345" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D345" t="s">
+        <v>9</v>
+      </c>
+      <c r="E345" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F345" t="s">
         <v>785</v>
       </c>
-      <c r="C345" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D345" t="s">
-        <v>9</v>
-      </c>
-      <c r="E345" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F345" t="s">
+      <c r="G345">
+        <v>288.83</v>
+      </c>
+      <c r="H345">
+        <v>4.81383333333333</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" t="s">
         <v>786</v>
       </c>
-      <c r="G345">
-        <v>246.38</v>
-      </c>
-      <c r="H345">
-        <v>4.10633333333333</v>
-      </c>
-    </row>
-    <row r="346" spans="1:8">
-      <c r="A346" t="s">
-        <v>784</v>
-      </c>
-      <c r="B346" t="s">
+      <c r="B346" s="11" t="s">
         <v>787</v>
       </c>
       <c r="C346" s="2">
         <v>46327</v>
       </c>
       <c r="D346" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E346" s="3">
         <v>46327</v>
-      </c>
-      <c r="F346" t="s">
-        <v>788</v>
-      </c>
-      <c r="G346">
-        <v>182.33</v>
-      </c>
-      <c r="H346">
-        <v>3.03883333333333</v>
       </c>
     </row>
     <row r="347" spans="1:8">
       <c r="A347" t="s">
+        <v>788</v>
+      </c>
+      <c r="B347" t="s">
         <v>789</v>
       </c>
-      <c r="B347" s="11" t="s">
+      <c r="C347" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D347" t="s">
+        <v>9</v>
+      </c>
+      <c r="E347" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F347" t="s">
         <v>790</v>
       </c>
-      <c r="C347" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D347" t="s">
-        <v>9</v>
-      </c>
-      <c r="E347" s="3">
-        <v>46327</v>
+      <c r="G347">
+        <v>246.38</v>
       </c>
       <c r="H347">
-        <v>4.20416666666666</v>
+        <v>4.10633333333333</v>
       </c>
     </row>
     <row r="348" spans="1:8">
       <c r="A348" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B348" t="s">
         <v>791</v>
@@ -12356,19 +12417,19 @@
         <v>792</v>
       </c>
       <c r="G348">
-        <v>187.25</v>
+        <v>182.33</v>
       </c>
       <c r="H348">
-        <v>3.12083333333333</v>
+        <v>3.03883333333333</v>
       </c>
     </row>
     <row r="349" spans="1:8">
       <c r="A349" t="s">
-        <v>789</v>
-      </c>
-      <c r="B349" t="s">
         <v>793</v>
       </c>
+      <c r="B349" s="11" t="s">
+        <v>794</v>
+      </c>
       <c r="C349" s="2">
         <v>46327</v>
       </c>
@@ -12378,99 +12439,93 @@
       <c r="E349" s="3">
         <v>46327</v>
       </c>
-      <c r="F349" t="s">
-        <v>794</v>
-      </c>
-      <c r="G349">
-        <v>255.21</v>
-      </c>
       <c r="H349">
-        <v>4.2535</v>
+        <v>4.20416666666666</v>
       </c>
     </row>
     <row r="350" spans="1:8">
       <c r="A350" t="s">
+        <v>793</v>
+      </c>
+      <c r="B350" t="s">
         <v>795</v>
       </c>
-      <c r="B350" t="s">
+      <c r="C350" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D350" t="s">
+        <v>9</v>
+      </c>
+      <c r="E350" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F350" t="s">
         <v>796</v>
       </c>
-      <c r="C350" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D350" t="s">
-        <v>9</v>
-      </c>
-      <c r="E350" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F350" t="s">
-        <v>797</v>
-      </c>
       <c r="G350">
-        <v>138.79</v>
+        <v>187.25</v>
       </c>
       <c r="H350">
-        <v>2.31316666666666</v>
+        <v>3.12083333333333</v>
       </c>
     </row>
     <row r="351" spans="1:8">
       <c r="A351" t="s">
+        <v>793</v>
+      </c>
+      <c r="B351" t="s">
+        <v>797</v>
+      </c>
+      <c r="C351" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D351" t="s">
+        <v>9</v>
+      </c>
+      <c r="E351" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F351" t="s">
         <v>798</v>
       </c>
-      <c r="B351" t="s">
-        <v>799</v>
-      </c>
-      <c r="C351" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D351" t="s">
-        <v>9</v>
-      </c>
-      <c r="E351" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F351" t="s">
-        <v>800</v>
-      </c>
       <c r="G351">
-        <v>331.5</v>
+        <v>255.21</v>
       </c>
       <c r="H351">
-        <v>5.525</v>
+        <v>4.2535</v>
       </c>
     </row>
     <row r="352" spans="1:8">
       <c r="A352" t="s">
+        <v>799</v>
+      </c>
+      <c r="B352" t="s">
+        <v>800</v>
+      </c>
+      <c r="C352" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D352" t="s">
+        <v>9</v>
+      </c>
+      <c r="E352" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F352" t="s">
         <v>801</v>
       </c>
-      <c r="B352" s="11" t="s">
-        <v>802</v>
-      </c>
-      <c r="C352" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D352" t="s">
-        <v>16</v>
-      </c>
-      <c r="E352" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F352" t="s">
-        <v>129</v>
-      </c>
       <c r="G352">
-        <v>242.63</v>
+        <v>138.79</v>
       </c>
       <c r="H352">
-        <v>4.04383333333333</v>
+        <v>2.31316666666666</v>
       </c>
     </row>
     <row r="353" spans="1:8">
       <c r="A353" t="s">
-        <v>801</v>
-      </c>
-      <c r="B353" s="11" t="s">
+        <v>802</v>
+      </c>
+      <c r="B353" t="s">
         <v>803</v>
       </c>
       <c r="C353" s="2">
@@ -12483,48 +12538,48 @@
         <v>46327</v>
       </c>
       <c r="F353" t="s">
-        <v>129</v>
+        <v>804</v>
       </c>
       <c r="G353">
-        <v>242.63</v>
+        <v>331.5</v>
       </c>
       <c r="H353">
-        <v>4.04383333333333</v>
+        <v>5.525</v>
       </c>
     </row>
     <row r="354" spans="1:8">
       <c r="A354" t="s">
-        <v>804</v>
-      </c>
-      <c r="B354" t="s">
         <v>805</v>
       </c>
+      <c r="B354" s="11" t="s">
+        <v>806</v>
+      </c>
       <c r="C354" s="2">
         <v>46327</v>
       </c>
       <c r="D354" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E354" s="3">
         <v>46327</v>
       </c>
       <c r="F354" t="s">
-        <v>806</v>
+        <v>129</v>
       </c>
       <c r="G354">
-        <v>157.54</v>
+        <v>242.63</v>
       </c>
       <c r="H354">
-        <v>2.62566666666666</v>
+        <v>4.04383333333333</v>
       </c>
     </row>
     <row r="355" spans="1:8">
       <c r="A355" t="s">
+        <v>805</v>
+      </c>
+      <c r="B355" s="11" t="s">
         <v>807</v>
       </c>
-      <c r="B355" t="s">
-        <v>808</v>
-      </c>
       <c r="C355" s="2">
         <v>46327</v>
       </c>
@@ -12535,44 +12590,44 @@
         <v>46327</v>
       </c>
       <c r="F355" t="s">
-        <v>809</v>
+        <v>129</v>
       </c>
       <c r="G355">
-        <v>195.25</v>
+        <v>242.63</v>
       </c>
       <c r="H355">
-        <v>3.25416666666666</v>
+        <v>4.04383333333333</v>
       </c>
     </row>
     <row r="356" spans="1:8">
       <c r="A356" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B356" t="s">
+        <v>809</v>
+      </c>
+      <c r="C356" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D356" t="s">
+        <v>9</v>
+      </c>
+      <c r="E356" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F356" t="s">
         <v>810</v>
       </c>
-      <c r="C356" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D356" t="s">
-        <v>9</v>
-      </c>
-      <c r="E356" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F356" t="s">
-        <v>811</v>
-      </c>
       <c r="G356">
-        <v>223.13</v>
+        <v>157.54</v>
       </c>
       <c r="H356">
-        <v>3.71883333333333</v>
+        <v>2.62566666666666</v>
       </c>
     </row>
     <row r="357" spans="1:8">
       <c r="A357" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="B357" t="s">
         <v>812</v>
@@ -12590,145 +12645,145 @@
         <v>813</v>
       </c>
       <c r="G357">
-        <v>205.38</v>
+        <v>195.25</v>
       </c>
       <c r="H357">
-        <v>3.423</v>
+        <v>3.25416666666666</v>
       </c>
     </row>
     <row r="358" spans="1:8">
       <c r="A358" t="s">
+        <v>811</v>
+      </c>
+      <c r="B358" t="s">
         <v>814</v>
       </c>
-      <c r="B358" t="s">
+      <c r="C358" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D358" t="s">
+        <v>9</v>
+      </c>
+      <c r="E358" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F358" t="s">
         <v>815</v>
       </c>
-      <c r="C358" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D358" t="s">
-        <v>9</v>
-      </c>
-      <c r="E358" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F358" t="s">
-        <v>816</v>
-      </c>
       <c r="G358">
-        <v>231.71</v>
+        <v>223.13</v>
       </c>
       <c r="H358">
-        <v>3.86183333333333</v>
+        <v>3.71883333333333</v>
       </c>
     </row>
     <row r="359" spans="1:8">
       <c r="A359" t="s">
+        <v>811</v>
+      </c>
+      <c r="B359" t="s">
+        <v>816</v>
+      </c>
+      <c r="C359" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D359" t="s">
+        <v>9</v>
+      </c>
+      <c r="E359" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F359" t="s">
         <v>817</v>
       </c>
-      <c r="B359" t="s">
-        <v>818</v>
-      </c>
-      <c r="C359" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D359" t="s">
-        <v>9</v>
-      </c>
-      <c r="E359" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F359" t="s">
-        <v>819</v>
-      </c>
       <c r="G359">
-        <v>224.579999999999</v>
+        <v>205.38</v>
       </c>
       <c r="H359">
-        <v>3.743</v>
+        <v>3.423</v>
       </c>
     </row>
     <row r="360" spans="1:8">
       <c r="A360" t="s">
+        <v>818</v>
+      </c>
+      <c r="B360" t="s">
+        <v>819</v>
+      </c>
+      <c r="C360" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D360" t="s">
+        <v>9</v>
+      </c>
+      <c r="E360" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F360" t="s">
         <v>820</v>
       </c>
-      <c r="B360" t="s">
-        <v>821</v>
-      </c>
-      <c r="C360" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D360" t="s">
-        <v>9</v>
-      </c>
-      <c r="E360" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F360" t="s">
-        <v>822</v>
-      </c>
       <c r="G360">
-        <v>230.5</v>
+        <v>231.71</v>
       </c>
       <c r="H360">
-        <v>3.84166666666666</v>
+        <v>3.86183333333333</v>
       </c>
     </row>
     <row r="361" spans="1:8">
       <c r="A361" t="s">
+        <v>821</v>
+      </c>
+      <c r="B361" t="s">
+        <v>822</v>
+      </c>
+      <c r="C361" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D361" t="s">
+        <v>9</v>
+      </c>
+      <c r="E361" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F361" t="s">
         <v>823</v>
       </c>
-      <c r="B361" t="s">
-        <v>824</v>
-      </c>
-      <c r="C361" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D361" t="s">
-        <v>9</v>
-      </c>
-      <c r="E361" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F361" t="s">
-        <v>825</v>
-      </c>
       <c r="G361">
-        <v>298.71</v>
+        <v>224.579999999999</v>
       </c>
       <c r="H361">
-        <v>4.97849999999999</v>
+        <v>3.743</v>
       </c>
     </row>
     <row r="362" spans="1:8">
       <c r="A362" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B362" t="s">
+        <v>825</v>
+      </c>
+      <c r="C362" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D362" t="s">
+        <v>9</v>
+      </c>
+      <c r="E362" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F362" t="s">
         <v>826</v>
       </c>
-      <c r="C362" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D362" t="s">
-        <v>9</v>
-      </c>
-      <c r="E362" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F362" t="s">
-        <v>827</v>
-      </c>
       <c r="G362">
-        <v>295.92</v>
+        <v>230.5</v>
       </c>
       <c r="H362">
-        <v>4.932</v>
+        <v>3.84166666666666</v>
       </c>
     </row>
     <row r="363" spans="1:8">
       <c r="A363" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B363" t="s">
         <v>828</v>
@@ -12746,15 +12801,15 @@
         <v>829</v>
       </c>
       <c r="G363">
-        <v>303.71</v>
+        <v>298.71</v>
       </c>
       <c r="H363">
-        <v>5.06183333333333</v>
+        <v>4.97849999999999</v>
       </c>
     </row>
     <row r="364" spans="1:8">
       <c r="A364" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B364" t="s">
         <v>830</v>
@@ -12772,15 +12827,15 @@
         <v>831</v>
       </c>
       <c r="G364">
-        <v>250.96</v>
+        <v>295.92</v>
       </c>
       <c r="H364">
-        <v>4.18266666666666</v>
+        <v>4.932</v>
       </c>
     </row>
     <row r="365" spans="1:8">
       <c r="A365" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B365" t="s">
         <v>832</v>
@@ -12798,15 +12853,15 @@
         <v>833</v>
       </c>
       <c r="G365">
-        <v>201.079999999999</v>
+        <v>303.71</v>
       </c>
       <c r="H365">
-        <v>3.35133333333333</v>
+        <v>5.06183333333333</v>
       </c>
     </row>
     <row r="366" spans="1:8">
       <c r="A366" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B366" t="s">
         <v>834</v>
@@ -12824,192 +12879,201 @@
         <v>835</v>
       </c>
       <c r="G366">
-        <v>335.92</v>
+        <v>250.96</v>
       </c>
       <c r="H366">
-        <v>5.59866666666666</v>
+        <v>4.18266666666666</v>
       </c>
     </row>
     <row r="367" spans="1:8">
       <c r="A367" t="s">
+        <v>827</v>
+      </c>
+      <c r="B367" t="s">
         <v>836</v>
       </c>
-      <c r="B367" t="s">
+      <c r="C367" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D367" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F367" t="s">
         <v>837</v>
       </c>
-      <c r="C367" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D367" t="s">
-        <v>9</v>
-      </c>
-      <c r="E367" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F367" t="s">
-        <v>838</v>
-      </c>
       <c r="G367">
-        <v>427.17</v>
+        <v>201.079999999999</v>
       </c>
       <c r="H367">
-        <v>7.1195</v>
+        <v>3.35133333333333</v>
       </c>
     </row>
     <row r="368" spans="1:8">
       <c r="A368" t="s">
+        <v>827</v>
+      </c>
+      <c r="B368" t="s">
+        <v>838</v>
+      </c>
+      <c r="C368" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D368" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F368" t="s">
         <v>839</v>
       </c>
-      <c r="B368" t="s">
-        <v>840</v>
-      </c>
-      <c r="C368" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D368" t="s">
-        <v>9</v>
-      </c>
-      <c r="E368" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F368" t="s">
-        <v>841</v>
-      </c>
       <c r="G368">
-        <v>193.71</v>
+        <v>335.92</v>
       </c>
       <c r="H368">
-        <v>3.2285</v>
+        <v>5.59866666666666</v>
       </c>
     </row>
     <row r="369" spans="1:8">
       <c r="A369" t="s">
+        <v>840</v>
+      </c>
+      <c r="B369" t="s">
+        <v>841</v>
+      </c>
+      <c r="C369" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D369" t="s">
+        <v>9</v>
+      </c>
+      <c r="E369" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F369" t="s">
         <v>842</v>
       </c>
-      <c r="B369" t="s">
-        <v>843</v>
-      </c>
-      <c r="C369" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D369" t="s">
-        <v>9</v>
-      </c>
-      <c r="E369" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F369" t="s">
-        <v>844</v>
-      </c>
       <c r="G369">
-        <v>236.829999999999</v>
+        <v>427.17</v>
       </c>
       <c r="H369">
-        <v>3.94716666666666</v>
+        <v>7.1195</v>
       </c>
     </row>
     <row r="370" spans="1:8">
       <c r="A370" t="s">
-        <v>183</v>
+        <v>843</v>
       </c>
       <c r="B370" t="s">
+        <v>844</v>
+      </c>
+      <c r="C370" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D370" t="s">
+        <v>9</v>
+      </c>
+      <c r="E370" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F370" t="s">
         <v>845</v>
       </c>
-      <c r="C370" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D370" t="s">
-        <v>9</v>
-      </c>
-      <c r="E370" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F370" t="s">
-        <v>846</v>
-      </c>
       <c r="G370">
-        <v>187.25</v>
+        <v>193.71</v>
       </c>
       <c r="H370">
-        <v>3.12083333333333</v>
+        <v>3.2285</v>
       </c>
     </row>
     <row r="371" spans="1:8">
       <c r="A371" t="s">
+        <v>846</v>
+      </c>
+      <c r="B371" t="s">
         <v>847</v>
       </c>
-      <c r="B371" t="s">
+      <c r="C371" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D371" t="s">
+        <v>9</v>
+      </c>
+      <c r="E371" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F371" t="s">
         <v>848</v>
       </c>
-      <c r="C371" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D371" t="s">
-        <v>9</v>
-      </c>
-      <c r="E371" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F371" t="s">
+      <c r="G371">
+        <v>236.829999999999</v>
+      </c>
+      <c r="H371">
+        <v>3.94716666666666</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" t="s">
+        <v>183</v>
+      </c>
+      <c r="B372" t="s">
         <v>849</v>
       </c>
-      <c r="G371">
-        <v>308.25</v>
-      </c>
-      <c r="H371">
-        <v>5.1375</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5">
-      <c r="A372" t="s">
+      <c r="C372" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D372" t="s">
+        <v>9</v>
+      </c>
+      <c r="E372" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F372" t="s">
         <v>850</v>
       </c>
-      <c r="B372" t="s">
-        <v>851</v>
-      </c>
-      <c r="C372" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D372" t="s">
-        <v>9</v>
-      </c>
-      <c r="E372" s="3">
-        <v>46327</v>
+      <c r="G372">
+        <v>187.25</v>
+      </c>
+      <c r="H372">
+        <v>3.12083333333333</v>
       </c>
     </row>
     <row r="373" spans="1:8">
       <c r="A373" t="s">
+        <v>851</v>
+      </c>
+      <c r="B373" t="s">
         <v>852</v>
       </c>
-      <c r="B373" t="s">
+      <c r="C373" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D373" t="s">
+        <v>9</v>
+      </c>
+      <c r="E373" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F373" t="s">
         <v>853</v>
       </c>
-      <c r="C373" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D373" t="s">
-        <v>9</v>
-      </c>
-      <c r="E373" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F373" t="s">
+      <c r="G373">
+        <v>308.25</v>
+      </c>
+      <c r="H373">
+        <v>5.1375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" t="s">
         <v>854</v>
       </c>
-      <c r="G373">
-        <v>254.29</v>
-      </c>
-      <c r="H373">
-        <v>4.23816666666666</v>
-      </c>
-    </row>
-    <row r="374" spans="1:8">
-      <c r="A374" t="s">
+      <c r="B374" t="s">
         <v>855</v>
       </c>
-      <c r="B374" t="s">
-        <v>856</v>
-      </c>
       <c r="C374" s="2">
         <v>46327</v>
       </c>
@@ -13018,74 +13082,65 @@
       </c>
       <c r="E374" s="3">
         <v>46327</v>
-      </c>
-      <c r="F374" t="s">
-        <v>857</v>
-      </c>
-      <c r="G374">
-        <v>173.5</v>
-      </c>
-      <c r="H374">
-        <v>2.89166666666666</v>
       </c>
     </row>
     <row r="375" spans="1:8">
       <c r="A375" t="s">
+        <v>856</v>
+      </c>
+      <c r="B375" t="s">
+        <v>857</v>
+      </c>
+      <c r="C375" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D375" t="s">
+        <v>9</v>
+      </c>
+      <c r="E375" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F375" t="s">
         <v>858</v>
       </c>
-      <c r="B375" t="s">
-        <v>859</v>
-      </c>
-      <c r="C375" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D375" t="s">
-        <v>9</v>
-      </c>
-      <c r="E375" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F375" t="s">
-        <v>860</v>
-      </c>
       <c r="G375">
-        <v>336.67</v>
+        <v>254.29</v>
       </c>
       <c r="H375">
-        <v>5.61116666666666</v>
+        <v>4.23816666666666</v>
       </c>
     </row>
     <row r="376" spans="1:8">
       <c r="A376" t="s">
+        <v>859</v>
+      </c>
+      <c r="B376" t="s">
+        <v>860</v>
+      </c>
+      <c r="C376" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D376" t="s">
+        <v>9</v>
+      </c>
+      <c r="E376" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F376" t="s">
         <v>861</v>
       </c>
-      <c r="B376" s="11" t="s">
-        <v>712</v>
-      </c>
-      <c r="C376" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D376" t="s">
-        <v>16</v>
-      </c>
-      <c r="E376" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F376" t="s">
-        <v>862</v>
-      </c>
       <c r="G376">
-        <v>275.5</v>
+        <v>173.5</v>
       </c>
       <c r="H376">
-        <v>4.59166666666666</v>
+        <v>2.89166666666666</v>
       </c>
     </row>
     <row r="377" spans="1:8">
       <c r="A377" t="s">
-        <v>267</v>
-      </c>
-      <c r="B377" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="B377" t="s">
         <v>863</v>
       </c>
       <c r="C377" s="2">
@@ -13098,55 +13153,70 @@
         <v>46327</v>
       </c>
       <c r="F377" t="s">
-        <v>269</v>
+        <v>864</v>
       </c>
       <c r="G377">
-        <v>229</v>
+        <v>336.67</v>
       </c>
       <c r="H377">
-        <v>3.81666666666666</v>
+        <v>5.61116666666666</v>
       </c>
     </row>
     <row r="378" spans="1:8">
       <c r="A378" t="s">
-        <v>61</v>
-      </c>
-      <c r="B378" t="s">
-        <v>864</v>
+        <v>865</v>
+      </c>
+      <c r="B378" s="11" t="s">
+        <v>718</v>
       </c>
       <c r="C378" s="2">
         <v>46327</v>
       </c>
       <c r="D378" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E378" s="3">
         <v>46327</v>
       </c>
       <c r="F378" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G378">
-        <v>161.79</v>
+        <v>275.5</v>
       </c>
       <c r="H378">
-        <v>2.6965</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5">
+        <v>4.59166666666666</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
       <c r="A379" t="s">
-        <v>866</v>
+        <v>267</v>
+      </c>
+      <c r="B379" s="10" t="s">
+        <v>867</v>
       </c>
       <c r="C379" s="2">
         <v>46327</v>
       </c>
+      <c r="D379" t="s">
+        <v>9</v>
+      </c>
       <c r="E379" s="3">
         <v>46327</v>
+      </c>
+      <c r="F379" t="s">
+        <v>269</v>
+      </c>
+      <c r="G379">
+        <v>229</v>
+      </c>
+      <c r="H379">
+        <v>3.81666666666666</v>
       </c>
     </row>
     <row r="380" spans="1:8">
       <c r="A380" t="s">
-        <v>867</v>
+        <v>61</v>
       </c>
       <c r="B380" t="s">
         <v>868</v>
@@ -13164,181 +13234,175 @@
         <v>869</v>
       </c>
       <c r="G380">
-        <v>351</v>
+        <v>161.79</v>
       </c>
       <c r="H380">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="381" spans="1:8">
+        <v>2.6965</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
       <c r="A381" t="s">
         <v>870</v>
       </c>
-      <c r="B381" t="s">
+      <c r="C381" s="2">
+        <v>46327</v>
+      </c>
+      <c r="E381" s="3">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" t="s">
         <v>871</v>
       </c>
-      <c r="C381" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D381" t="s">
-        <v>9</v>
-      </c>
-      <c r="E381" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F381" t="s">
+      <c r="B382" t="s">
         <v>872</v>
       </c>
-      <c r="G381">
+      <c r="C382" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D382" t="s">
+        <v>9</v>
+      </c>
+      <c r="E382" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F382" t="s">
+        <v>873</v>
+      </c>
+      <c r="G382">
+        <v>351</v>
+      </c>
+      <c r="H382">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" t="s">
+        <v>874</v>
+      </c>
+      <c r="B383" t="s">
+        <v>875</v>
+      </c>
+      <c r="C383" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D383" t="s">
+        <v>9</v>
+      </c>
+      <c r="E383" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F383" t="s">
+        <v>876</v>
+      </c>
+      <c r="G383">
         <v>306.67</v>
       </c>
-      <c r="H381">
+      <c r="H383">
         <v>5.11116666666666</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
-      <c r="A382" t="s">
-        <v>873</v>
-      </c>
-      <c r="C382" s="2">
-        <v>46327</v>
-      </c>
-      <c r="E382" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5">
-      <c r="A383" t="s">
+    <row r="384" spans="1:5">
+      <c r="A384" t="s">
+        <v>877</v>
+      </c>
+      <c r="C384" s="2">
+        <v>46327</v>
+      </c>
+      <c r="E384" s="3">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" t="s">
         <v>154</v>
       </c>
-      <c r="B383" t="s">
-        <v>874</v>
-      </c>
-      <c r="C383" s="2">
-        <v>46327</v>
-      </c>
-      <c r="E383" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="384" spans="1:8">
-      <c r="A384" t="s">
-        <v>875</v>
-      </c>
-      <c r="B384" t="s">
-        <v>876</v>
-      </c>
-      <c r="C384" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D384" t="s">
-        <v>9</v>
-      </c>
-      <c r="E384" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F384" t="s">
-        <v>877</v>
-      </c>
-      <c r="G384">
+      <c r="B385" t="s">
+        <v>878</v>
+      </c>
+      <c r="C385" s="2">
+        <v>46327</v>
+      </c>
+      <c r="E385" s="3">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" t="s">
+        <v>879</v>
+      </c>
+      <c r="B386" t="s">
+        <v>880</v>
+      </c>
+      <c r="C386" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D386" t="s">
+        <v>9</v>
+      </c>
+      <c r="E386" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F386" t="s">
+        <v>881</v>
+      </c>
+      <c r="G386">
         <v>262.79</v>
       </c>
-      <c r="H384">
+      <c r="H386">
         <v>4.37983333333333</v>
       </c>
     </row>
-    <row r="385" spans="1:8">
-      <c r="A385" t="s">
-        <v>878</v>
-      </c>
-      <c r="B385" t="s">
-        <v>879</v>
-      </c>
-      <c r="C385" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D385" t="s">
-        <v>9</v>
-      </c>
-      <c r="E385" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F385" t="s">
-        <v>880</v>
-      </c>
-      <c r="G385">
+    <row r="387" spans="1:8">
+      <c r="A387" t="s">
+        <v>882</v>
+      </c>
+      <c r="B387" t="s">
+        <v>883</v>
+      </c>
+      <c r="C387" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D387" t="s">
+        <v>9</v>
+      </c>
+      <c r="E387" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F387" t="s">
+        <v>884</v>
+      </c>
+      <c r="G387">
         <v>214.21</v>
       </c>
-      <c r="H385">
+      <c r="H387">
         <v>3.57016666666666</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
-      <c r="A386" t="s">
+    <row r="388" spans="1:5">
+      <c r="A388" t="s">
         <v>74</v>
       </c>
-      <c r="B386" t="s">
-        <v>881</v>
-      </c>
-      <c r="C386" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D386" t="s">
-        <v>9</v>
-      </c>
-      <c r="E386" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5">
-      <c r="A387" t="s">
+      <c r="B388" t="s">
+        <v>885</v>
+      </c>
+      <c r="C388" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D388" t="s">
+        <v>9</v>
+      </c>
+      <c r="E388" s="3">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" t="s">
         <v>74</v>
       </c>
-      <c r="B387" t="s">
-        <v>882</v>
-      </c>
-      <c r="C387" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D387" t="s">
-        <v>9</v>
-      </c>
-      <c r="E387" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="388" spans="1:8">
-      <c r="A388" t="s">
-        <v>270</v>
-      </c>
-      <c r="B388" t="s">
-        <v>883</v>
-      </c>
-      <c r="C388" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D388" t="s">
-        <v>9</v>
-      </c>
-      <c r="E388" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F388" t="s">
-        <v>884</v>
-      </c>
-      <c r="G388">
-        <v>290.54</v>
-      </c>
-      <c r="H388">
-        <v>4.84233333333333</v>
-      </c>
-    </row>
-    <row r="389" spans="1:8">
-      <c r="A389" t="s">
-        <v>270</v>
-      </c>
       <c r="B389" t="s">
-        <v>709</v>
+        <v>886</v>
       </c>
       <c r="C389" s="2">
         <v>46327</v>
@@ -13348,20 +13412,11 @@
       </c>
       <c r="E389" s="3">
         <v>46327</v>
-      </c>
-      <c r="F389" t="s">
-        <v>885</v>
-      </c>
-      <c r="G389">
-        <v>280.5</v>
-      </c>
-      <c r="H389">
-        <v>4.675</v>
       </c>
     </row>
     <row r="390" spans="1:8">
       <c r="A390" t="s">
-        <v>886</v>
+        <v>270</v>
       </c>
       <c r="B390" t="s">
         <v>887</v>
@@ -13379,67 +13434,67 @@
         <v>888</v>
       </c>
       <c r="G390">
-        <v>492.46</v>
+        <v>290.54</v>
       </c>
       <c r="H390">
-        <v>8.20766666666666</v>
+        <v>4.84233333333333</v>
       </c>
     </row>
     <row r="391" spans="1:8">
       <c r="A391" t="s">
+        <v>270</v>
+      </c>
+      <c r="B391" t="s">
+        <v>311</v>
+      </c>
+      <c r="C391" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D391" t="s">
+        <v>9</v>
+      </c>
+      <c r="E391" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F391" t="s">
         <v>889</v>
       </c>
-      <c r="B391" t="s">
-        <v>890</v>
-      </c>
-      <c r="C391" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D391" t="s">
-        <v>9</v>
-      </c>
-      <c r="E391" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F391" t="s">
-        <v>891</v>
-      </c>
       <c r="G391">
-        <v>237.88</v>
+        <v>280.5</v>
       </c>
       <c r="H391">
-        <v>3.96466666666666</v>
+        <v>4.675</v>
       </c>
     </row>
     <row r="392" spans="1:8">
       <c r="A392" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B392" t="s">
+        <v>891</v>
+      </c>
+      <c r="C392" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D392" t="s">
+        <v>9</v>
+      </c>
+      <c r="E392" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F392" t="s">
         <v>892</v>
       </c>
-      <c r="C392" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D392" t="s">
-        <v>9</v>
-      </c>
-      <c r="E392" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F392" t="s">
-        <v>893</v>
-      </c>
       <c r="G392">
-        <v>279.46</v>
+        <v>492.46</v>
       </c>
       <c r="H392">
-        <v>4.65766666666666</v>
+        <v>8.20766666666666</v>
       </c>
     </row>
     <row r="393" spans="1:8">
       <c r="A393" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B393" t="s">
         <v>894</v>
@@ -13457,15 +13512,15 @@
         <v>895</v>
       </c>
       <c r="G393">
-        <v>166.329999999999</v>
+        <v>237.88</v>
       </c>
       <c r="H393">
-        <v>2.77216666666666</v>
+        <v>3.96466666666666</v>
       </c>
     </row>
     <row r="394" spans="1:8">
       <c r="A394" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B394" t="s">
         <v>896</v>
@@ -13483,15 +13538,15 @@
         <v>897</v>
       </c>
       <c r="G394">
-        <v>272.71</v>
+        <v>279.46</v>
       </c>
       <c r="H394">
-        <v>4.54516666666666</v>
+        <v>4.65766666666666</v>
       </c>
     </row>
     <row r="395" spans="1:8">
       <c r="A395" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B395" t="s">
         <v>898</v>
@@ -13509,15 +13564,15 @@
         <v>899</v>
       </c>
       <c r="G395">
-        <v>182.67</v>
+        <v>166.329999999999</v>
       </c>
       <c r="H395">
-        <v>3.04449999999999</v>
+        <v>2.77216666666666</v>
       </c>
     </row>
     <row r="396" spans="1:8">
       <c r="A396" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B396" t="s">
         <v>900</v>
@@ -13535,15 +13590,15 @@
         <v>901</v>
       </c>
       <c r="G396">
-        <v>225.54</v>
+        <v>272.71</v>
       </c>
       <c r="H396">
-        <v>3.759</v>
+        <v>4.54516666666666</v>
       </c>
     </row>
     <row r="397" spans="1:8">
       <c r="A397" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B397" t="s">
         <v>902</v>
@@ -13561,15 +13616,15 @@
         <v>903</v>
       </c>
       <c r="G397">
-        <v>528.88</v>
+        <v>182.67</v>
       </c>
       <c r="H397">
-        <v>8.81466666666666</v>
+        <v>3.04449999999999</v>
       </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B398" t="s">
         <v>904</v>
@@ -13587,15 +13642,15 @@
         <v>905</v>
       </c>
       <c r="G398">
-        <v>340.5</v>
+        <v>225.54</v>
       </c>
       <c r="H398">
-        <v>5.675</v>
+        <v>3.759</v>
       </c>
     </row>
     <row r="399" spans="1:8">
       <c r="A399" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B399" t="s">
         <v>906</v>
@@ -13613,15 +13668,15 @@
         <v>907</v>
       </c>
       <c r="G399">
-        <v>268.54</v>
+        <v>528.88</v>
       </c>
       <c r="H399">
-        <v>4.47566666666666</v>
+        <v>8.81466666666666</v>
       </c>
     </row>
     <row r="400" spans="1:8">
       <c r="A400" t="s">
-        <v>69</v>
+        <v>893</v>
       </c>
       <c r="B400" t="s">
         <v>908</v>
@@ -13639,114 +13694,114 @@
         <v>909</v>
       </c>
       <c r="G400">
-        <v>182.46</v>
+        <v>340.5</v>
       </c>
       <c r="H400">
-        <v>3.041</v>
+        <v>5.675</v>
       </c>
     </row>
     <row r="401" spans="1:8">
       <c r="A401" t="s">
+        <v>893</v>
+      </c>
+      <c r="B401" t="s">
         <v>910</v>
       </c>
-      <c r="B401" t="s">
+      <c r="C401" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D401" t="s">
+        <v>9</v>
+      </c>
+      <c r="E401" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F401" t="s">
         <v>911</v>
       </c>
-      <c r="C401" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D401" t="s">
-        <v>9</v>
-      </c>
-      <c r="E401" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F401" t="s">
-        <v>912</v>
-      </c>
       <c r="G401">
-        <v>258.04</v>
+        <v>268.54</v>
       </c>
       <c r="H401">
-        <v>4.30066666666666</v>
+        <v>4.47566666666666</v>
       </c>
     </row>
     <row r="402" spans="1:8">
       <c r="A402" t="s">
+        <v>69</v>
+      </c>
+      <c r="B402" t="s">
+        <v>912</v>
+      </c>
+      <c r="C402" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D402" t="s">
+        <v>9</v>
+      </c>
+      <c r="E402" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F402" t="s">
         <v>913</v>
       </c>
-      <c r="B402" t="s">
-        <v>914</v>
-      </c>
-      <c r="C402" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D402" t="s">
-        <v>9</v>
-      </c>
-      <c r="E402" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F402" t="s">
-        <v>915</v>
-      </c>
       <c r="G402">
-        <v>194.42</v>
+        <v>182.46</v>
       </c>
       <c r="H402">
-        <v>3.24033333333333</v>
+        <v>3.041</v>
       </c>
     </row>
     <row r="403" spans="1:8">
       <c r="A403" t="s">
+        <v>914</v>
+      </c>
+      <c r="B403" t="s">
+        <v>915</v>
+      </c>
+      <c r="C403" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D403" t="s">
+        <v>9</v>
+      </c>
+      <c r="E403" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F403" t="s">
         <v>916</v>
       </c>
-      <c r="B403" t="s">
-        <v>917</v>
-      </c>
-      <c r="C403" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D403" t="s">
-        <v>9</v>
-      </c>
-      <c r="E403" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F403" t="s">
-        <v>918</v>
-      </c>
       <c r="G403">
-        <v>282.83</v>
+        <v>258.04</v>
       </c>
       <c r="H403">
-        <v>4.71383333333333</v>
+        <v>4.30066666666666</v>
       </c>
     </row>
     <row r="404" spans="1:8">
       <c r="A404" t="s">
-        <v>76</v>
+        <v>917</v>
       </c>
       <c r="B404" t="s">
+        <v>918</v>
+      </c>
+      <c r="C404" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D404" t="s">
+        <v>9</v>
+      </c>
+      <c r="E404" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F404" t="s">
         <v>919</v>
       </c>
-      <c r="C404" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D404" t="s">
-        <v>9</v>
-      </c>
-      <c r="E404" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F404" t="s">
-        <v>212</v>
-      </c>
       <c r="G404">
-        <v>200.29</v>
+        <v>194.42</v>
       </c>
       <c r="H404">
-        <v>3.33816666666666</v>
+        <v>3.24033333333333</v>
       </c>
     </row>
     <row r="405" spans="1:8">
@@ -13769,19 +13824,19 @@
         <v>922</v>
       </c>
       <c r="G405">
-        <v>277.38</v>
+        <v>282.83</v>
       </c>
       <c r="H405">
-        <v>4.623</v>
+        <v>4.71383333333333</v>
       </c>
     </row>
     <row r="406" spans="1:8">
       <c r="A406" t="s">
+        <v>76</v>
+      </c>
+      <c r="B406" t="s">
         <v>923</v>
       </c>
-      <c r="B406" t="s">
-        <v>924</v>
-      </c>
       <c r="C406" s="2">
         <v>46327</v>
       </c>
@@ -13792,47 +13847,47 @@
         <v>46327</v>
       </c>
       <c r="F406" t="s">
-        <v>925</v>
+        <v>212</v>
       </c>
       <c r="G406">
-        <v>280.29</v>
+        <v>200.29</v>
       </c>
       <c r="H406">
-        <v>4.6715</v>
+        <v>3.33816666666666</v>
       </c>
     </row>
     <row r="407" spans="1:8">
       <c r="A407" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B407" t="s">
+        <v>925</v>
+      </c>
+      <c r="C407" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D407" t="s">
+        <v>9</v>
+      </c>
+      <c r="E407" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F407" t="s">
         <v>926</v>
       </c>
-      <c r="C407" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D407" t="s">
-        <v>9</v>
-      </c>
-      <c r="E407" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F407" t="s">
-        <v>927</v>
-      </c>
       <c r="G407">
-        <v>312.38</v>
+        <v>277.38</v>
       </c>
       <c r="H407">
-        <v>5.20633333333333</v>
+        <v>4.623</v>
       </c>
     </row>
     <row r="408" spans="1:8">
       <c r="A408" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B408" t="s">
-        <v>296</v>
+        <v>928</v>
       </c>
       <c r="C408" s="2">
         <v>46327</v>
@@ -13844,38 +13899,47 @@
         <v>46327</v>
       </c>
       <c r="F408" t="s">
-        <v>297</v>
+        <v>929</v>
       </c>
       <c r="G408">
-        <v>239</v>
+        <v>280.29</v>
       </c>
       <c r="H408">
-        <v>3.98333333333333</v>
-      </c>
-    </row>
-    <row r="409" spans="1:5">
+        <v>4.6715</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8">
       <c r="A409" t="s">
-        <v>928</v>
-      </c>
-      <c r="B409" s="11" t="s">
-        <v>929</v>
+        <v>927</v>
+      </c>
+      <c r="B409" t="s">
+        <v>930</v>
       </c>
       <c r="C409" s="2">
         <v>46327</v>
       </c>
       <c r="D409" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E409" s="3">
         <v>46327</v>
+      </c>
+      <c r="F409" t="s">
+        <v>931</v>
+      </c>
+      <c r="G409">
+        <v>312.38</v>
+      </c>
+      <c r="H409">
+        <v>5.20633333333333</v>
       </c>
     </row>
     <row r="410" spans="1:8">
       <c r="A410" t="s">
-        <v>81</v>
+        <v>927</v>
       </c>
       <c r="B410" t="s">
-        <v>930</v>
+        <v>296</v>
       </c>
       <c r="C410" s="2">
         <v>46327</v>
@@ -13887,39 +13951,30 @@
         <v>46327</v>
       </c>
       <c r="F410" t="s">
-        <v>931</v>
+        <v>297</v>
       </c>
       <c r="G410">
-        <v>600.88</v>
+        <v>239</v>
       </c>
       <c r="H410">
-        <v>10.0146666666666</v>
-      </c>
-    </row>
-    <row r="411" spans="1:8">
+        <v>3.98333333333333</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
       <c r="A411" t="s">
-        <v>81</v>
-      </c>
-      <c r="B411" t="s">
         <v>932</v>
       </c>
+      <c r="B411" s="11" t="s">
+        <v>933</v>
+      </c>
       <c r="C411" s="2">
         <v>46327</v>
       </c>
       <c r="D411" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E411" s="3">
         <v>46327</v>
-      </c>
-      <c r="F411" t="s">
-        <v>933</v>
-      </c>
-      <c r="G411">
-        <v>309.5</v>
-      </c>
-      <c r="H411">
-        <v>5.15833333333333</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -13942,10 +13997,10 @@
         <v>935</v>
       </c>
       <c r="G412">
-        <v>240.13</v>
+        <v>600.88</v>
       </c>
       <c r="H412">
-        <v>4.00216666666666</v>
+        <v>10.0146666666666</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -13968,10 +14023,10 @@
         <v>937</v>
       </c>
       <c r="G413">
-        <v>240.54</v>
+        <v>309.5</v>
       </c>
       <c r="H413">
-        <v>4.00899999999999</v>
+        <v>5.15833333333333</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -13994,10 +14049,10 @@
         <v>939</v>
       </c>
       <c r="G414">
-        <v>238.29</v>
+        <v>240.13</v>
       </c>
       <c r="H414">
-        <v>3.9715</v>
+        <v>4.00216666666666</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -14020,10 +14075,10 @@
         <v>941</v>
       </c>
       <c r="G415">
-        <v>236.17</v>
+        <v>240.54</v>
       </c>
       <c r="H415">
-        <v>3.93616666666666</v>
+        <v>4.00899999999999</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -14046,10 +14101,10 @@
         <v>943</v>
       </c>
       <c r="G416">
-        <v>258.13</v>
+        <v>238.29</v>
       </c>
       <c r="H416">
-        <v>4.30216666666666</v>
+        <v>3.9715</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -14072,10 +14127,10 @@
         <v>945</v>
       </c>
       <c r="G417">
-        <v>243.08</v>
+        <v>236.17</v>
       </c>
       <c r="H417">
-        <v>4.05133333333333</v>
+        <v>3.93616666666666</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -14098,10 +14153,10 @@
         <v>947</v>
       </c>
       <c r="G418">
-        <v>226.13</v>
+        <v>258.13</v>
       </c>
       <c r="H418">
-        <v>3.76883333333333</v>
+        <v>4.30216666666666</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -14124,125 +14179,149 @@
         <v>949</v>
       </c>
       <c r="G419">
-        <v>234.75</v>
+        <v>243.08</v>
       </c>
       <c r="H419">
-        <v>3.9125</v>
+        <v>4.05133333333333</v>
       </c>
     </row>
     <row r="420" spans="1:8">
       <c r="A420" t="s">
+        <v>81</v>
+      </c>
+      <c r="B420" t="s">
         <v>950</v>
       </c>
-      <c r="B420" t="s">
+      <c r="C420" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D420" t="s">
+        <v>9</v>
+      </c>
+      <c r="E420" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F420" t="s">
         <v>951</v>
       </c>
-      <c r="C420" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D420" t="s">
-        <v>9</v>
-      </c>
-      <c r="E420" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F420" t="s">
-        <v>952</v>
-      </c>
       <c r="G420">
-        <v>203.13</v>
+        <v>226.13</v>
       </c>
       <c r="H420">
-        <v>3.3855</v>
+        <v>3.76883333333333</v>
       </c>
     </row>
     <row r="421" spans="1:8">
       <c r="A421" t="s">
-        <v>950</v>
+        <v>81</v>
       </c>
       <c r="B421" t="s">
+        <v>952</v>
+      </c>
+      <c r="C421" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D421" t="s">
+        <v>9</v>
+      </c>
+      <c r="E421" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F421" t="s">
         <v>953</v>
       </c>
-      <c r="C421" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D421" t="s">
-        <v>9</v>
-      </c>
-      <c r="E421" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F421" t="s">
-        <v>954</v>
-      </c>
       <c r="G421">
-        <v>205</v>
+        <v>234.75</v>
       </c>
       <c r="H421">
-        <v>3.41666666666666</v>
+        <v>3.9125</v>
       </c>
     </row>
     <row r="422" spans="1:8">
       <c r="A422" t="s">
+        <v>954</v>
+      </c>
+      <c r="B422" t="s">
         <v>955</v>
       </c>
-      <c r="B422" t="s">
+      <c r="C422" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D422" t="s">
+        <v>9</v>
+      </c>
+      <c r="E422" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F422" t="s">
         <v>956</v>
       </c>
-      <c r="C422" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D422" t="s">
-        <v>9</v>
-      </c>
-      <c r="E422" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F422" t="s">
+      <c r="G422">
+        <v>203.13</v>
+      </c>
+      <c r="H422">
+        <v>3.3855</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8">
+      <c r="A423" t="s">
+        <v>954</v>
+      </c>
+      <c r="B423" t="s">
         <v>957</v>
       </c>
-      <c r="G422">
+      <c r="C423" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D423" t="s">
+        <v>9</v>
+      </c>
+      <c r="E423" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F423" t="s">
+        <v>958</v>
+      </c>
+      <c r="G423">
+        <v>205</v>
+      </c>
+      <c r="H423">
+        <v>3.41666666666666</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8">
+      <c r="A424" t="s">
+        <v>959</v>
+      </c>
+      <c r="B424" t="s">
+        <v>960</v>
+      </c>
+      <c r="C424" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D424" t="s">
+        <v>9</v>
+      </c>
+      <c r="E424" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F424" t="s">
+        <v>961</v>
+      </c>
+      <c r="G424">
         <v>246.71</v>
       </c>
-      <c r="H422">
+      <c r="H424">
         <v>4.11183333333333</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
-      <c r="A423" t="s">
-        <v>958</v>
-      </c>
-      <c r="B423" s="11" t="s">
-        <v>959</v>
-      </c>
-      <c r="C423" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D423" t="s">
-        <v>9</v>
-      </c>
-      <c r="E423" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5">
-      <c r="A424" t="s">
-        <v>960</v>
-      </c>
-      <c r="C424" s="2">
-        <v>46327</v>
-      </c>
-      <c r="E424" s="3">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="425" spans="1:8">
+    <row r="425" spans="1:5">
       <c r="A425" t="s">
-        <v>961</v>
-      </c>
-      <c r="B425" t="s">
         <v>962</v>
       </c>
+      <c r="B425" s="11" t="s">
+        <v>963</v>
+      </c>
       <c r="C425" s="2">
         <v>46327</v>
       </c>
@@ -14252,409 +14331,397 @@
       <c r="E425" s="3">
         <v>46327</v>
       </c>
-      <c r="F425" t="s">
-        <v>963</v>
-      </c>
-      <c r="G425">
-        <v>273.17</v>
-      </c>
-      <c r="H425">
-        <v>4.55283333333333</v>
-      </c>
-    </row>
-    <row r="426" spans="1:8">
+    </row>
+    <row r="426" spans="1:5">
       <c r="A426" t="s">
         <v>964</v>
       </c>
-      <c r="B426" t="s">
-        <v>965</v>
-      </c>
       <c r="C426" s="2">
         <v>46327</v>
       </c>
-      <c r="D426" t="s">
-        <v>9</v>
-      </c>
       <c r="E426" s="3">
         <v>46327</v>
-      </c>
-      <c r="F426" t="s">
-        <v>966</v>
-      </c>
-      <c r="G426">
-        <v>296.67</v>
-      </c>
-      <c r="H426">
-        <v>4.9445</v>
       </c>
     </row>
     <row r="427" spans="1:8">
       <c r="A427" t="s">
+        <v>965</v>
+      </c>
+      <c r="B427" t="s">
+        <v>966</v>
+      </c>
+      <c r="C427" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D427" t="s">
+        <v>9</v>
+      </c>
+      <c r="E427" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F427" t="s">
         <v>967</v>
       </c>
-      <c r="B427" t="s">
-        <v>968</v>
-      </c>
-      <c r="C427" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D427" t="s">
-        <v>9</v>
-      </c>
-      <c r="E427" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F427" t="s">
-        <v>969</v>
-      </c>
       <c r="G427">
-        <v>280.08</v>
+        <v>273.17</v>
       </c>
       <c r="H427">
-        <v>4.668</v>
+        <v>4.55283333333333</v>
       </c>
     </row>
     <row r="428" spans="1:8">
       <c r="A428" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B428" t="s">
+        <v>969</v>
+      </c>
+      <c r="C428" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D428" t="s">
+        <v>9</v>
+      </c>
+      <c r="E428" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F428" t="s">
         <v>970</v>
       </c>
-      <c r="C428" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D428" t="s">
-        <v>9</v>
-      </c>
-      <c r="E428" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F428" t="s">
-        <v>971</v>
-      </c>
       <c r="G428">
-        <v>292.29</v>
+        <v>296.67</v>
       </c>
       <c r="H428">
-        <v>4.8715</v>
+        <v>4.9445</v>
       </c>
     </row>
     <row r="429" spans="1:8">
       <c r="A429" t="s">
+        <v>971</v>
+      </c>
+      <c r="B429" t="s">
         <v>972</v>
       </c>
-      <c r="B429" t="s">
+      <c r="C429" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D429" t="s">
+        <v>9</v>
+      </c>
+      <c r="E429" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F429" t="s">
         <v>973</v>
       </c>
-      <c r="C429" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D429" t="s">
-        <v>9</v>
-      </c>
-      <c r="E429" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F429" t="s">
-        <v>974</v>
-      </c>
       <c r="G429">
-        <v>215.829999999999</v>
+        <v>280.08</v>
       </c>
       <c r="H429">
-        <v>3.59716666666666</v>
+        <v>4.668</v>
       </c>
     </row>
     <row r="430" spans="1:8">
       <c r="A430" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B430" t="s">
+        <v>974</v>
+      </c>
+      <c r="C430" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D430" t="s">
+        <v>9</v>
+      </c>
+      <c r="E430" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F430" t="s">
         <v>975</v>
       </c>
-      <c r="C430" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D430" t="s">
-        <v>9</v>
-      </c>
-      <c r="E430" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F430" t="s">
-        <v>976</v>
-      </c>
       <c r="G430">
-        <v>203.579999999999</v>
+        <v>292.29</v>
       </c>
       <c r="H430">
-        <v>3.393</v>
+        <v>4.8715</v>
       </c>
     </row>
     <row r="431" spans="1:8">
       <c r="A431" t="s">
+        <v>976</v>
+      </c>
+      <c r="B431" t="s">
         <v>977</v>
       </c>
-      <c r="B431" t="s">
+      <c r="C431" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D431" t="s">
+        <v>9</v>
+      </c>
+      <c r="E431" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F431" t="s">
         <v>978</v>
       </c>
-      <c r="C431" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D431" t="s">
-        <v>9</v>
-      </c>
-      <c r="E431" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F431" t="s">
-        <v>979</v>
-      </c>
       <c r="G431">
-        <v>202</v>
+        <v>215.829999999999</v>
       </c>
       <c r="H431">
-        <v>3.36666666666666</v>
+        <v>3.59716666666666</v>
       </c>
     </row>
     <row r="432" spans="1:8">
       <c r="A432" t="s">
+        <v>976</v>
+      </c>
+      <c r="B432" t="s">
+        <v>979</v>
+      </c>
+      <c r="C432" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D432" t="s">
+        <v>9</v>
+      </c>
+      <c r="E432" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F432" t="s">
         <v>980</v>
       </c>
-      <c r="B432" t="s">
-        <v>981</v>
-      </c>
-      <c r="C432" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D432" t="s">
-        <v>9</v>
-      </c>
-      <c r="E432" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F432" t="s">
-        <v>982</v>
-      </c>
       <c r="G432">
-        <v>166.329999999999</v>
+        <v>203.579999999999</v>
       </c>
       <c r="H432">
-        <v>2.77216666666666</v>
+        <v>3.393</v>
       </c>
     </row>
     <row r="433" spans="1:8">
       <c r="A433" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B433" t="s">
+        <v>982</v>
+      </c>
+      <c r="C433" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D433" t="s">
+        <v>9</v>
+      </c>
+      <c r="E433" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F433" t="s">
         <v>983</v>
       </c>
-      <c r="C433" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D433" t="s">
-        <v>9</v>
-      </c>
-      <c r="E433" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F433" t="s">
+      <c r="G433">
+        <v>202</v>
+      </c>
+      <c r="H433">
+        <v>3.36666666666666</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8">
+      <c r="A434" t="s">
         <v>984</v>
       </c>
-      <c r="G433">
+      <c r="B434" t="s">
+        <v>985</v>
+      </c>
+      <c r="C434" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D434" t="s">
+        <v>9</v>
+      </c>
+      <c r="E434" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F434" t="s">
+        <v>986</v>
+      </c>
+      <c r="G434">
         <v>166.329999999999</v>
       </c>
-      <c r="H433">
+      <c r="H434">
         <v>2.77216666666666</v>
-      </c>
-    </row>
-    <row r="434" spans="1:5">
-      <c r="A434" t="s">
-        <v>985</v>
-      </c>
-      <c r="B434" t="s">
-        <v>986</v>
-      </c>
-      <c r="C434" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D434" t="s">
-        <v>16</v>
-      </c>
-      <c r="E434" s="3">
-        <v>46327</v>
       </c>
     </row>
     <row r="435" spans="1:8">
       <c r="A435" t="s">
+        <v>984</v>
+      </c>
+      <c r="B435" t="s">
         <v>987</v>
       </c>
-      <c r="B435" t="s">
+      <c r="C435" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D435" t="s">
+        <v>9</v>
+      </c>
+      <c r="E435" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F435" t="s">
         <v>988</v>
       </c>
-      <c r="C435" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D435" t="s">
-        <v>9</v>
-      </c>
-      <c r="E435" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F435" t="s">
+      <c r="G435">
+        <v>166.329999999999</v>
+      </c>
+      <c r="H435">
+        <v>2.77216666666666</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" t="s">
         <v>989</v>
       </c>
-      <c r="G435">
-        <v>254.75</v>
-      </c>
-      <c r="H435">
-        <v>4.24583333333333</v>
-      </c>
-    </row>
-    <row r="436" spans="1:8">
-      <c r="A436" t="s">
+      <c r="B436" t="s">
         <v>990</v>
       </c>
-      <c r="B436" t="s">
-        <v>991</v>
-      </c>
       <c r="C436" s="2">
         <v>46327</v>
       </c>
       <c r="D436" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E436" s="3">
         <v>46327</v>
-      </c>
-      <c r="F436" t="s">
-        <v>992</v>
-      </c>
-      <c r="G436">
-        <v>278.5</v>
-      </c>
-      <c r="H436">
-        <v>4.64166666666666</v>
       </c>
     </row>
     <row r="437" spans="1:8">
       <c r="A437" t="s">
+        <v>991</v>
+      </c>
+      <c r="B437" t="s">
+        <v>992</v>
+      </c>
+      <c r="C437" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D437" t="s">
+        <v>9</v>
+      </c>
+      <c r="E437" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F437" t="s">
         <v>993</v>
       </c>
-      <c r="B437" t="s">
-        <v>994</v>
-      </c>
-      <c r="C437" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D437" t="s">
-        <v>9</v>
-      </c>
-      <c r="E437" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F437" t="s">
-        <v>995</v>
-      </c>
       <c r="G437">
-        <v>274.08</v>
+        <v>254.75</v>
       </c>
       <c r="H437">
-        <v>4.568</v>
+        <v>4.24583333333333</v>
       </c>
     </row>
     <row r="438" spans="1:8">
       <c r="A438" t="s">
+        <v>994</v>
+      </c>
+      <c r="B438" t="s">
+        <v>995</v>
+      </c>
+      <c r="C438" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D438" t="s">
+        <v>9</v>
+      </c>
+      <c r="E438" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F438" t="s">
         <v>996</v>
       </c>
-      <c r="B438" t="s">
-        <v>997</v>
-      </c>
-      <c r="C438" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D438" t="s">
-        <v>9</v>
-      </c>
-      <c r="E438" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F438" t="s">
-        <v>998</v>
-      </c>
       <c r="G438">
-        <v>237.46</v>
+        <v>278.5</v>
       </c>
       <c r="H438">
-        <v>3.95766666666666</v>
+        <v>4.64166666666666</v>
       </c>
     </row>
     <row r="439" spans="1:8">
       <c r="A439" t="s">
+        <v>997</v>
+      </c>
+      <c r="B439" t="s">
+        <v>998</v>
+      </c>
+      <c r="C439" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D439" t="s">
+        <v>9</v>
+      </c>
+      <c r="E439" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F439" t="s">
         <v>999</v>
       </c>
-      <c r="B439" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C439" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D439" t="s">
-        <v>9</v>
-      </c>
-      <c r="E439" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F439" t="s">
-        <v>1001</v>
-      </c>
       <c r="G439">
-        <v>421.54</v>
+        <v>274.08</v>
       </c>
       <c r="H439">
-        <v>7.02566666666666</v>
+        <v>4.568</v>
       </c>
     </row>
     <row r="440" spans="1:8">
       <c r="A440" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C440" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D440" t="s">
+        <v>9</v>
+      </c>
+      <c r="E440" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F440" t="s">
         <v>1002</v>
       </c>
-      <c r="B440" t="s">
+      <c r="G440">
+        <v>237.46</v>
+      </c>
+      <c r="H440">
+        <v>3.95766666666666</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8">
+      <c r="A441" t="s">
         <v>1003</v>
       </c>
-      <c r="C440" s="2">
-        <v>46327</v>
-      </c>
-      <c r="D440" t="s">
-        <v>9</v>
-      </c>
-      <c r="E440" s="3">
-        <v>46327</v>
-      </c>
-      <c r="F440" t="s">
+      <c r="B441" t="s">
         <v>1004</v>
       </c>
-      <c r="G440">
-        <v>279</v>
-      </c>
-      <c r="H440">
-        <v>4.65</v>
-      </c>
-    </row>
-    <row r="441" spans="1:5">
-      <c r="A441" t="s">
+      <c r="C441" s="2">
+        <v>46327</v>
+      </c>
+      <c r="D441" t="s">
+        <v>9</v>
+      </c>
+      <c r="E441" s="3">
+        <v>46327</v>
+      </c>
+      <c r="F441" t="s">
         <v>1005</v>
       </c>
-      <c r="B441" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="C441" s="2">
-        <v>46327</v>
-      </c>
-      <c r="E441" s="3">
-        <v>46327</v>
+      <c r="G441">
+        <v>421.54</v>
+      </c>
+      <c r="H441">
+        <v>7.02566666666666</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -14665,23 +14732,63 @@
         <v>1007</v>
       </c>
       <c r="C442" s="2">
-        <f>C441+1</f>
-        <v>46328</v>
+        <v>46327</v>
       </c>
       <c r="D442" t="s">
         <v>9</v>
       </c>
       <c r="E442" s="3">
-        <f>E441+1</f>
-        <v>46328</v>
+        <v>46327</v>
       </c>
       <c r="F442" t="s">
         <v>1008</v>
       </c>
       <c r="G442">
+        <v>279</v>
+      </c>
+      <c r="H442">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B443" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C443" s="2">
+        <v>46327</v>
+      </c>
+      <c r="E443" s="3">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8">
+      <c r="A444" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C444" s="2">
+        <f>C443+1</f>
+        <v>46328</v>
+      </c>
+      <c r="D444" t="s">
+        <v>9</v>
+      </c>
+      <c r="E444" s="3">
+        <f>E443+1</f>
+        <v>46328</v>
+      </c>
+      <c r="F444" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G444">
         <v>164.29</v>
       </c>
-      <c r="H442">
+      <c r="H444">
         <v>2.73816666666666</v>
       </c>
     </row>
